--- a/besi/dist/20261025_BESI模型_v0.1.1.xlsx
+++ b/besi/dist/20261025_BESI模型_v0.1.1.xlsx
@@ -6453,26 +6453,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -6491,7 +6472,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D37:F37</t>
+      <t xml:space="preserve">SIF_hbm_den_25</t>
     </r>
   </si>
   <si>
@@ -6540,26 +6521,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -6578,7 +6540,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D38:F38</t>
+      <t xml:space="preserve">SIF_hbm_den_26</t>
     </r>
   </si>
   <si>
@@ -6624,26 +6586,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -6662,7 +6605,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D39:F39</t>
+      <t xml:space="preserve">SIF_hbm_den_27</t>
     </r>
   </si>
   <si>
@@ -6708,26 +6651,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -6746,7 +6670,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D40:F40</t>
+      <t xml:space="preserve">SIF_hbm_den_28</t>
     </r>
   </si>
   <si>
@@ -6792,26 +6716,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -6830,7 +6735,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D41:F41</t>
+      <t xml:space="preserve">SIF_hbm_den_29</t>
     </r>
   </si>
   <si>
@@ -6876,26 +6781,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -6914,7 +6800,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D42:F42</t>
+      <t xml:space="preserve">SIF_hbm_den_30</t>
     </r>
   </si>
   <si>
@@ -6963,26 +6849,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7001,7 +6868,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D43:F43</t>
+      <t xml:space="preserve">SIF_hbm_stk_25</t>
     </r>
   </si>
   <si>
@@ -7077,26 +6944,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7115,7 +6963,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D44:F44</t>
+      <t xml:space="preserve">SIF_hbm_stk_26</t>
     </r>
   </si>
   <si>
@@ -7161,26 +7009,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7199,7 +7028,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D45:F45</t>
+      <t xml:space="preserve">SIF_hbm_stk_27</t>
     </r>
   </si>
   <si>
@@ -7245,26 +7074,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7283,7 +7093,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D46:F46</t>
+      <t xml:space="preserve">SIF_hbm_stk_28</t>
     </r>
   </si>
   <si>
@@ -7329,26 +7139,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7367,7 +7158,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D47:F47</t>
+      <t xml:space="preserve">SIF_hbm_stk_29</t>
     </r>
   </si>
   <si>
@@ -7413,26 +7204,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7451,7 +7223,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D48:F48</t>
+      <t xml:space="preserve">SIF_hbm_stk_30</t>
     </r>
   </si>
   <si>
@@ -7689,26 +7461,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7727,7 +7480,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D66:F66</t>
+      <t xml:space="preserve">SIF_hbm_hbp_25</t>
     </r>
   </si>
   <si>
@@ -8011,26 +7764,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -8049,7 +7783,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D67:F67</t>
+      <t xml:space="preserve">SIF_hbm_hbp_26</t>
     </r>
   </si>
   <si>
@@ -8132,26 +7866,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -8170,7 +7885,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D68:F68</t>
+      <t xml:space="preserve">SIF_hbm_hbp_27</t>
     </r>
   </si>
   <si>
@@ -8253,26 +7968,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -8291,7 +7987,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D69:F69</t>
+      <t xml:space="preserve">SIF_hbm_hbp_28</t>
     </r>
   </si>
   <si>
@@ -8374,26 +8070,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -8412,7 +8089,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D70:F70</t>
+      <t xml:space="preserve">SIF_hbm_hbp_29</t>
     </r>
   </si>
   <si>
@@ -8495,26 +8172,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">disco/dist/20261025_Disco</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -8533,7 +8191,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D71:F71</t>
+      <t xml:space="preserve">SIF_hbm_hbp_30</t>
     </r>
   </si>
   <si>

--- a/besi/dist/20261025_BESI模型_v0.1.1.xlsx
+++ b/besi/dist/20261025_BESI模型_v0.1.1.xlsx
@@ -8452,26 +8452,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8808,26 +8808,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8978,26 +8978,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9099,26 +9099,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9220,26 +9220,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9341,26 +9341,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9462,26 +9462,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/besi/dist/20261025_BESI模型_v0.1.1.xlsx
+++ b/besi/dist/20261025_BESI模型_v0.1.1.xlsx
@@ -4712,26 +4712,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5305,26 +5305,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5760,26 +5760,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/besi/dist/20261025_BESI模型_v0.1.1.xlsx
+++ b/besi/dist/20261025_BESI模型_v0.1.1.xlsx
@@ -226,6 +226,7 @@
     <definedName function="false" hidden="false" name="q4opx_hi" vbProcedure="false">In!$F$82</definedName>
     <definedName function="false" hidden="false" name="q4opx_lo" vbProcedure="false">In!$D$82</definedName>
     <definedName function="false" hidden="false" name="rev26" vbProcedure="false">In!$E$84</definedName>
+    <definedName function="false" hidden="false" name="rm_factor" vbProcedure="false">Val!$B$143</definedName>
     <definedName function="false" hidden="false" name="shares" vbProcedure="false">In!$E$112</definedName>
     <definedName function="false" hidden="false" name="shl_A" vbProcedure="false">In!$E$76</definedName>
     <definedName function="false" hidden="false" name="shl_A_hi" vbProcedure="false">In!$F$76</definedName>
@@ -267,6 +268,7 @@
     <definedName function="false" hidden="false" name="tax_hi" vbProcedure="false">In!$F$111</definedName>
     <definedName function="false" hidden="false" name="tax_lo" vbProcedure="false">In!$D$111</definedName>
     <definedName function="false" hidden="false" name="thr" vbProcedure="false">In!$E$71</definedName>
+    <definedName function="false" hidden="false" name="tp_comp_adj" vbProcedure="false">Val!$B$144</definedName>
     <definedName function="false" hidden="false" name="tp_g" vbProcedure="false">In!$E$134</definedName>
     <definedName function="false" hidden="false" name="tp_r" vbProcedure="false">In!$E$133</definedName>
     <definedName function="false" hidden="false" name="tp_roe" vbProcedure="false">In!$E$135</definedName>
@@ -297,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3834" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3891" uniqueCount="905">
   <si>
     <r>
       <rPr>
@@ -3127,45 +3129,685 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：目標價 €</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">133.69</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF 97.68</t>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：本模型 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月後前瞻 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPS 6.52 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">比共識前瞻 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPS 8.14 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；共識目標價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">270.57 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隱含 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍，同業中位數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">26.0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍（倍數因素 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+27.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：最敏感的是邏輯（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SoIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">類）混合鍵合導入速度：導入比例 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×0.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×1.3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">使 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 EPS −22.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+22.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，改走情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">路徑 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12.2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合鍵合取 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Disco </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低值 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7.2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。下一個檢驗事件是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q4-26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">財報（約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027-02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下旬）的混合鍵合訂單（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q3-26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">訂單 €</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">342.6M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：加權目標價中的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改用相對倍數調整後的值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節：同業前瞻倍數中位數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年相對同業的倍數比，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前瞻倍數；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy 2026-10-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「照建議做」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料取回）。「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）」維持不調整。重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的第一句已改為公式；重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -3184,836 +3826,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Comparable 169.71 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">各半），比現價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">145.10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-23</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）低 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，級距 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～−</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Comparable </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">單獨為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+17.0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低是情境分歧造成：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">情境價值 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A 158.4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（現價的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.09 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍）、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B 82.4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C 44.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 EPS 6.59 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">比 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9.37 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：本模型 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">個月後前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS 6.52 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">比共識前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS 8.14 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">19.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；共識目標價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">270.57 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隱含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">33.2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍，同業中位數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">26.0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍（倍數因素 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+27.7%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：最敏感的是邏輯（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SoIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">類）混合鍵合導入速度：導入比例 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×0.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×1.3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">使 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027 EPS −22.0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+22.0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，改走情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">路徑 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合取 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Disco </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低值 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。下一個檢驗事件是 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Q4-26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">財報（約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027-02 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下旬）的混合鍵合訂單（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Q3-26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">訂單 €</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">342.6M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。</t>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與其他說明中的目標價與上檔空間數字為調整前撰寫，以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁為準。</t>
     </r>
   </si>
   <si>
@@ -29930,97 +29771,14 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Recon — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本模型 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">共識、公司長期目標、累計訂單。只作事後對照，不為對上數字而調整參數。差距 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt; 10% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的原因見 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">README</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">對照值</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">模型 </t>
-    </r>
-    <r>
-      <rPr>
         <b val="true"/>
         <sz val="11"/>
         <rFont val="Cambria"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">0.5 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -30028,7 +29786,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">差距 </t>
+      <t xml:space="preserve">相對倍數調整（</t>
     </r>
     <r>
       <rPr>
@@ -30038,10 +29796,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">Comparable </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -30049,7 +29805,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">模型 </t>
+      <t xml:space="preserve">目標倍數＝同業中位數 </t>
     </r>
     <r>
       <rPr>
@@ -30059,10 +29815,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">× </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -30070,7 +29824,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">差距 </t>
+      <t xml:space="preserve">本公司 </t>
     </r>
     <r>
       <rPr>
@@ -30080,10 +29834,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">10 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -30091,7 +29843,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">模型 </t>
+      <t xml:space="preserve">年相對同業的 </t>
     </r>
     <r>
       <rPr>
@@ -30101,10 +29853,8 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">P/E </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -30112,7 +29862,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">差距 </t>
+      <t xml:space="preserve">比；</t>
     </r>
     <r>
       <rPr>
@@ -30122,11 +29872,352 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">對照來源</t>
+      <t xml:space="preserve">Andy 2026-10-27 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新增，放在本頁最後以免位移既有儲存格）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2017–2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各年度窗口（前一年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月～當年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月底前瞻 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）的中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/data/fwd_mult_hist.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Verified] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Derived] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">彙總；有效值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 &lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">值 ≤ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，無效值以「剔除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」文字列示、不進中位數。本公司或同業有效年數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不納入；有效同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">家或本公司不足時係數＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016/11–2017/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017/11–2018/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018/11–2019/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019/11–2020/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020/11–2021/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/11–2022/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022/11–2023/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023/11–2024/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/11–2025/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11–2026/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有效年數</t>
   </si>
   <si>
     <r>
@@ -30137,7 +30228,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A. FY2026 vs </t>
+      <t xml:space="preserve">10 </t>
     </r>
     <r>
       <rPr>
@@ -30146,35 +30237,642 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">共識（校準未使用）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">錨點＝前三季實績＋第四季指引中點</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（歐元）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">stockanalysis 4.42</t>
+      <t xml:space="preserve">年中位數</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">納入值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BESI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BESI.AS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本公司</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg BESI NA Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">同業</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg ASM NA Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 0522 HK Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg KLIC US Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 6146 JT Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 042700 KS Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數（納入值）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">空白＝本公司有效年數不足</t>
+  </si>
+  <si>
+    <t xml:space="preserve">納入的同業家數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數的中位數</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原始比值（本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝本公司長期比同業便宜（折價），＞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝長期溢價</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值下限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避免單一歷史異常主導；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_LO</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值上限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_HI</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">相對倍數調整係數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料不足時＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -30185,7 +30883,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">B. FY2027–FY2028 vs </t>
+      <t xml:space="preserve">Comparable </t>
     </r>
     <r>
       <rPr>
@@ -30194,97 +30892,140 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">共識（第三季財報前的共識）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">marketscreener</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027 EPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（歐元）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 EPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（歐元）</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">目標價（相對倍數調整後）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">調整係數；加權目標價使用本列</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Recon — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本模型 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">共識、公司長期目標、累計訂單。只作事後對照，不為對上數字而調整參數。差距 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt; 10% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的原因見 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">README</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">對照值</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模型 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -30293,8 +31034,10 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">C. </t>
-    </r>
+      <t xml:space="preserve">A</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -30302,438 +31045,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">公司長期目標與累計訂單</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2029 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">長期目標下緣 €</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.7B</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">投資人日 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-06-19</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（目標年度未載明）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2029 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">長期目標上緣 €</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2.2B</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合隱含機台數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs 2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年前三季新增訂單（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">215 − 150</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公司：累計 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">150</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋→ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">215</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋台</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">口徑：營收（出貨）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">訂單；邏輯機台單價可能與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不同</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sens — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一次動一個輸入（情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）：對 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的影響。每個案例是一個完整的推導區塊（本頁下方，與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同一引擎；校準係數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">k </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">在各區塊內重算）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">案例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">設定</t>
-  </si>
-  <si>
+      <t xml:space="preserve">差距 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -30742,8 +31055,10 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">FY2027 </t>
-    </r>
+      <t xml:space="preserve">A</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -30751,7 +31066,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">營收 €</t>
+      <t xml:space="preserve">模型 </t>
     </r>
     <r>
       <rPr>
@@ -30761,16 +31076,19 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">M</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">FY2027 EPS €</t>
-  </si>
-  <si>
-    <t xml:space="preserve">相對基準</t>
-  </si>
-  <si>
+      <t xml:space="preserve">B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">差距 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -30779,8 +31097,10 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">FY2028 </t>
-    </r>
+      <t xml:space="preserve">B</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -30788,7 +31108,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">營收 €</t>
+      <t xml:space="preserve">模型 </t>
     </r>
     <r>
       <rPr>
@@ -30798,1268 +31118,18 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">M</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">FY2028 EPS €</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">基準（情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">區塊 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Disco </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">基準</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028 5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2029 15%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2030 25%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Disco </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低值</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028 0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2029 5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2030 10%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">邏輯導入 低（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×0.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起各年比例 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 0.7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">邏輯導入 高（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×1.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">邏輯導入 取情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">路徑</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合占比 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">k </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">較低、主流業務基期較高</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合占比 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">35%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">k </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">較高、主流業務基期較低</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機台有效產出 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">600</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／時</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">機台數較多</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機台有效產出 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,500</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／時</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機台單價 €</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2.0M</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">機台單價 €</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3.5M</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BESI HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">份額 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10pt</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">50%</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BESI HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">份額 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+10pt</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">70%</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">邏輯相對份額 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.9</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">晶粒容量 低</t>
-  </si>
-  <si>
-    <t xml:space="preserve">各年取低值（晶粒較多）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">晶粒容量 高</t>
-  </si>
-  <si>
-    <t xml:space="preserve">各年取高值（晶粒較少）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰換比例 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汰換比例 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">主流業務彈性 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">主流業務彈性 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合毛利溢價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合毛利溢價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15pt</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業費用變動比例 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業費用變動比例 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">60%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">第四季營收 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">錨點較低 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">k</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、主流基期較低</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">第四季營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+5%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">稅率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上游皆取 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合基準；邏輯導入、份額取 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">情境 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">C</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上游皆取 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合低值；邏輯導入慢、份額流失、毛利率下調</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">讀法：機台比產能早一年買，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的營收看 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CY2027→2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的需求增量。邏輯段的校準係數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">k </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">由 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收推得，導入比例的水準被 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">k </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">吸收，只有比例的變化（斜率）影響之後各年；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合占比同時改變 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">k </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">與主流業務基期，兩者方向相反。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b val="true"/>
         <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：</t>
+      <t xml:space="preserve">差距 </t>
     </r>
     <r>
       <rPr>
@@ -32069,17 +31139,13 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合 </t>
-    </r>
+      <t xml:space="preserve">C</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">對照來源</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -32088,7 +31154,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Disco </t>
+      <t xml:space="preserve">A. FY2026 vs </t>
     </r>
     <r>
       <rPr>
@@ -32097,8 +31163,37 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">基準（情境 </t>
-    </r>
+      <t xml:space="preserve">共識（校準未使用）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">錨點＝前三季實績＋第四季指引中點</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（歐元）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">stockanalysis 4.42</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -32107,7 +31202,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">B. FY2027–FY2028 vs </t>
     </r>
     <r>
       <rPr>
@@ -32116,19 +31211,97 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：</t>
-    </r>
+      <t xml:space="preserve">共識（第三季財報前的共識）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">marketscreener</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（歐元）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 EPS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（歐元）</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -32137,17 +31310,447 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">C. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司長期目標與累計訂單</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長期目標下緣 €</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.7B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投資人日 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-06-19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（目標年度未載明）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長期目標上緣 €</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.2B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合鍵合隱含機台數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs 2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年前三季新增訂單（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">215 − 150</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司：累計 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">150</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋→ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">215</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋台</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">口徑：營收（出貨）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">訂單；邏輯機台單價可能與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">HBM </t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">混合鍵合 </t>
-    </r>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不同</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sens — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一次動一個輸入（情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：對 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的影響。每個案例是一個完整的推導區塊（本頁下方，與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同一引擎；校準係數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">在各區塊內重算）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">案例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設定</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -32156,7 +31759,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Disco </t>
+      <t xml:space="preserve">FY2027 </t>
     </r>
     <r>
       <rPr>
@@ -32165,7 +31768,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">低值（情境 </t>
+      <t xml:space="preserve">營收 €</t>
     </r>
     <r>
       <rPr>
@@ -32175,28 +31778,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：邏輯導入 低（</t>
-    </r>
+      <t xml:space="preserve">M</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2027 EPS €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">相對基準</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -32205,7 +31796,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">×0.7</t>
+      <t xml:space="preserve">FY2028 </t>
     </r>
     <r>
       <rPr>
@@ -32214,7 +31805,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）（情境 </t>
+      <t xml:space="preserve">營收 €</t>
     </r>
     <r>
       <rPr>
@@ -32224,27 +31815,1268 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">M</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">FY2028 EPS €</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基準（情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">區塊 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合鍵合 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Disco </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基準</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 15%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2030 25%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合鍵合 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Disco </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2030 10%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">邏輯導入 低（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×0.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起各年比例 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 0.7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">邏輯導入 高（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×1.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">邏輯導入 取情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">路徑</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合鍵合占比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">較低、主流業務基期較高</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合鍵合占比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">35%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">較高、主流業務基期較低</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機台有效產出 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">600</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／時</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">機台數較多</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機台有效產出 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／時</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機台單價 €</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.0M</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機台單價 €</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.5M</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BESI HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">份額 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10pt</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">50%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BESI HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">份額 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+10pt</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">70%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">邏輯相對份額 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.9</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">晶粒容量 低</t>
+  </si>
+  <si>
+    <t xml:space="preserve">各年取低值（晶粒較多）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">晶粒容量 高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">各年取高值（晶粒較少）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">汰換比例 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">汰換比例 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">主流業務彈性 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">主流業務彈性 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合鍵合毛利溢價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合鍵合毛利溢價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15pt</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業費用變動比例 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業費用變動比例 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">60%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第四季營收 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">錨點較低 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、主流基期較低</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第四季營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+5%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">稅率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上游皆取 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合鍵合基準；邏輯導入、份額取 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上游皆取 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合鍵合低值；邏輯導入慢、份額流失、毛利率下調</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">讀法：機台比產能早一年買，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的營收看 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CY2027→2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的需求增量。邏輯段的校準係數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">由 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收推得，導入比例的水準被 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">吸收，只有比例的變化（斜率）影響之後各年；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">混合鍵合占比同時改變 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">k </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與主流業務基期，兩者方向相反。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b val="true"/>
         <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：邏輯導入 高（</t>
+      <t xml:space="preserve">案例區塊：</t>
     </r>
     <r>
       <rPr>
@@ -32254,7 +33086,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">×1.3</t>
+      <t xml:space="preserve">HBM </t>
     </r>
     <r>
       <rPr>
@@ -32263,7 +33095,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）（情境 </t>
+      <t xml:space="preserve">混合鍵合 </t>
     </r>
     <r>
       <rPr>
@@ -32273,7 +33105,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">Disco </t>
     </r>
     <r>
       <rPr>
@@ -32282,18 +33114,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：邏輯導入 取情境 </t>
+      <t xml:space="preserve">基準（情境 </t>
     </r>
     <r>
       <rPr>
@@ -32303,7 +33124,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">B </t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -32312,7 +33133,18 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">路徑（情境 </t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案例區塊：</t>
     </r>
     <r>
       <rPr>
@@ -32322,7 +33154,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">HBM </t>
     </r>
     <r>
       <rPr>
@@ -32331,18 +33163,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：</t>
+      <t xml:space="preserve">混合鍵合 </t>
     </r>
     <r>
       <rPr>
@@ -32352,7 +33173,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">FY2026 </t>
+      <t xml:space="preserve">Disco </t>
     </r>
     <r>
       <rPr>
@@ -32361,7 +33182,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">混合鍵合占比 </t>
+      <t xml:space="preserve">低值（情境 </t>
     </r>
     <r>
       <rPr>
@@ -32371,7 +33192,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">18%</t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -32380,7 +33201,18 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（情境 </t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案例區塊：邏輯導入 低（</t>
     </r>
     <r>
       <rPr>
@@ -32390,7 +33222,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">×0.7</t>
     </r>
     <r>
       <rPr>
@@ -32399,18 +33231,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：</t>
+      <t xml:space="preserve">）（情境 </t>
     </r>
     <r>
       <rPr>
@@ -32420,7 +33241,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">FY2026 </t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -32429,7 +33250,18 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">混合鍵合占比 </t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案例區塊：邏輯導入 高（</t>
     </r>
     <r>
       <rPr>
@@ -32439,7 +33271,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">35%</t>
+      <t xml:space="preserve">×1.3</t>
     </r>
     <r>
       <rPr>
@@ -32448,7 +33280,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（情境 </t>
+      <t xml:space="preserve">）（情境 </t>
     </r>
     <r>
       <rPr>
@@ -32478,7 +33310,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：機台有效產出 </t>
+      <t xml:space="preserve">案例區塊：邏輯導入 取情境 </t>
     </r>
     <r>
       <rPr>
@@ -32488,7 +33320,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">600</t>
+      <t xml:space="preserve">B </t>
     </r>
     <r>
       <rPr>
@@ -32497,7 +33329,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">／時（情境 </t>
+      <t xml:space="preserve">路徑（情境 </t>
     </r>
     <r>
       <rPr>
@@ -32527,7 +33359,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：機台有效產出 </t>
+      <t xml:space="preserve">案例區塊：</t>
     </r>
     <r>
       <rPr>
@@ -32537,7 +33369,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1,500</t>
+      <t xml:space="preserve">FY2026 </t>
     </r>
     <r>
       <rPr>
@@ -32546,7 +33378,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">／時（情境 </t>
+      <t xml:space="preserve">混合鍵合占比 </t>
     </r>
     <r>
       <rPr>
@@ -32556,7 +33388,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">18%</t>
     </r>
     <r>
       <rPr>
@@ -32565,18 +33397,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：</t>
+      <t xml:space="preserve">（情境 </t>
     </r>
     <r>
       <rPr>
@@ -32586,7 +33407,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">HBM </t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -32595,7 +33416,18 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">機台單價 €</t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案例區塊：</t>
     </r>
     <r>
       <rPr>
@@ -32605,7 +33437,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2.0M</t>
+      <t xml:space="preserve">FY2026 </t>
     </r>
     <r>
       <rPr>
@@ -32614,7 +33446,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（情境 </t>
+      <t xml:space="preserve">混合鍵合占比 </t>
     </r>
     <r>
       <rPr>
@@ -32624,7 +33456,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">35%</t>
     </r>
     <r>
       <rPr>
@@ -32633,18 +33465,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：</t>
+      <t xml:space="preserve">（情境 </t>
     </r>
     <r>
       <rPr>
@@ -32654,7 +33475,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">HBM </t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -32663,7 +33484,18 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">機台單價 €</t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案例區塊：機台有效產出 </t>
     </r>
     <r>
       <rPr>
@@ -32673,7 +33505,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3.5M</t>
+      <t xml:space="preserve">600</t>
     </r>
     <r>
       <rPr>
@@ -32682,7 +33514,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（情境 </t>
+      <t xml:space="preserve">／時（情境 </t>
     </r>
     <r>
       <rPr>
@@ -32712,7 +33544,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：</t>
+      <t xml:space="preserve">案例區塊：機台有效產出 </t>
     </r>
     <r>
       <rPr>
@@ -32722,7 +33554,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">BESI HBM </t>
+      <t xml:space="preserve">1,500</t>
     </r>
     <r>
       <rPr>
@@ -32731,7 +33563,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">份額 −</t>
+      <t xml:space="preserve">／時（情境 </t>
     </r>
     <r>
       <rPr>
@@ -32741,7 +33573,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">10pt</t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -32750,7 +33582,18 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（情境 </t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案例區塊：</t>
     </r>
     <r>
       <rPr>
@@ -32760,7 +33603,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">HBM </t>
     </r>
     <r>
       <rPr>
@@ -32769,18 +33612,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：</t>
+      <t xml:space="preserve">機台單價 €</t>
     </r>
     <r>
       <rPr>
@@ -32790,7 +33622,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">BESI HBM </t>
+      <t xml:space="preserve">2.0M</t>
     </r>
     <r>
       <rPr>
@@ -32799,7 +33631,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">份額 </t>
+      <t xml:space="preserve">（情境 </t>
     </r>
     <r>
       <rPr>
@@ -32809,7 +33641,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+10pt</t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -32818,7 +33650,18 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（情境 </t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案例區塊：</t>
     </r>
     <r>
       <rPr>
@@ -32828,7 +33671,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">HBM </t>
     </r>
     <r>
       <rPr>
@@ -32837,18 +33680,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：邏輯相對份額 </t>
+      <t xml:space="preserve">機台單價 €</t>
     </r>
     <r>
       <rPr>
@@ -32858,7 +33690,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.9</t>
+      <t xml:space="preserve">3.5M</t>
     </r>
     <r>
       <rPr>
@@ -32897,7 +33729,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：晶粒容量 低（情境 </t>
+      <t xml:space="preserve">案例區塊：</t>
     </r>
     <r>
       <rPr>
@@ -32907,7 +33739,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">BESI HBM </t>
     </r>
     <r>
       <rPr>
@@ -32916,18 +33748,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：晶粒容量 高（情境 </t>
+      <t xml:space="preserve">份額 −</t>
     </r>
     <r>
       <rPr>
@@ -32937,7 +33758,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">10pt</t>
     </r>
     <r>
       <rPr>
@@ -32946,18 +33767,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：汰換比例 </t>
+      <t xml:space="preserve">（情境 </t>
     </r>
     <r>
       <rPr>
@@ -32967,7 +33777,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5%</t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -32976,7 +33786,18 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（情境 </t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案例區塊：</t>
     </r>
     <r>
       <rPr>
@@ -32986,7 +33807,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A</t>
+      <t xml:space="preserve">BESI HBM </t>
     </r>
     <r>
       <rPr>
@@ -32995,18 +33816,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案例區塊：汰換比例 </t>
+      <t xml:space="preserve">份額 </t>
     </r>
     <r>
       <rPr>
@@ -33016,7 +33826,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">15%</t>
+      <t xml:space="preserve">+10pt</t>
     </r>
     <r>
       <rPr>
@@ -33055,7 +33865,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：主流業務彈性 </t>
+      <t xml:space="preserve">案例區塊：邏輯相對份額 </t>
     </r>
     <r>
       <rPr>
@@ -33065,7 +33875,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.5</t>
+      <t xml:space="preserve">0.9</t>
     </r>
     <r>
       <rPr>
@@ -33104,7 +33914,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：主流業務彈性 </t>
+      <t xml:space="preserve">案例區塊：晶粒容量 低（情境 </t>
     </r>
     <r>
       <rPr>
@@ -33114,7 +33924,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1.5</t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -33123,7 +33933,18 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（情境 </t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案例區塊：晶粒容量 高（情境 </t>
     </r>
     <r>
       <rPr>
@@ -33153,7 +33974,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：混合鍵合毛利溢價 </t>
+      <t xml:space="preserve">案例區塊：汰換比例 </t>
     </r>
     <r>
       <rPr>
@@ -33163,7 +33984,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0</t>
+      <t xml:space="preserve">5%</t>
     </r>
     <r>
       <rPr>
@@ -33202,7 +34023,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：混合鍵合毛利溢價 </t>
+      <t xml:space="preserve">案例區塊：汰換比例 </t>
     </r>
     <r>
       <rPr>
@@ -33212,7 +34033,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">15pt</t>
+      <t xml:space="preserve">15%</t>
     </r>
     <r>
       <rPr>
@@ -33251,7 +34072,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：營業費用變動比例 </t>
+      <t xml:space="preserve">案例區塊：主流業務彈性 </t>
     </r>
     <r>
       <rPr>
@@ -33261,7 +34082,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">25%</t>
+      <t xml:space="preserve">0.5</t>
     </r>
     <r>
       <rPr>
@@ -33300,7 +34121,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：營業費用變動比例 </t>
+      <t xml:space="preserve">案例區塊：主流業務彈性 </t>
     </r>
     <r>
       <rPr>
@@ -33310,7 +34131,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">60%</t>
+      <t xml:space="preserve">1.5</t>
     </r>
     <r>
       <rPr>
@@ -33349,7 +34170,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：第四季營收 −</t>
+      <t xml:space="preserve">案例區塊：混合鍵合毛利溢價 </t>
     </r>
     <r>
       <rPr>
@@ -33359,7 +34180,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5%</t>
+      <t xml:space="preserve">0</t>
     </r>
     <r>
       <rPr>
@@ -33398,7 +34219,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：第四季營收 </t>
+      <t xml:space="preserve">案例區塊：混合鍵合毛利溢價 </t>
     </r>
     <r>
       <rPr>
@@ -33408,7 +34229,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+5%</t>
+      <t xml:space="preserve">15pt</t>
     </r>
     <r>
       <rPr>
@@ -33447,7 +34268,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">案例區塊：稅率 </t>
+      <t xml:space="preserve">案例區塊：營業費用變動比例 </t>
     </r>
     <r>
       <rPr>
@@ -33457,7 +34278,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">16%</t>
+      <t xml:space="preserve">25%</t>
     </r>
     <r>
       <rPr>
@@ -33496,7 +34317,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">目標價參數（只改 </t>
+      <t xml:space="preserve">案例區塊：營業費用變動比例 </t>
     </r>
     <r>
       <rPr>
@@ -33506,7 +34327,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF </t>
+      <t xml:space="preserve">60%</t>
     </r>
     <r>
       <rPr>
@@ -33515,7 +34336,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">參數與權重，</t>
+      <t xml:space="preserve">（情境 </t>
     </r>
     <r>
       <rPr>
@@ -33525,7 +34346,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PL </t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -33534,7 +34355,18 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">收斂法的長期成長不隨 </t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案例區塊：第四季營收 −</t>
     </r>
     <r>
       <rPr>
@@ -33544,7 +34376,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tp_g </t>
+      <t xml:space="preserve">5%</t>
     </r>
     <r>
       <rPr>
@@ -33553,7 +34385,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">變動；</t>
+      <t xml:space="preserve">（情境 </t>
     </r>
     <r>
       <rPr>
@@ -33563,7 +34395,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF </t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -33572,7 +34404,18 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">負值取 </t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案例區塊：第四季營收 </t>
     </r>
     <r>
       <rPr>
@@ -33582,7 +34425,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0</t>
+      <t xml:space="preserve">+5%</t>
     </r>
     <r>
       <rPr>
@@ -33591,10 +34434,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">（情境 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -33603,7 +34444,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF </t>
+      <t xml:space="preserve">A</t>
     </r>
     <r>
       <rPr>
@@ -33612,10 +34453,19 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">目標價</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案例區塊：稅率 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -33624,7 +34474,153 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Comparable </t>
+      <t xml:space="preserve">16%</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價參數（只改 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">參數與權重，</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PL </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收斂法的長期成長不隨 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tp_g </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">變動；</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">負值取 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
     </r>
     <r>
       <rPr>
@@ -35183,7 +36179,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0%"/>
@@ -35194,6 +36190,7 @@
     <numFmt numFmtId="171" formatCode="0.0"/>
     <numFmt numFmtId="172" formatCode="0.000"/>
     <numFmt numFmtId="173" formatCode="@"/>
+    <numFmt numFmtId="174" formatCode="0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -35316,7 +36313,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -35454,6 +36451,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -35709,7 +36710,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="170"/>
@@ -35801,17 +36802,23 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>14</v>
+      <c r="A19" s="0" t="str">
+        <f aca="false">"重點觀察 1：目標價 €"&amp;TEXT(Val!$B$112,"#,##0.00")&amp;"（DCF "&amp;TEXT(Val!$B$97,"#,##0.00")&amp;"、Comparable（相對倍數調整後）"&amp;TEXT(tp_comp_adj,"#,##0.00")&amp;"；DCF 權重 "&amp;TEXT(tp_w_dcf,"0%")&amp;"），比現價 "&amp;TEXT(px,"#,##0.00")&amp;"（2026-10-23）"&amp;IF(Val!$B$115&gt;=0,"高 "&amp;TEXT(Val!$B$115,"0.0%"),"低 "&amp;TEXT(-Val!$B$115,"0.0%"))&amp;"，級距 "&amp;Val!$B$123&amp;"、投資建議 "&amp;Val!$B$124&amp;"。相對倍數調整係數 "&amp;TEXT(rm_factor,"0.00")&amp;"（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 "&amp;TEXT((tp_w_dcf*Val!$B$97+(1-tp_w_dcf)*Val!$B$108)/px-1,"+0.0%;−0.0%")&amp;"；Comparable 單獨（市場主流同業法、未調整）為 "&amp;TEXT(Val!$B$116,"+0.0%;−0.0%")&amp;"。"&amp;"以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：DCF 低是情境分歧造成：DCF 情境價值 A 158.4（現價的 1.09 倍）、B 82.4、C 44.8，B 的 FY2028 EPS 6.59 比 A 的 9.37 低 30%。"</f>
+        <v>重點觀察 1：目標價 €159.93（DCF 97.68、Comparable（相對倍數調整後）222.18；DCF 權重 50%），比現價 145.10（2026-10-23）高 10.2%，級距 0%–25%、投資建議 中立。相對倍數調整係數 1.31（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 −7.9%；Comparable 單獨（市場主流同業法、未調整）為 +17.0%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：DCF 低是情境分歧造成：DCF 情境價值 A 158.4（現價的 1.09 倍）、B 82.4、C 44.8，B 的 FY2028 EPS 6.59 比 A 的 9.37 低 30%。</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
         <v>16</v>
       </c>
     </row>
@@ -44599,7 +45606,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:Q144"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -46363,8 +47370,8 @@
         <v>687</v>
       </c>
       <c r="B112" s="33" t="n">
-        <f aca="false">tp_w_dcf*B97+(1-tp_w_dcf)*B108</f>
-        <v>133.694918094684</v>
+        <f aca="false">tp_w_dcf*B97+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>159.929027934149</v>
       </c>
       <c r="E112" s="8" t="s">
         <v>688</v>
@@ -46400,7 +47407,7 @@
       </c>
       <c r="B115" s="10" t="n">
         <f aca="false">B112/px-1</f>
-        <v>-0.0786015293267841</v>
+        <v>0.10219867632081</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>693</v>
@@ -46486,7 +47493,7 @@
       </c>
       <c r="B123" s="34" t="str">
         <f aca="false">IF(B115&gt;0.5,"大於 50%",IF(B115&gt;0.25,"25%–50%",IF(B115&gt;=0,"0%–25%",IF(B115&gt;=-0.25,"0%～−25%",IF(B115&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v>0%～−25%</v>
+        <v>0%–25%</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>705</v>
@@ -46502,6 +47509,493 @@
       </c>
       <c r="E124" s="5" t="s">
         <v>707</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="5" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="D129" s="14" t="s">
+        <v>712</v>
+      </c>
+      <c r="E129" s="14" t="s">
+        <v>713</v>
+      </c>
+      <c r="F129" s="14" t="s">
+        <v>714</v>
+      </c>
+      <c r="G129" s="14" t="s">
+        <v>715</v>
+      </c>
+      <c r="H129" s="14" t="s">
+        <v>716</v>
+      </c>
+      <c r="I129" s="14" t="s">
+        <v>717</v>
+      </c>
+      <c r="J129" s="14" t="s">
+        <v>718</v>
+      </c>
+      <c r="K129" s="14" t="s">
+        <v>719</v>
+      </c>
+      <c r="L129" s="14" t="s">
+        <v>720</v>
+      </c>
+      <c r="M129" s="14" t="s">
+        <v>721</v>
+      </c>
+      <c r="N129" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="O129" s="14" t="s">
+        <v>723</v>
+      </c>
+      <c r="P129" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="Q129" s="6" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="0" t="s">
+        <v>725</v>
+      </c>
+      <c r="B130" s="0" t="s">
+        <v>726</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>727</v>
+      </c>
+      <c r="D130" s="17" t="n">
+        <v>16.997</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>12.1645</v>
+      </c>
+      <c r="F130" s="17" t="n">
+        <v>17.0685</v>
+      </c>
+      <c r="G130" s="17" t="n">
+        <v>26.015</v>
+      </c>
+      <c r="H130" s="17" t="n">
+        <v>23.457</v>
+      </c>
+      <c r="I130" s="17" t="n">
+        <v>18.0605</v>
+      </c>
+      <c r="J130" s="17" t="n">
+        <v>29.8845</v>
+      </c>
+      <c r="K130" s="17" t="n">
+        <v>38.1565</v>
+      </c>
+      <c r="L130" s="17" t="n">
+        <v>37.0955</v>
+      </c>
+      <c r="M130" s="17" t="n">
+        <v>44.0715</v>
+      </c>
+      <c r="N130" s="8" t="n">
+        <f aca="false">COUNT(D130:M130)</f>
+        <v>10</v>
+      </c>
+      <c r="O130" s="18" t="n">
+        <f aca="false">IF(N130&gt;0,MEDIAN(D130:M130),"")</f>
+        <v>24.736</v>
+      </c>
+      <c r="P130" s="18" t="n">
+        <f aca="false">IF(N130&gt;=7,O130,"")</f>
+        <v>24.736</v>
+      </c>
+      <c r="Q130" s="8" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="0" t="s">
+        <v>663</v>
+      </c>
+      <c r="B131" s="0" t="s">
+        <v>664</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="D131" s="17" t="n">
+        <v>14.9905</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>13.2105</v>
+      </c>
+      <c r="F131" s="17" t="n">
+        <v>13.653</v>
+      </c>
+      <c r="G131" s="17" t="n">
+        <v>18.9585</v>
+      </c>
+      <c r="H131" s="17" t="n">
+        <v>29.3795</v>
+      </c>
+      <c r="I131" s="17" t="n">
+        <v>22.5025</v>
+      </c>
+      <c r="J131" s="17" t="n">
+        <v>28.161</v>
+      </c>
+      <c r="K131" s="17" t="n">
+        <v>37.435</v>
+      </c>
+      <c r="L131" s="17" t="n">
+        <v>29.427</v>
+      </c>
+      <c r="M131" s="17" t="n">
+        <v>32.259</v>
+      </c>
+      <c r="N131" s="8" t="n">
+        <f aca="false">COUNT(D131:M131)</f>
+        <v>10</v>
+      </c>
+      <c r="O131" s="18" t="n">
+        <f aca="false">IF(N131&gt;0,MEDIAN(D131:M131),"")</f>
+        <v>25.33175</v>
+      </c>
+      <c r="P131" s="18" t="n">
+        <f aca="false">IF(N131&gt;=7,O131,"")</f>
+        <v>25.33175</v>
+      </c>
+      <c r="Q131" s="8" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="0" t="s">
+        <v>667</v>
+      </c>
+      <c r="B132" s="0" t="s">
+        <v>668</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="D132" s="17" t="n">
+        <v>18.5965</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>14.378</v>
+      </c>
+      <c r="F132" s="17" t="n">
+        <v>16.3415</v>
+      </c>
+      <c r="G132" s="17" t="n">
+        <v>21.023</v>
+      </c>
+      <c r="H132" s="17" t="n">
+        <v>19.1925</v>
+      </c>
+      <c r="I132" s="17" t="n">
+        <v>10.5945</v>
+      </c>
+      <c r="J132" s="17" t="n">
+        <v>14.305</v>
+      </c>
+      <c r="K132" s="17" t="n">
+        <v>23.1025</v>
+      </c>
+      <c r="L132" s="17" t="n">
+        <v>20.718</v>
+      </c>
+      <c r="M132" s="17" t="n">
+        <v>29.0835</v>
+      </c>
+      <c r="N132" s="8" t="n">
+        <f aca="false">COUNT(D132:M132)</f>
+        <v>10</v>
+      </c>
+      <c r="O132" s="18" t="n">
+        <f aca="false">IF(N132&gt;0,MEDIAN(D132:M132),"")</f>
+        <v>18.8945</v>
+      </c>
+      <c r="P132" s="18" t="n">
+        <f aca="false">IF(N132&gt;=7,O132,"")</f>
+        <v>18.8945</v>
+      </c>
+      <c r="Q132" s="8" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="0" t="s">
+        <v>671</v>
+      </c>
+      <c r="B133" s="0" t="s">
+        <v>672</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="D133" s="17" t="n">
+        <v>14.699</v>
+      </c>
+      <c r="E133" s="17" t="n">
+        <v>10.885</v>
+      </c>
+      <c r="F133" s="17" t="n">
+        <v>18.2685</v>
+      </c>
+      <c r="G133" s="17" t="n">
+        <v>17.7735</v>
+      </c>
+      <c r="H133" s="17" t="n">
+        <v>14.6295</v>
+      </c>
+      <c r="I133" s="17" t="n">
+        <v>9.362</v>
+      </c>
+      <c r="J133" s="17" t="n">
+        <v>22.145</v>
+      </c>
+      <c r="K133" s="17" t="n">
+        <v>23.597</v>
+      </c>
+      <c r="L133" s="17" t="n">
+        <v>25.411</v>
+      </c>
+      <c r="M133" s="17" t="n">
+        <v>25.2495</v>
+      </c>
+      <c r="N133" s="8" t="n">
+        <f aca="false">COUNT(D133:M133)</f>
+        <v>10</v>
+      </c>
+      <c r="O133" s="18" t="n">
+        <f aca="false">IF(N133&gt;0,MEDIAN(D133:M133),"")</f>
+        <v>18.021</v>
+      </c>
+      <c r="P133" s="18" t="n">
+        <f aca="false">IF(N133&gt;=7,O133,"")</f>
+        <v>18.021</v>
+      </c>
+      <c r="Q133" s="8" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="0" t="s">
+        <v>674</v>
+      </c>
+      <c r="B134" s="0" t="s">
+        <v>675</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="D134" s="17" t="n">
+        <v>21.227</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>18.311</v>
+      </c>
+      <c r="F134" s="17" t="n">
+        <v>21.2065</v>
+      </c>
+      <c r="G134" s="17" t="n">
+        <v>26.9885</v>
+      </c>
+      <c r="H134" s="17" t="n">
+        <v>26.1895</v>
+      </c>
+      <c r="I134" s="17" t="n">
+        <v>17.8975</v>
+      </c>
+      <c r="J134" s="17" t="n">
+        <v>27.598</v>
+      </c>
+      <c r="K134" s="17" t="n">
+        <v>40.0635</v>
+      </c>
+      <c r="L134" s="17" t="n">
+        <v>33.295</v>
+      </c>
+      <c r="M134" s="17" t="n">
+        <v>37.754</v>
+      </c>
+      <c r="N134" s="8" t="n">
+        <f aca="false">COUNT(D134:M134)</f>
+        <v>10</v>
+      </c>
+      <c r="O134" s="18" t="n">
+        <f aca="false">IF(N134&gt;0,MEDIAN(D134:M134),"")</f>
+        <v>26.589</v>
+      </c>
+      <c r="P134" s="18" t="n">
+        <f aca="false">IF(N134&gt;=7,O134,"")</f>
+        <v>26.589</v>
+      </c>
+      <c r="Q134" s="8" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="B135" s="0" t="s">
+        <v>677</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="D135" s="17" t="n">
+        <v>11.158</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>11.6755</v>
+      </c>
+      <c r="F135" s="17" t="n">
+        <v>7.992</v>
+      </c>
+      <c r="G135" s="17" t="n">
+        <v>7.992</v>
+      </c>
+      <c r="H135" s="17" t="n">
+        <v>16.4005</v>
+      </c>
+      <c r="I135" s="17" t="n">
+        <v>12.6425</v>
+      </c>
+      <c r="J135" s="17" t="n">
+        <v>20.3175</v>
+      </c>
+      <c r="K135" s="17" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="L135" s="17" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="M135" s="17" t="n">
+        <v>53.1365</v>
+      </c>
+      <c r="N135" s="8" t="n">
+        <f aca="false">COUNT(D135:M135)</f>
+        <v>10</v>
+      </c>
+      <c r="O135" s="18" t="n">
+        <f aca="false">IF(N135&gt;0,MEDIAN(D135:M135),"")</f>
+        <v>14.5215</v>
+      </c>
+      <c r="P135" s="18" t="n">
+        <f aca="false">IF(N135&gt;=7,O135,"")</f>
+        <v>14.5215</v>
+      </c>
+      <c r="Q135" s="8" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="B137" s="18" t="n">
+        <f aca="false">P130</f>
+        <v>24.736</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="B138" s="35" t="n">
+        <f aca="false">COUNT(P131:P135)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="B139" s="18" t="n">
+        <f aca="false">IF(B138&gt;0,MEDIAN(P131:P135),"")</f>
+        <v>18.8945</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="B140" s="18" t="n">
+        <f aca="false">IF(AND(ISNUMBER(B137),B138&gt;=2),B137/B139,"")</f>
+        <v>1.30916404244621</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="B141" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="B142" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="B143" s="30" t="n">
+        <f aca="false">IF(ISNUMBER(B140),MIN(MAX(B140,B141),B142),1)</f>
+        <v>1.30916404244621</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B144" s="33" t="n">
+        <f aca="false">Val!$B$108*B143</f>
+        <v>222.178187448096</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>748</v>
       </c>
     </row>
   </sheetData>
@@ -46531,7 +48025,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>708</v>
+        <v>749</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46539,28 +48033,28 @@
         <v>20</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>709</v>
+        <v>750</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>710</v>
+        <v>751</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>711</v>
+        <v>752</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>712</v>
+        <v>753</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>713</v>
+        <v>754</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>714</v>
+        <v>755</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>715</v>
+        <v>756</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>716</v>
+        <v>757</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>464</v>
@@ -46568,7 +48062,7 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>717</v>
+        <v>758</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46607,12 +48101,12 @@
         <v>370</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>718</v>
+        <v>759</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>719</v>
+        <v>760</v>
       </c>
       <c r="B6" s="18" t="n">
         <f aca="false">cons_eps26</f>
@@ -46646,17 +48140,17 @@
         <v>370</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>721</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>722</v>
+        <v>763</v>
       </c>
       <c r="B8" s="19" t="n">
         <f aca="false">cons_rev27</f>
@@ -46687,12 +48181,12 @@
         <v>-0.293104849525013</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>723</v>
+        <v>764</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>724</v>
+        <v>765</v>
       </c>
       <c r="B9" s="18" t="n">
         <f aca="false">cons_eps27</f>
@@ -46723,12 +48217,12 @@
         <v>-0.40142708552717</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>723</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>725</v>
+        <v>766</v>
       </c>
       <c r="B10" s="19" t="n">
         <f aca="false">cons_rev28</f>
@@ -46759,12 +48253,12 @@
         <v>-0.476074330235896</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>723</v>
+        <v>764</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>726</v>
+        <v>767</v>
       </c>
       <c r="B11" s="18" t="n">
         <f aca="false">cons_eps28</f>
@@ -46795,17 +48289,17 @@
         <v>-0.616081455163665</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>723</v>
+        <v>764</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>727</v>
+        <v>768</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>728</v>
+        <v>769</v>
       </c>
       <c r="B13" s="19" t="n">
         <f aca="false">lt_lo</f>
@@ -46836,7 +48330,7 @@
         <v>-0.484172210662433</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>729</v>
+        <v>770</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>240</v>
@@ -46844,7 +48338,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>730</v>
+        <v>771</v>
       </c>
       <c r="B14" s="19" t="n">
         <f aca="false">lt_hi</f>
@@ -46880,7 +48374,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>731</v>
+        <v>772</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">hb_cum26q3-hb_cum25</f>
@@ -46911,10 +48405,10 @@
         <v>0.540923076923077</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>732</v>
+        <v>773</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>733</v>
+        <v>774</v>
       </c>
     </row>
   </sheetData>
@@ -46942,41 +48436,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>734</v>
+        <v>775</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>735</v>
+        <v>776</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>736</v>
+        <v>777</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>737</v>
+        <v>778</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>738</v>
+        <v>779</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>739</v>
+        <v>780</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>740</v>
+        <v>781</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>741</v>
+        <v>782</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>739</v>
+        <v>780</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>742</v>
+        <v>783</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>743</v>
+        <v>784</v>
       </c>
       <c r="C4" s="19" t="n">
         <f aca="false">PL!E63</f>
@@ -47005,10 +48499,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>744</v>
+        <v>785</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>745</v>
+        <v>786</v>
       </c>
       <c r="C5" s="19" t="n">
         <f aca="false">E83</f>
@@ -47037,10 +48531,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>746</v>
+        <v>787</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>747</v>
+        <v>788</v>
       </c>
       <c r="C6" s="19" t="n">
         <f aca="false">E128</f>
@@ -47069,10 +48563,10 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>748</v>
+        <v>789</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>749</v>
+        <v>790</v>
       </c>
       <c r="C7" s="19" t="n">
         <f aca="false">E173</f>
@@ -47101,7 +48595,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>750</v>
+        <v>791</v>
       </c>
       <c r="C8" s="19" t="n">
         <f aca="false">E218</f>
@@ -47130,7 +48624,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>751</v>
+        <v>792</v>
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">E263</f>
@@ -47159,10 +48653,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>752</v>
+        <v>793</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>753</v>
+        <v>794</v>
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">E308</f>
@@ -47191,10 +48685,10 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>754</v>
+        <v>795</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>755</v>
+        <v>796</v>
       </c>
       <c r="C11" s="19" t="n">
         <f aca="false">E353</f>
@@ -47223,10 +48717,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>756</v>
+        <v>797</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>757</v>
+        <v>798</v>
       </c>
       <c r="C12" s="19" t="n">
         <f aca="false">E398</f>
@@ -47255,7 +48749,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>758</v>
+        <v>799</v>
       </c>
       <c r="C13" s="19" t="n">
         <f aca="false">E443</f>
@@ -47284,7 +48778,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>759</v>
+        <v>800</v>
       </c>
       <c r="C14" s="19" t="n">
         <f aca="false">E488</f>
@@ -47313,7 +48807,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>760</v>
+        <v>801</v>
       </c>
       <c r="C15" s="19" t="n">
         <f aca="false">E533</f>
@@ -47342,10 +48836,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>761</v>
+        <v>802</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>762</v>
+        <v>803</v>
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">E578</f>
@@ -47374,10 +48868,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>763</v>
+        <v>804</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>764</v>
+        <v>805</v>
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">E623</f>
@@ -47406,7 +48900,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>765</v>
+        <v>806</v>
       </c>
       <c r="C18" s="19" t="n">
         <f aca="false">E668</f>
@@ -47435,10 +48929,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>766</v>
+        <v>807</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>767</v>
+        <v>808</v>
       </c>
       <c r="C19" s="19" t="n">
         <f aca="false">E713</f>
@@ -47467,10 +48961,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>768</v>
+        <v>809</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>769</v>
+        <v>810</v>
       </c>
       <c r="C20" s="19" t="n">
         <f aca="false">E758</f>
@@ -47499,7 +48993,7 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>770</v>
+        <v>811</v>
       </c>
       <c r="C21" s="19" t="n">
         <f aca="false">E803</f>
@@ -47528,7 +49022,7 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>771</v>
+        <v>812</v>
       </c>
       <c r="C22" s="19" t="n">
         <f aca="false">E848</f>
@@ -47557,7 +49051,7 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>772</v>
+        <v>813</v>
       </c>
       <c r="C23" s="19" t="n">
         <f aca="false">E893</f>
@@ -47586,7 +49080,7 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>773</v>
+        <v>814</v>
       </c>
       <c r="C24" s="19" t="n">
         <f aca="false">E938</f>
@@ -47615,7 +49109,7 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>774</v>
+        <v>815</v>
       </c>
       <c r="C25" s="19" t="n">
         <f aca="false">E983</f>
@@ -47644,7 +49138,7 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>775</v>
+        <v>816</v>
       </c>
       <c r="C26" s="19" t="n">
         <f aca="false">E1028</f>
@@ -47673,7 +49167,7 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>776</v>
+        <v>817</v>
       </c>
       <c r="C27" s="19" t="n">
         <f aca="false">E1073</f>
@@ -47702,7 +49196,7 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>777</v>
+        <v>818</v>
       </c>
       <c r="C28" s="19" t="n">
         <f aca="false">E1118</f>
@@ -47731,10 +49225,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>778</v>
+        <v>819</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>779</v>
+        <v>820</v>
       </c>
       <c r="C29" s="19" t="n">
         <f aca="false">E1163</f>
@@ -47763,7 +49257,7 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>780</v>
+        <v>821</v>
       </c>
       <c r="C30" s="19" t="n">
         <f aca="false">E1208</f>
@@ -47792,7 +49286,7 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>781</v>
+        <v>822</v>
       </c>
       <c r="C31" s="19" t="n">
         <f aca="false">E1253</f>
@@ -47821,10 +49315,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>782</v>
+        <v>823</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>783</v>
+        <v>824</v>
       </c>
       <c r="C32" s="19" t="n">
         <f aca="false">PL!E98</f>
@@ -47853,10 +49347,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>784</v>
+        <v>825</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>785</v>
+        <v>826</v>
       </c>
       <c r="C33" s="19" t="n">
         <f aca="false">PL!E133</f>
@@ -47885,12 +49379,12 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>786</v>
+        <v>827</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>787</v>
+        <v>828</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48765,7 +50259,7 @@
     </row>
     <row r="105" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="4" t="s">
-        <v>788</v>
+        <v>829</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49640,7 +51134,7 @@
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="4" t="s">
-        <v>789</v>
+        <v>830</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50518,7 +52012,7 @@
     </row>
     <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="4" t="s">
-        <v>790</v>
+        <v>831</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51396,7 +52890,7 @@
     </row>
     <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="4" t="s">
-        <v>791</v>
+        <v>832</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52274,7 +53768,7 @@
     </row>
     <row r="285" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="4" t="s">
-        <v>792</v>
+        <v>833</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53152,7 +54646,7 @@
     </row>
     <row r="330" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="4" t="s">
-        <v>793</v>
+        <v>834</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54030,7 +55524,7 @@
     </row>
     <row r="375" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="4" t="s">
-        <v>794</v>
+        <v>835</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54908,7 +56402,7 @@
     </row>
     <row r="420" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="4" t="s">
-        <v>795</v>
+        <v>836</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55786,7 +57280,7 @@
     </row>
     <row r="465" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="4" t="s">
-        <v>796</v>
+        <v>837</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56664,7 +58158,7 @@
     </row>
     <row r="510" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="4" t="s">
-        <v>797</v>
+        <v>838</v>
       </c>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57542,7 +59036,7 @@
     </row>
     <row r="555" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="4" t="s">
-        <v>798</v>
+        <v>839</v>
       </c>
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58420,7 +59914,7 @@
     </row>
     <row r="600" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A600" s="4" t="s">
-        <v>799</v>
+        <v>840</v>
       </c>
     </row>
     <row r="601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59298,7 +60792,7 @@
     </row>
     <row r="645" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A645" s="4" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
     </row>
     <row r="646" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60176,7 +61670,7 @@
     </row>
     <row r="690" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A690" s="4" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
     </row>
     <row r="691" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61054,7 +62548,7 @@
     </row>
     <row r="735" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A735" s="4" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
     </row>
     <row r="736" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61932,7 +63426,7 @@
     </row>
     <row r="780" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A780" s="4" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
     </row>
     <row r="781" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62810,7 +64304,7 @@
     </row>
     <row r="825" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A825" s="4" t="s">
-        <v>804</v>
+        <v>845</v>
       </c>
     </row>
     <row r="826" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63688,7 +65182,7 @@
     </row>
     <row r="870" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A870" s="4" t="s">
-        <v>805</v>
+        <v>846</v>
       </c>
     </row>
     <row r="871" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64566,7 +66060,7 @@
     </row>
     <row r="915" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A915" s="4" t="s">
-        <v>806</v>
+        <v>847</v>
       </c>
     </row>
     <row r="916" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65444,7 +66938,7 @@
     </row>
     <row r="960" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A960" s="4" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
     </row>
     <row r="961" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66322,7 +67816,7 @@
     </row>
     <row r="1005" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1005" s="4" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
     </row>
     <row r="1006" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67200,7 +68694,7 @@
     </row>
     <row r="1050" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1050" s="4" t="s">
-        <v>809</v>
+        <v>850</v>
       </c>
     </row>
     <row r="1051" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68078,7 +69572,7 @@
     </row>
     <row r="1095" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1095" s="4" t="s">
-        <v>810</v>
+        <v>851</v>
       </c>
     </row>
     <row r="1096" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68956,7 +70450,7 @@
     </row>
     <row r="1140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1140" s="4" t="s">
-        <v>811</v>
+        <v>852</v>
       </c>
     </row>
     <row r="1141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69834,7 +71328,7 @@
     </row>
     <row r="1185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1185" s="4" t="s">
-        <v>812</v>
+        <v>853</v>
       </c>
     </row>
     <row r="1186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70712,7 +72206,7 @@
     </row>
     <row r="1230" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1230" s="4" t="s">
-        <v>813</v>
+        <v>854</v>
       </c>
     </row>
     <row r="1231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71590,27 +73084,27 @@
     </row>
     <row r="1265" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1265" s="4" t="s">
-        <v>814</v>
+        <v>855</v>
       </c>
     </row>
     <row r="1266" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1266" s="6" t="s">
-        <v>735</v>
+        <v>776</v>
       </c>
       <c r="B1266" s="6" t="s">
-        <v>736</v>
+        <v>777</v>
       </c>
       <c r="C1266" s="14" t="s">
-        <v>815</v>
+        <v>856</v>
       </c>
       <c r="D1266" s="14" t="s">
-        <v>816</v>
+        <v>747</v>
       </c>
       <c r="E1266" s="6" t="s">
-        <v>817</v>
+        <v>857</v>
       </c>
       <c r="F1266" s="6" t="s">
-        <v>739</v>
+        <v>780</v>
       </c>
     </row>
     <row r="1267" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71618,19 +73112,19 @@
         <v>23</v>
       </c>
       <c r="B1267" s="0" t="s">
-        <v>818</v>
+        <v>858</v>
       </c>
       <c r="C1267" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>97.6798684202028</v>
       </c>
       <c r="D1267" s="13" t="n">
-        <f aca="false">Val!B108</f>
-        <v>169.709967769164</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>222.178187448096</v>
       </c>
       <c r="E1267" s="13" t="n">
         <f aca="false">tp_w_dcf*C1267+(1-tp_w_dcf)*D1267</f>
-        <v>133.694918094684</v>
+        <v>159.929027934149</v>
       </c>
       <c r="F1267" s="10" t="n">
         <f aca="false">E1267/E$1267-1</f>
@@ -71639,146 +73133,146 @@
     </row>
     <row r="1268" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1268" s="5" t="s">
-        <v>819</v>
+        <v>859</v>
       </c>
       <c r="B1268" s="0" t="s">
-        <v>820</v>
+        <v>860</v>
       </c>
       <c r="C1268" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!B82*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!B83*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!B84*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B85*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B86*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*MAX(0,Val!C81*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!C82*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!C83*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!C84*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C85*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C86*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*MAX(0,Val!D81*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!D82*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!D83*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!D84*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D85*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D86*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
         <v>84.5300035208355</v>
       </c>
       <c r="D1268" s="13" t="n">
-        <f aca="false">Val!B108</f>
-        <v>169.709967769164</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>222.178187448096</v>
       </c>
       <c r="E1268" s="13" t="n">
         <f aca="false">tp_w_dcf*C1268+(1-tp_w_dcf)*D1268</f>
-        <v>127.119985645</v>
+        <v>153.354095484466</v>
       </c>
       <c r="F1268" s="10" t="n">
         <f aca="false">E1268/E$1267-1</f>
-        <v>-0.0491786265580213</v>
+        <v>-0.0411115638893955</v>
       </c>
     </row>
     <row r="1269" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1269" s="5" t="s">
-        <v>821</v>
+        <v>861</v>
       </c>
       <c r="B1269" s="0" t="s">
-        <v>822</v>
+        <v>862</v>
       </c>
       <c r="C1269" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!B82*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!B83*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!B84*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B85*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B86*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*MAX(0,Val!C81*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!C82*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!C83*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!C84*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C85*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C86*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*MAX(0,Val!D81*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!D82*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!D83*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!D84*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D85*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D86*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
         <v>116.08316484556</v>
       </c>
       <c r="D1269" s="13" t="n">
-        <f aca="false">Val!B108</f>
-        <v>169.709967769164</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>222.178187448096</v>
       </c>
       <c r="E1269" s="13" t="n">
         <f aca="false">tp_w_dcf*C1269+(1-tp_w_dcf)*D1269</f>
-        <v>142.896566307362</v>
+        <v>169.130676146828</v>
       </c>
       <c r="F1269" s="10" t="n">
         <f aca="false">E1269/E$1267-1</f>
-        <v>0.0688257141244664</v>
+        <v>0.0575358228055221</v>
       </c>
     </row>
     <row r="1270" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1270" s="5" t="s">
-        <v>823</v>
+        <v>863</v>
       </c>
       <c r="B1270" s="0" t="s">
-        <v>824</v>
+        <v>864</v>
       </c>
       <c r="C1270" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B82*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B83*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B84*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B85*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B86*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B86*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*MAX(0,Val!C81*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C82*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C83*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C84*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C85*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C86*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C86*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*MAX(0,Val!D81*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D82*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D83*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D84*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D85*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D86*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D86*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
         <v>108.618992598606</v>
       </c>
       <c r="D1270" s="13" t="n">
-        <f aca="false">Val!B108</f>
-        <v>169.709967769164</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>222.178187448096</v>
       </c>
       <c r="E1270" s="13" t="n">
         <f aca="false">tp_w_dcf*C1270+(1-tp_w_dcf)*D1270</f>
-        <v>139.164480183885</v>
+        <v>165.398590023351</v>
       </c>
       <c r="F1270" s="10" t="n">
         <f aca="false">E1270/E$1267-1</f>
-        <v>0.0409107703355471</v>
+        <v>0.0341999333070009</v>
       </c>
     </row>
     <row r="1271" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1271" s="5" t="s">
-        <v>825</v>
+        <v>865</v>
       </c>
       <c r="B1271" s="0" t="s">
-        <v>826</v>
+        <v>866</v>
       </c>
       <c r="C1271" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B82*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B83*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B84*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B85*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B86*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B86*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*MAX(0,Val!C81*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C82*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C83*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C84*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C85*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C86*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C86*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*MAX(0,Val!D81*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D82*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D83*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D84*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D85*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D86*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D86*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
         <v>90.0972926493276</v>
       </c>
       <c r="D1271" s="13" t="n">
-        <f aca="false">Val!B108</f>
-        <v>169.709967769164</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>222.178187448096</v>
       </c>
       <c r="E1271" s="13" t="n">
         <f aca="false">tp_w_dcf*C1271+(1-tp_w_dcf)*D1271</f>
-        <v>129.903630209246</v>
+        <v>156.137740048712</v>
       </c>
       <c r="F1271" s="10" t="n">
         <f aca="false">E1271/E$1267-1</f>
-        <v>-0.0283577561471154</v>
+        <v>-0.023706064711396</v>
       </c>
     </row>
     <row r="1272" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1272" s="0" t="s">
-        <v>827</v>
+        <v>867</v>
       </c>
       <c r="B1272" s="0" t="s">
-        <v>828</v>
+        <v>868</v>
       </c>
       <c r="C1272" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>97.6798684202028</v>
       </c>
       <c r="D1272" s="13" t="n">
-        <f aca="false">Val!B108</f>
-        <v>169.709967769164</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>222.178187448096</v>
       </c>
       <c r="E1272" s="13" t="n">
         <f aca="false">0.3*C1272+(1-0.3)*D1272</f>
-        <v>148.100937964476</v>
+        <v>184.828691739728</v>
       </c>
       <c r="F1272" s="10" t="n">
         <f aca="false">E1272/E$1267-1</f>
-        <v>0.107752935377767</v>
+        <v>0.155691959910061</v>
       </c>
     </row>
     <row r="1273" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1273" s="0" t="s">
-        <v>829</v>
+        <v>869</v>
       </c>
       <c r="B1273" s="0" t="s">
-        <v>830</v>
+        <v>870</v>
       </c>
       <c r="C1273" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>97.6798684202028</v>
       </c>
       <c r="D1273" s="13" t="n">
-        <f aca="false">Val!B108</f>
-        <v>169.709967769164</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>222.178187448096</v>
       </c>
       <c r="E1273" s="13" t="n">
         <f aca="false">0.7*C1273+(1-0.7)*D1273</f>
-        <v>119.288898224891</v>
+        <v>135.029364128571</v>
       </c>
       <c r="F1273" s="10" t="n">
         <f aca="false">E1273/E$1267-1</f>
-        <v>-0.107752935377767</v>
+        <v>-0.155691959910061</v>
       </c>
     </row>
   </sheetData>
@@ -71806,140 +73300,140 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>831</v>
+        <v>871</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>832</v>
+        <v>872</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>833</v>
+        <v>873</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>834</v>
+        <v>874</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>835</v>
+        <v>875</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>836</v>
+        <v>876</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>837</v>
+        <v>877</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>838</v>
+        <v>878</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>839</v>
+        <v>879</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>840</v>
+        <v>880</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>841</v>
+        <v>881</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>842</v>
+        <v>882</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>843</v>
+        <v>883</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>844</v>
+        <v>884</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>845</v>
+        <v>885</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>846</v>
+        <v>886</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>847</v>
+        <v>887</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>848</v>
+        <v>888</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>849</v>
+        <v>889</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>850</v>
+        <v>890</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>851</v>
+        <v>891</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>852</v>
+        <v>892</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>853</v>
+        <v>893</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>854</v>
+        <v>894</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>855</v>
+        <v>895</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>856</v>
+        <v>896</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>857</v>
+        <v>897</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>858</v>
+        <v>898</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>859</v>
+        <v>899</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>861</v>
+        <v>901</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>862</v>
+        <v>902</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>863</v>
+        <v>903</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>864</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>

--- a/besi/dist/20261025_BESI模型_v0.1.1.xlsx
+++ b/besi/dist/20261025_BESI模型_v0.1.1.xlsx
@@ -4553,7 +4553,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -4572,7 +4572,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5146,7 +5146,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -5165,7 +5165,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5601,7 +5601,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -5620,7 +5620,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8293,7 +8293,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8312,7 +8312,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8649,7 +8649,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8668,7 +8668,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8819,7 +8819,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8838,7 +8838,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8940,7 +8940,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8959,7 +8959,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9061,7 +9061,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9080,7 +9080,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9182,7 +9182,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9201,7 +9201,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9303,7 +9303,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9322,7 +9322,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/besi/dist/20261025_BESI模型_v0.1.1.xlsx
+++ b/besi/dist/20261025_BESI模型_v0.1.1.xlsx
@@ -36804,7 +36804,7 @@
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="str">
         <f aca="false">"重點觀察 1：目標價 €"&amp;TEXT(Val!$B$112,"#,##0.00")&amp;"（DCF "&amp;TEXT(Val!$B$97,"#,##0.00")&amp;"、Comparable（相對倍數調整後）"&amp;TEXT(tp_comp_adj,"#,##0.00")&amp;"；DCF 權重 "&amp;TEXT(tp_w_dcf,"0%")&amp;"），比現價 "&amp;TEXT(px,"#,##0.00")&amp;"（2026-10-23）"&amp;IF(Val!$B$115&gt;=0,"高 "&amp;TEXT(Val!$B$115,"0.0%"),"低 "&amp;TEXT(-Val!$B$115,"0.0%"))&amp;"，級距 "&amp;Val!$B$123&amp;"、投資建議 "&amp;Val!$B$124&amp;"。相對倍數調整係數 "&amp;TEXT(rm_factor,"0.00")&amp;"（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 "&amp;TEXT((tp_w_dcf*Val!$B$97+(1-tp_w_dcf)*Val!$B$108)/px-1,"+0.0%;−0.0%")&amp;"；Comparable 單獨（市場主流同業法、未調整）為 "&amp;TEXT(Val!$B$116,"+0.0%;−0.0%")&amp;"。"&amp;"以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：DCF 低是情境分歧造成：DCF 情境價值 A 158.4（現價的 1.09 倍）、B 82.4、C 44.8，B 的 FY2028 EPS 6.59 比 A 的 9.37 低 30%。"</f>
-        <v>重點觀察 1：目標價 €159.93（DCF 97.68、Comparable（相對倍數調整後）222.18；DCF 權重 50%），比現價 145.10（2026-10-23）高 10.2%，級距 0%–25%、投資建議 中立。相對倍數調整係數 1.31（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 −7.9%；Comparable 單獨（市場主流同業法、未調整）為 +17.0%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：DCF 低是情境分歧造成：DCF 情境價值 A 158.4（現價的 1.09 倍）、B 82.4、C 44.8，B 的 FY2028 EPS 6.59 比 A 的 9.37 低 30%。</v>
+        <v>重點觀察 1：目標價 €157.28（DCF 96.23、Comparable（相對倍數調整後）218.34；DCF 權重 50%），比現價 145.10（2026-10-23）高 8.4%，級距 0%–25%、投資建議 中立。相對倍數調整係數 1.31（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 −9.4%；Comparable 單獨（市場主流同業法、未調整）為 +14.9%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：DCF 低是情境分歧造成：DCF 情境價值 A 158.4（現價的 1.09 倍）、B 82.4、C 44.8，B 的 FY2028 EPS 6.59 比 A 的 9.37 低 30%。</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39176,7 +39176,7 @@
         <v>68</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>0.224905413856655</v>
+        <v>0.198744917723333</v>
       </c>
       <c r="G94" s="8" t="s">
         <v>32</v>
@@ -39245,7 +39245,7 @@
         <v>68</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>0.224905413856655</v>
+        <v>0.198744917723333</v>
       </c>
       <c r="G97" s="8" t="s">
         <v>32</v>
@@ -39314,7 +39314,7 @@
         <v>68</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>0.224905413856655</v>
+        <v>0.198744917723333</v>
       </c>
       <c r="G100" s="8" t="s">
         <v>32</v>
@@ -41622,15 +41622,15 @@
       </c>
       <c r="E5" s="16" t="n">
         <f aca="false">E63</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="F5" s="16" t="n">
         <f aca="false">F63</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G5" s="16" t="n">
         <f aca="false">G63</f>
-        <v>1927.10446122904</v>
+        <v>1903.63175356863</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>487</v>
@@ -41681,15 +41681,15 @@
       </c>
       <c r="E7" s="16" t="n">
         <f aca="false">E62</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F7" s="16" t="n">
         <f aca="false">F62</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G7" s="16" t="n">
         <f aca="false">G62</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41709,15 +41709,15 @@
       </c>
       <c r="E8" s="10" t="n">
         <f aca="false">E65</f>
-        <v>0.655359989722361</v>
+        <v>0.655758613662263</v>
       </c>
       <c r="F8" s="10" t="n">
         <f aca="false">F65</f>
-        <v>0.660478793792801</v>
+        <v>0.660901001490768</v>
       </c>
       <c r="G8" s="10" t="n">
         <f aca="false">G65</f>
-        <v>0.661016203541849</v>
+        <v>0.66144006195241</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41737,15 +41737,15 @@
       </c>
       <c r="E9" s="16" t="n">
         <f aca="false">E68</f>
-        <v>678.944025029319</v>
+        <v>668.380593274033</v>
       </c>
       <c r="F9" s="16" t="n">
         <f aca="false">F68</f>
-        <v>893.318855963851</v>
+        <v>881.40958698298</v>
       </c>
       <c r="G9" s="16" t="n">
         <f aca="false">G68</f>
-        <v>968.242680463026</v>
+        <v>955.625373604005</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41765,15 +41765,15 @@
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">E69</f>
-        <v>0.472983062059672</v>
+        <v>0.472087115901772</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">F69</f>
-        <v>0.496899295135026</v>
+        <v>0.496392312106413</v>
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">G69</f>
-        <v>0.502433936479767</v>
+        <v>0.502001173185176</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41793,15 +41793,15 @@
       </c>
       <c r="E11" s="16" t="n">
         <f aca="false">E70</f>
-        <v>569.986581650361</v>
+        <v>560.849213182038</v>
       </c>
       <c r="F11" s="16" t="n">
         <f aca="false">F70</f>
-        <v>755.420810408731</v>
+        <v>745.119292740278</v>
       </c>
       <c r="G11" s="16" t="n">
         <f aca="false">G70</f>
-        <v>820.229918600517</v>
+        <v>809.315948167465</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41821,15 +41821,15 @@
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">E71</f>
-        <v>7.07166188055019</v>
+        <v>6.95829714115775</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">F71</f>
-        <v>9.37229177092922</v>
+        <v>9.24448376254262</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">G71</f>
-        <v>10.1763599975624</v>
+        <v>10.040953461406</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41854,15 +41854,15 @@
       </c>
       <c r="E15" s="16" t="n">
         <f aca="false">E98</f>
-        <v>1115.01704209625</v>
+        <v>1095.3652774009</v>
       </c>
       <c r="F15" s="16" t="n">
         <f aca="false">F98</f>
-        <v>1362.23504530487</v>
+        <v>1342.58328060951</v>
       </c>
       <c r="G15" s="16" t="n">
         <f aca="false">G98</f>
-        <v>1347.1557164714</v>
+        <v>1328.48654001082</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41910,15 +41910,15 @@
       </c>
       <c r="E17" s="16" t="n">
         <f aca="false">E97</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F17" s="16" t="n">
         <f aca="false">F97</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="G17" s="16" t="n">
         <f aca="false">G97</f>
-        <v>874.141499544663</v>
+        <v>855.472323084079</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41938,15 +41938,15 @@
       </c>
       <c r="E18" s="10" t="n">
         <f aca="false">E100</f>
-        <v>0.640622727474559</v>
+        <v>0.640873564595441</v>
       </c>
       <c r="F18" s="10" t="n">
         <f aca="false">F100</f>
-        <v>0.652603771403679</v>
+        <v>0.652983790234515</v>
       </c>
       <c r="G18" s="10" t="n">
         <f aca="false">G100</f>
-        <v>0.654731027352329</v>
+        <v>0.655125770304595</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41966,15 +41966,15 @@
       </c>
       <c r="E19" s="16" t="n">
         <f aca="false">E103</f>
-        <v>481.066118055113</v>
+        <v>470.502686299827</v>
       </c>
       <c r="F19" s="16" t="n">
         <f aca="false">F103</f>
-        <v>633.730886552106</v>
+        <v>623.167454796819</v>
       </c>
       <c r="G19" s="16" t="n">
         <f aca="false">G103</f>
-        <v>628.099530072542</v>
+        <v>618.06426990502</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41994,15 +41994,15 @@
       </c>
       <c r="E20" s="10" t="n">
         <f aca="false">E104</f>
-        <v>0.43144283889213</v>
+        <v>0.429539529878327</v>
       </c>
       <c r="F20" s="10" t="n">
         <f aca="false">F104</f>
-        <v>0.465214052990597</v>
+        <v>0.464155530459093</v>
       </c>
       <c r="G20" s="10" t="n">
         <f aca="false">G104</f>
-        <v>0.466241223930461</v>
+        <v>0.46523939181197</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42022,15 +42022,15 @@
       </c>
       <c r="E21" s="16" t="n">
         <f aca="false">E105</f>
-        <v>398.822192117673</v>
+        <v>389.68482364935</v>
       </c>
       <c r="F21" s="16" t="n">
         <f aca="false">F105</f>
-        <v>530.877216867571</v>
+        <v>521.739848399248</v>
       </c>
       <c r="G21" s="16" t="n">
         <f aca="false">G105</f>
-        <v>526.006093512749</v>
+        <v>517.325593467842</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42050,15 +42050,15 @@
       </c>
       <c r="E22" s="18" t="n">
         <f aca="false">E106</f>
-        <v>4.94807383877337</v>
+        <v>4.83470909938093</v>
       </c>
       <c r="F22" s="18" t="n">
         <f aca="false">F106</f>
-        <v>6.5864430824055</v>
+        <v>6.47307834301306</v>
       </c>
       <c r="G22" s="18" t="n">
         <f aca="false">G106</f>
-        <v>6.52600843630556</v>
+        <v>6.41831193388275</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42083,15 +42083,15 @@
       </c>
       <c r="E25" s="16" t="n">
         <f aca="false">E133</f>
-        <v>950.773977388857</v>
+        <v>931.122212693506</v>
       </c>
       <c r="F25" s="16" t="n">
         <f aca="false">F133</f>
-        <v>863.953429441008</v>
+        <v>848.232017684726</v>
       </c>
       <c r="G25" s="16" t="n">
         <f aca="false">G133</f>
-        <v>876.907241873864</v>
+        <v>861.185830117582</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42139,15 +42139,15 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">E132</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">F132</f>
-        <v>736.119157511296</v>
+        <v>720.397745755014</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">G132</f>
-        <v>736.119157511296</v>
+        <v>720.397745755014</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42167,15 +42167,15 @@
       </c>
       <c r="E28" s="10" t="n">
         <f aca="false">E135</f>
-        <v>0.629218224344995</v>
+        <v>0.629272609966815</v>
       </c>
       <c r="F28" s="10" t="n">
         <f aca="false">F135</f>
-        <v>0.618478518497313</v>
+        <v>0.618697912038107</v>
       </c>
       <c r="G28" s="10" t="n">
         <f aca="false">G135</f>
-        <v>0.619485430973731</v>
+        <v>0.619719906164053</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42195,15 +42195,15 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">E138</f>
-        <v>379.640942196732</v>
+        <v>369.077510441446</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">F138</f>
-        <v>323.469881262775</v>
+        <v>315.333564093671</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">G138</f>
-        <v>331.210185118109</v>
+        <v>323.073867949005</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42223,15 +42223,15 @@
       </c>
       <c r="E30" s="10" t="n">
         <f aca="false">E139</f>
-        <v>0.39929673216273</v>
+        <v>0.396379235088588</v>
       </c>
       <c r="F30" s="10" t="n">
         <f aca="false">F139</f>
-        <v>0.374406617578988</v>
+        <v>0.371753904025438</v>
       </c>
       <c r="G30" s="10" t="n">
         <f aca="false">G139</f>
-        <v>0.377702645504838</v>
+        <v>0.375150004389754</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42251,15 +42251,15 @@
       </c>
       <c r="E31" s="16" t="n">
         <f aca="false">E140</f>
-        <v>311.089415000174</v>
+        <v>301.952046531851</v>
       </c>
       <c r="F31" s="16" t="n">
         <f aca="false">F140</f>
-        <v>262.5014472923</v>
+        <v>255.463532941025</v>
       </c>
       <c r="G31" s="16" t="n">
         <f aca="false">G140</f>
-        <v>269.196810127164</v>
+        <v>262.15889577589</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42279,15 +42279,15 @@
       </c>
       <c r="E32" s="18" t="n">
         <f aca="false">E141</f>
-        <v>3.85959815252081</v>
+        <v>3.74623341312837</v>
       </c>
       <c r="F32" s="18" t="n">
         <f aca="false">F141</f>
-        <v>3.25678101584663</v>
+        <v>3.16946360831683</v>
       </c>
       <c r="G32" s="18" t="n">
         <f aca="false">G141</f>
-        <v>3.33984848385381</v>
+        <v>3.252531076324</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42877,15 +42877,15 @@
       </c>
       <c r="E62" s="16" t="n">
         <f aca="false">D62*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F62" s="16" t="n">
         <f aca="false">E62*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G62" s="16" t="n">
         <f aca="false">F62*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I62" s="8" t="s">
         <v>526</v>
@@ -42908,15 +42908,15 @@
       </c>
       <c r="E63" s="16" t="n">
         <f aca="false">E61+E62</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="F63" s="16" t="n">
         <f aca="false">F61+F62</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G63" s="16" t="n">
         <f aca="false">G61+G62</f>
-        <v>1927.10446122904</v>
+        <v>1903.63175356863</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42936,15 +42936,15 @@
       </c>
       <c r="E64" s="10" t="n">
         <f aca="false">E61/E63</f>
-        <v>0.358982699005556</v>
+        <v>0.363965498254324</v>
       </c>
       <c r="F64" s="10" t="n">
         <f aca="false">F61/F63</f>
-        <v>0.422967749886054</v>
+        <v>0.428245346110634</v>
       </c>
       <c r="G64" s="10" t="n">
         <f aca="false">G61/G63</f>
-        <v>0.429685371749146</v>
+        <v>0.434983601881163</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42964,15 +42964,15 @@
       </c>
       <c r="E65" s="10" t="n">
         <f aca="false">$D65+gm_prem*(E64-$D64)+0</f>
-        <v>0.655359989722361</v>
+        <v>0.655758613662263</v>
       </c>
       <c r="F65" s="10" t="n">
         <f aca="false">$D65+gm_prem*(F64-$D64)+0</f>
-        <v>0.660478793792801</v>
+        <v>0.660901001490768</v>
       </c>
       <c r="G65" s="10" t="n">
         <f aca="false">$D65+gm_prem*(G64-$D64)+0</f>
-        <v>0.661016203541849</v>
+        <v>0.66144006195241</v>
       </c>
       <c r="I65" s="8" t="s">
         <v>528</v>
@@ -42995,15 +42995,15 @@
       </c>
       <c r="E66" s="16" t="n">
         <f aca="false">E63*E65</f>
-        <v>940.737174239736</v>
+        <v>928.422565413409</v>
       </c>
       <c r="F66" s="16" t="n">
         <f aca="false">F63*F65</f>
-        <v>1187.39987405102</v>
+        <v>1173.51631875342</v>
       </c>
       <c r="G66" s="16" t="n">
         <f aca="false">G63*G65</f>
-        <v>1273.84727479018</v>
+        <v>1259.13830501501</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43023,15 +43023,15 @@
       </c>
       <c r="E67" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E63</f>
-        <v>261.793149210416</v>
+        <v>260.041972139376</v>
       </c>
       <c r="F67" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F63</f>
-        <v>294.081018087167</v>
+        <v>292.106731770439</v>
       </c>
       <c r="G67" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G63</f>
-        <v>305.604594327152</v>
+        <v>303.512931411003</v>
       </c>
       <c r="I67" s="5" t="s">
         <v>530</v>
@@ -43054,15 +43054,15 @@
       </c>
       <c r="E68" s="16" t="n">
         <f aca="false">E66-E67</f>
-        <v>678.944025029319</v>
+        <v>668.380593274033</v>
       </c>
       <c r="F68" s="16" t="n">
         <f aca="false">F66-F67</f>
-        <v>893.318855963851</v>
+        <v>881.40958698298</v>
       </c>
       <c r="G68" s="16" t="n">
         <f aca="false">G66-G67</f>
-        <v>968.242680463026</v>
+        <v>955.625373604005</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43082,15 +43082,15 @@
       </c>
       <c r="E69" s="10" t="n">
         <f aca="false">E68/E63</f>
-        <v>0.472983062059672</v>
+        <v>0.472087115901772</v>
       </c>
       <c r="F69" s="10" t="n">
         <f aca="false">F68/F63</f>
-        <v>0.496899295135026</v>
+        <v>0.496392312106413</v>
       </c>
       <c r="G69" s="10" t="n">
         <f aca="false">G68/G63</f>
-        <v>0.502433936479767</v>
+        <v>0.502001173185176</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43110,15 +43110,15 @@
       </c>
       <c r="E70" s="16" t="n">
         <f aca="false">(E68-fin)*(1-tax)</f>
-        <v>569.986581650361</v>
+        <v>560.849213182038</v>
       </c>
       <c r="F70" s="16" t="n">
         <f aca="false">(F68-fin)*(1-tax)</f>
-        <v>755.420810408731</v>
+        <v>745.119292740278</v>
       </c>
       <c r="G70" s="16" t="n">
         <f aca="false">(G68-fin)*(1-tax)</f>
-        <v>820.229918600517</v>
+        <v>809.315948167465</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43138,15 +43138,15 @@
       </c>
       <c r="E71" s="18" t="n">
         <f aca="false">E70/shares</f>
-        <v>7.07166188055019</v>
+        <v>6.95829714115775</v>
       </c>
       <c r="F71" s="18" t="n">
         <f aca="false">F70/shares</f>
-        <v>9.37229177092922</v>
+        <v>9.24448376254262</v>
       </c>
       <c r="G71" s="18" t="n">
         <f aca="false">G70/shares</f>
-        <v>10.1763599975624</v>
+        <v>10.040953461406</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43755,15 +43755,15 @@
       </c>
       <c r="E97" s="16" t="n">
         <f aca="false">D97*(1+el*eqgB_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F97" s="16" t="n">
         <f aca="false">E97*(1+el*eqgB_28)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="G97" s="16" t="n">
         <f aca="false">F97*(1+el*eqgB_29)</f>
-        <v>874.141499544663</v>
+        <v>855.472323084079</v>
       </c>
       <c r="I97" s="8" t="s">
         <v>526</v>
@@ -43786,15 +43786,15 @@
       </c>
       <c r="E98" s="16" t="n">
         <f aca="false">E96+E97</f>
-        <v>1115.01704209625</v>
+        <v>1095.3652774009</v>
       </c>
       <c r="F98" s="16" t="n">
         <f aca="false">F96+F97</f>
-        <v>1362.23504530487</v>
+        <v>1342.58328060951</v>
       </c>
       <c r="G98" s="16" t="n">
         <f aca="false">G96+G97</f>
-        <v>1347.1557164714</v>
+        <v>1328.48654001082</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43814,15 +43814,15 @@
       </c>
       <c r="E99" s="10" t="n">
         <f aca="false">E96/E98</f>
-        <v>0.174766920908024</v>
+        <v>0.177902384919048</v>
       </c>
       <c r="F99" s="10" t="n">
         <f aca="false">F96/F98</f>
-        <v>0.32452997002203</v>
+        <v>0.329280205407478</v>
       </c>
       <c r="G99" s="10" t="n">
         <f aca="false">G96/G98</f>
-        <v>0.351120669380152</v>
+        <v>0.356054956283475</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43842,15 +43842,15 @@
       </c>
       <c r="E100" s="10" t="n">
         <f aca="false">$D100+gm_prem*(E99-$D99)+0</f>
-        <v>0.640622727474559</v>
+        <v>0.640873564595441</v>
       </c>
       <c r="F100" s="10" t="n">
         <f aca="false">$D100+gm_prem*(F99-$D99)+0</f>
-        <v>0.652603771403679</v>
+        <v>0.652983790234515</v>
       </c>
       <c r="G100" s="10" t="n">
         <f aca="false">$D100+gm_prem*(G99-$D99)+0</f>
-        <v>0.654731027352329</v>
+        <v>0.655125770304595</v>
       </c>
       <c r="I100" s="8" t="s">
         <v>528</v>
@@ -43873,15 +43873,15 @@
       </c>
       <c r="E101" s="16" t="n">
         <f aca="false">E98*E100</f>
-        <v>714.305258688317</v>
+        <v>701.99064986199</v>
       </c>
       <c r="F101" s="16" t="n">
         <f aca="false">F98*F100</f>
-        <v>888.999728104217</v>
+        <v>876.68511927789</v>
       </c>
       <c r="G101" s="16" t="n">
         <f aca="false">G98*G100</f>
-        <v>882.024646248882</v>
+        <v>870.325767863871</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43901,15 +43901,15 @@
       </c>
       <c r="E102" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E98</f>
-        <v>233.239140633204</v>
+        <v>231.487963562163</v>
       </c>
       <c r="F102" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F98</f>
-        <v>255.268841552112</v>
+        <v>253.517664481071</v>
       </c>
       <c r="G102" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G98</f>
-        <v>253.92511617634</v>
+        <v>252.261497958851</v>
       </c>
       <c r="I102" s="5" t="s">
         <v>530</v>
@@ -43932,15 +43932,15 @@
       </c>
       <c r="E103" s="16" t="n">
         <f aca="false">E101-E102</f>
-        <v>481.066118055113</v>
+        <v>470.502686299827</v>
       </c>
       <c r="F103" s="16" t="n">
         <f aca="false">F101-F102</f>
-        <v>633.730886552106</v>
+        <v>623.167454796819</v>
       </c>
       <c r="G103" s="16" t="n">
         <f aca="false">G101-G102</f>
-        <v>628.099530072542</v>
+        <v>618.06426990502</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43960,15 +43960,15 @@
       </c>
       <c r="E104" s="10" t="n">
         <f aca="false">E103/E98</f>
-        <v>0.43144283889213</v>
+        <v>0.429539529878327</v>
       </c>
       <c r="F104" s="10" t="n">
         <f aca="false">F103/F98</f>
-        <v>0.465214052990597</v>
+        <v>0.464155530459093</v>
       </c>
       <c r="G104" s="10" t="n">
         <f aca="false">G103/G98</f>
-        <v>0.466241223930461</v>
+        <v>0.46523939181197</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43988,15 +43988,15 @@
       </c>
       <c r="E105" s="16" t="n">
         <f aca="false">(E103-fin)*(1-tax)</f>
-        <v>398.822192117673</v>
+        <v>389.68482364935</v>
       </c>
       <c r="F105" s="16" t="n">
         <f aca="false">(F103-fin)*(1-tax)</f>
-        <v>530.877216867571</v>
+        <v>521.739848399248</v>
       </c>
       <c r="G105" s="16" t="n">
         <f aca="false">(G103-fin)*(1-tax)</f>
-        <v>526.006093512749</v>
+        <v>517.325593467842</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44016,15 +44016,15 @@
       </c>
       <c r="E106" s="18" t="n">
         <f aca="false">E105/shares</f>
-        <v>4.94807383877337</v>
+        <v>4.83470909938093</v>
       </c>
       <c r="F106" s="18" t="n">
         <f aca="false">F105/shares</f>
-        <v>6.5864430824055</v>
+        <v>6.47307834301306</v>
       </c>
       <c r="G106" s="18" t="n">
         <f aca="false">G105/shares</f>
-        <v>6.52600843630556</v>
+        <v>6.41831193388275</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44633,15 +44633,15 @@
       </c>
       <c r="E132" s="16" t="n">
         <f aca="false">D132*(1+el*eqgC_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F132" s="16" t="n">
         <f aca="false">E132*(1+el*eqgC_28)</f>
-        <v>736.119157511296</v>
+        <v>720.397745755014</v>
       </c>
       <c r="G132" s="16" t="n">
         <f aca="false">F132*(1+el*eqgC_29)</f>
-        <v>736.119157511296</v>
+        <v>720.397745755014</v>
       </c>
       <c r="I132" s="8" t="s">
         <v>526</v>
@@ -44664,15 +44664,15 @@
       </c>
       <c r="E133" s="16" t="n">
         <f aca="false">E131+E132</f>
-        <v>950.773977388857</v>
+        <v>931.122212693506</v>
       </c>
       <c r="F133" s="16" t="n">
         <f aca="false">F131+F132</f>
-        <v>863.953429441008</v>
+        <v>848.232017684726</v>
       </c>
       <c r="G133" s="16" t="n">
         <f aca="false">G131+G132</f>
-        <v>876.907241873864</v>
+        <v>861.185830117582</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44692,15 +44692,15 @@
       </c>
       <c r="E134" s="10" t="n">
         <f aca="false">E131/E133</f>
-        <v>0.0322106317884768</v>
+        <v>0.0328904520612256</v>
       </c>
       <c r="F134" s="10" t="n">
         <f aca="false">F131/F133</f>
-        <v>0.147964308692452</v>
+        <v>0.150706727952382</v>
       </c>
       <c r="G134" s="10" t="n">
         <f aca="false">G131/G133</f>
-        <v>0.160550714647673</v>
+        <v>0.163481654526696</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44720,15 +44720,15 @@
       </c>
       <c r="E135" s="10" t="n">
         <f aca="false">$D135+gm_prem*(E134-$D134)+0</f>
-        <v>0.629218224344995</v>
+        <v>0.629272609966815</v>
       </c>
       <c r="F135" s="10" t="n">
         <f aca="false">$D135+gm_prem*(F134-$D134)+gm_adj_C</f>
-        <v>0.618478518497313</v>
+        <v>0.618697912038107</v>
       </c>
       <c r="G135" s="10" t="n">
         <f aca="false">$D135+gm_prem*(G134-$D134)+gm_adj_C</f>
-        <v>0.619485430973731</v>
+        <v>0.619719906164053</v>
       </c>
       <c r="I135" s="8" t="s">
         <v>528</v>
@@ -44751,15 +44751,15 @@
       </c>
       <c r="E136" s="16" t="n">
         <f aca="false">E133*E135</f>
-        <v>598.244313806045</v>
+        <v>585.929704979718</v>
       </c>
       <c r="F136" s="16" t="n">
         <f aca="false">F133*F135</f>
-        <v>534.336637091347</v>
+        <v>524.799378265411</v>
       </c>
       <c r="G136" s="16" t="n">
         <f aca="false">G133*G135</f>
-        <v>543.231260656216</v>
+        <v>533.69400183028</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44779,15 +44779,15 @@
       </c>
       <c r="E137" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E133</f>
-        <v>218.603371609313</v>
+        <v>216.852194538272</v>
       </c>
       <c r="F137" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F133</f>
-        <v>210.866755828573</v>
+        <v>209.46581417174</v>
       </c>
       <c r="G137" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G133</f>
-        <v>212.021075538107</v>
+        <v>210.620133881275</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>530</v>
@@ -44810,15 +44810,15 @@
       </c>
       <c r="E138" s="16" t="n">
         <f aca="false">E136-E137</f>
-        <v>379.640942196732</v>
+        <v>369.077510441446</v>
       </c>
       <c r="F138" s="16" t="n">
         <f aca="false">F136-F137</f>
-        <v>323.469881262775</v>
+        <v>315.333564093671</v>
       </c>
       <c r="G138" s="16" t="n">
         <f aca="false">G136-G137</f>
-        <v>331.210185118109</v>
+        <v>323.073867949005</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44838,15 +44838,15 @@
       </c>
       <c r="E139" s="10" t="n">
         <f aca="false">E138/E133</f>
-        <v>0.39929673216273</v>
+        <v>0.396379235088588</v>
       </c>
       <c r="F139" s="10" t="n">
         <f aca="false">F138/F133</f>
-        <v>0.374406617578988</v>
+        <v>0.371753904025438</v>
       </c>
       <c r="G139" s="10" t="n">
         <f aca="false">G138/G133</f>
-        <v>0.377702645504838</v>
+        <v>0.375150004389754</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44866,15 +44866,15 @@
       </c>
       <c r="E140" s="16" t="n">
         <f aca="false">(E138-fin)*(1-tax)</f>
-        <v>311.089415000174</v>
+        <v>301.952046531851</v>
       </c>
       <c r="F140" s="16" t="n">
         <f aca="false">(F138-fin)*(1-tax)</f>
-        <v>262.5014472923</v>
+        <v>255.463532941025</v>
       </c>
       <c r="G140" s="16" t="n">
         <f aca="false">(G138-fin)*(1-tax)</f>
-        <v>269.196810127164</v>
+        <v>262.15889577589</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44894,15 +44894,15 @@
       </c>
       <c r="E141" s="18" t="n">
         <f aca="false">E140/shares</f>
-        <v>3.85959815252081</v>
+        <v>3.74623341312837</v>
       </c>
       <c r="F141" s="18" t="n">
         <f aca="false">F140/shares</f>
-        <v>3.25678101584663</v>
+        <v>3.16946360831683</v>
       </c>
       <c r="G141" s="18" t="n">
         <f aca="false">G140/shares</f>
-        <v>3.33984848385381</v>
+        <v>3.252531076324</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45000,27 +45000,27 @@
       </c>
       <c r="E149" s="16" t="n">
         <f aca="false">E5</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="F149" s="16" t="n">
         <f aca="false">F5</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G149" s="16" t="n">
         <f aca="false">G5</f>
-        <v>1927.10446122904</v>
+        <v>1903.63175356863</v>
       </c>
       <c r="H149" s="22" t="n">
         <f aca="false">G149*(1+H150)</f>
-        <v>2058.05988688366</v>
+        <v>2033.18971043688</v>
       </c>
       <c r="I149" s="22" t="n">
         <f aca="false">H149*(1+I150)</f>
-        <v>2189.72890174217</v>
+        <v>2163.37312787295</v>
       </c>
       <c r="J149" s="22" t="n">
         <f aca="false">I149*(1+J150)</f>
-        <v>2321.1126358467</v>
+        <v>2293.17551554533</v>
       </c>
       <c r="K149" s="8" t="s">
         <v>543</v>
@@ -45039,23 +45039,23 @@
       </c>
       <c r="E150" s="10" t="n">
         <f aca="false">E149/D149-1</f>
-        <v>0.433157980240622</v>
+        <v>0.41353760814063</v>
       </c>
       <c r="F150" s="10" t="n">
         <f aca="false">F149/E149-1</f>
-        <v>0.25241926155697</v>
+        <v>0.25415449687479</v>
       </c>
       <c r="G150" s="10" t="n">
         <f aca="false">G149/F149-1</f>
-        <v>0.0719317543153055</v>
+        <v>0.0720874625242345</v>
       </c>
       <c r="H150" s="23" t="n">
         <f aca="false">$G150+((tp_g+0.02)-$G150)*1/3</f>
-        <v>0.0679545028768703</v>
+        <v>0.0680583083494897</v>
       </c>
       <c r="I150" s="23" t="n">
         <f aca="false">$G150+((tp_g+0.02)-$G150)*2/3</f>
-        <v>0.0639772514384352</v>
+        <v>0.0640291541747448</v>
       </c>
       <c r="J150" s="23" t="n">
         <f aca="false">$G150+((tp_g+0.02)-$G150)*3/3</f>
@@ -45079,27 +45079,27 @@
       </c>
       <c r="E151" s="10" t="n">
         <f aca="false">E152/E149</f>
-        <v>0.397078387589126</v>
+        <v>0.396136108934468</v>
       </c>
       <c r="F151" s="10" t="n">
         <f aca="false">F152/F149</f>
-        <v>0.420194945753634</v>
+        <v>0.41963633477654</v>
       </c>
       <c r="G151" s="10" t="n">
         <f aca="false">G152/G149</f>
-        <v>0.425628156180701</v>
+        <v>0.425143122691816</v>
       </c>
       <c r="H151" s="23" t="n">
         <f aca="false">$G151+($G151-$G151)*1/3</f>
-        <v>0.425628156180701</v>
+        <v>0.425143122691816</v>
       </c>
       <c r="I151" s="23" t="n">
         <f aca="false">$G151+($G151-$G151)*2/3</f>
-        <v>0.425628156180701</v>
+        <v>0.425143122691816</v>
       </c>
       <c r="J151" s="23" t="n">
         <f aca="false">$G151+($G151-$G151)*3/3</f>
-        <v>0.425628156180701</v>
+        <v>0.425143122691816</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45119,27 +45119,27 @@
       </c>
       <c r="E152" s="16" t="n">
         <f aca="false">E11</f>
-        <v>569.986581650361</v>
+        <v>560.849213182038</v>
       </c>
       <c r="F152" s="16" t="n">
         <f aca="false">F11</f>
-        <v>755.420810408731</v>
+        <v>745.119292740278</v>
       </c>
       <c r="G152" s="16" t="n">
         <f aca="false">G11</f>
-        <v>820.229918600517</v>
+        <v>809.315948167465</v>
       </c>
       <c r="H152" s="22" t="n">
         <f aca="false">H149*H151</f>
-        <v>875.968234963752</v>
+        <v>864.396622520005</v>
       </c>
       <c r="I152" s="22" t="n">
         <f aca="false">I149*I151</f>
-        <v>932.01027498411</v>
+        <v>919.743207131468</v>
       </c>
       <c r="J152" s="22" t="n">
         <f aca="false">J149*J151</f>
-        <v>987.930891483156</v>
+        <v>974.927799559356</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45159,27 +45159,27 @@
       </c>
       <c r="E153" s="13" t="n">
         <f aca="false">E12</f>
-        <v>7.07166188055019</v>
+        <v>6.95829714115775</v>
       </c>
       <c r="F153" s="13" t="n">
         <f aca="false">F12</f>
-        <v>9.37229177092922</v>
+        <v>9.24448376254262</v>
       </c>
       <c r="G153" s="13" t="n">
         <f aca="false">G12</f>
-        <v>10.1763599975624</v>
+        <v>10.040953461406</v>
       </c>
       <c r="H153" s="24" t="n">
         <f aca="false">$G153*H152/$G152</f>
-        <v>10.8678894822928</v>
+        <v>10.7243237682053</v>
       </c>
       <c r="I153" s="24" t="n">
         <f aca="false">$G153*I152/$G152</f>
-        <v>11.5631871803066</v>
+        <v>11.4109931481796</v>
       </c>
       <c r="J153" s="24" t="n">
         <f aca="false">$G153*J152/$G152</f>
-        <v>12.256978411125</v>
+        <v>12.0956527370704</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45204,27 +45204,27 @@
       </c>
       <c r="E156" s="16" t="n">
         <f aca="false">E15</f>
-        <v>1115.01704209625</v>
+        <v>1095.3652774009</v>
       </c>
       <c r="F156" s="16" t="n">
         <f aca="false">F15</f>
-        <v>1362.23504530487</v>
+        <v>1342.58328060951</v>
       </c>
       <c r="G156" s="16" t="n">
         <f aca="false">G15</f>
-        <v>1347.1557164714</v>
+        <v>1328.48654001082</v>
       </c>
       <c r="H156" s="22" t="n">
         <f aca="false">G156*(1+H157)</f>
-        <v>1355.1761877242</v>
+        <v>1336.90054130916</v>
       </c>
       <c r="I156" s="22" t="n">
         <f aca="false">H156*(1+I157)</f>
-        <v>1386.31382257781</v>
+        <v>1367.87219792382</v>
       </c>
       <c r="J156" s="22" t="n">
         <f aca="false">I156*(1+J157)</f>
-        <v>1441.76637548092</v>
+        <v>1422.58708584077</v>
       </c>
       <c r="K156" s="8" t="s">
         <v>543</v>
@@ -45243,23 +45243,23 @@
       </c>
       <c r="E157" s="10" t="n">
         <f aca="false">E156/D156-1</f>
-        <v>0.113235864712714</v>
+        <v>0.0936154926127222</v>
       </c>
       <c r="F157" s="10" t="n">
         <f aca="false">F156/E156-1</f>
-        <v>0.221716793443656</v>
+        <v>0.225694577242045</v>
       </c>
       <c r="G157" s="10" t="n">
         <f aca="false">G156/F156-1</f>
-        <v>-0.011069549917571</v>
+        <v>-0.0104997140976606</v>
       </c>
       <c r="H157" s="23" t="n">
         <f aca="false">$G157+((tp_g)-$G157)*1/3</f>
-        <v>0.00595363338828598</v>
+        <v>0.00633352393489294</v>
       </c>
       <c r="I157" s="23" t="n">
         <f aca="false">$G157+((tp_g)-$G157)*2/3</f>
-        <v>0.022976816694143</v>
+        <v>0.0231667619674465</v>
       </c>
       <c r="J157" s="23" t="n">
         <f aca="false">$G157+((tp_g)-$G157)*3/3</f>
@@ -45283,27 +45283,27 @@
       </c>
       <c r="E158" s="10" t="n">
         <f aca="false">E159/E156</f>
-        <v>0.357682597718757</v>
+        <v>0.355757875193926</v>
       </c>
       <c r="F158" s="10" t="n">
         <f aca="false">F159/F156</f>
-        <v>0.389710438515963</v>
+        <v>0.388608927233464</v>
       </c>
       <c r="G158" s="10" t="n">
         <f aca="false">G159/G156</f>
-        <v>0.390456787646283</v>
+        <v>0.389409736483767</v>
       </c>
       <c r="H158" s="23" t="n">
         <f aca="false">$G158+(($G158+nim10)/2-$G158)*1/3</f>
-        <v>0.371930656371902</v>
+        <v>0.371058113736472</v>
       </c>
       <c r="I158" s="23" t="n">
         <f aca="false">$G158+(($G158+nim10)/2-$G158)*2/3</f>
-        <v>0.353404525097522</v>
+        <v>0.352706490989178</v>
       </c>
       <c r="J158" s="23" t="n">
         <f aca="false">$G158+(($G158+nim10)/2-$G158)*3/3</f>
-        <v>0.334878393823141</v>
+        <v>0.334354868241883</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45323,27 +45323,27 @@
       </c>
       <c r="E159" s="16" t="n">
         <f aca="false">E21</f>
-        <v>398.822192117673</v>
+        <v>389.68482364935</v>
       </c>
       <c r="F159" s="16" t="n">
         <f aca="false">F21</f>
-        <v>530.877216867571</v>
+        <v>521.739848399248</v>
       </c>
       <c r="G159" s="16" t="n">
         <f aca="false">G21</f>
-        <v>526.006093512749</v>
+        <v>517.325593467842</v>
       </c>
       <c r="H159" s="22" t="n">
         <f aca="false">H156*H158</f>
-        <v>504.031568999835</v>
+        <v>496.067793111444</v>
       </c>
       <c r="I159" s="22" t="n">
         <f aca="false">I156*I158</f>
-        <v>489.929578104241</v>
+        <v>482.457403051363</v>
       </c>
       <c r="J159" s="22" t="n">
         <f aca="false">J156*J158</f>
-        <v>482.816408089264</v>
+        <v>475.648917648895</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45363,27 +45363,27 @@
       </c>
       <c r="E160" s="13" t="n">
         <f aca="false">E22</f>
-        <v>4.94807383877337</v>
+        <v>4.83470909938093</v>
       </c>
       <c r="F160" s="13" t="n">
         <f aca="false">F22</f>
-        <v>6.5864430824055</v>
+        <v>6.47307834301306</v>
       </c>
       <c r="G160" s="13" t="n">
         <f aca="false">G22</f>
-        <v>6.52600843630556</v>
+        <v>6.41831193388275</v>
       </c>
       <c r="H160" s="24" t="n">
         <f aca="false">$G160*H159/$G159</f>
-        <v>6.25337674225542</v>
+        <v>6.15457243319236</v>
       </c>
       <c r="I160" s="24" t="n">
         <f aca="false">$G160*I159/$G159</f>
-        <v>6.07841734028583</v>
+        <v>5.98571218337979</v>
       </c>
       <c r="J160" s="24" t="n">
         <f aca="false">$G160*J159/$G159</f>
-        <v>5.99016625707762</v>
+        <v>5.90124123575588</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45408,27 +45408,27 @@
       </c>
       <c r="E163" s="16" t="n">
         <f aca="false">E25</f>
-        <v>950.773977388857</v>
+        <v>931.122212693506</v>
       </c>
       <c r="F163" s="16" t="n">
         <f aca="false">F25</f>
-        <v>863.953429441008</v>
+        <v>848.232017684726</v>
       </c>
       <c r="G163" s="16" t="n">
         <f aca="false">G25</f>
-        <v>876.907241873864</v>
+        <v>861.185830117582</v>
       </c>
       <c r="H163" s="22" t="n">
         <f aca="false">G163*(1+H164)</f>
-        <v>891.51864836575</v>
+        <v>875.694827083127</v>
       </c>
       <c r="I163" s="22" t="n">
         <f aca="false">H163*(1+I164)</f>
-        <v>907.861268872266</v>
+        <v>891.82849542096</v>
       </c>
       <c r="J163" s="22" t="n">
         <f aca="false">I163*(1+J164)</f>
-        <v>926.018494249712</v>
+        <v>909.665065329379</v>
       </c>
       <c r="K163" s="8" t="s">
         <v>543</v>
@@ -45447,23 +45447,23 @@
       </c>
       <c r="E164" s="10" t="n">
         <f aca="false">E163/D163-1</f>
-        <v>-0.0507448308817319</v>
+        <v>-0.0703652029817236</v>
       </c>
       <c r="F164" s="10" t="n">
         <f aca="false">F163/E163-1</f>
-        <v>-0.0913156544169289</v>
+        <v>-0.0890218210657856</v>
       </c>
       <c r="G164" s="10" t="n">
         <f aca="false">G163/F163-1</f>
-        <v>0.0149936466381499</v>
+        <v>0.0152715438261977</v>
       </c>
       <c r="H164" s="23" t="n">
         <f aca="false">$G164+((tp_g-0.02)-$G164)*1/3</f>
-        <v>0.0166624310921</v>
+        <v>0.0168476958841318</v>
       </c>
       <c r="I164" s="23" t="n">
         <f aca="false">$G164+((tp_g-0.02)-$G164)*2/3</f>
-        <v>0.01833121554605</v>
+        <v>0.0184238479420659</v>
       </c>
       <c r="J164" s="23" t="n">
         <f aca="false">$G164+((tp_g-0.02)-$G164)*3/3</f>
@@ -45487,23 +45487,23 @@
       </c>
       <c r="E165" s="10" t="n">
         <f aca="false">E166/E163</f>
-        <v>0.327195971280713</v>
+        <v>0.32428830760935</v>
       </c>
       <c r="F165" s="10" t="n">
         <f aca="false">F166/F163</f>
-        <v>0.30383749672959</v>
+        <v>0.301171763874607</v>
       </c>
       <c r="G165" s="10" t="n">
         <f aca="false">G166/G163</f>
-        <v>0.306984361939944</v>
+        <v>0.304416174311757</v>
       </c>
       <c r="H165" s="23" t="n">
         <f aca="false">$G165+(nim10-$G165)*1/3</f>
-        <v>0.297756241293296</v>
+        <v>0.296044116207838</v>
       </c>
       <c r="I165" s="23" t="n">
         <f aca="false">$G165+(nim10-$G165)*2/3</f>
-        <v>0.288528120646648</v>
+        <v>0.287672058103919</v>
       </c>
       <c r="J165" s="23" t="n">
         <f aca="false">$G165+(nim10-$G165)*3/3</f>
@@ -45527,27 +45527,27 @@
       </c>
       <c r="E166" s="16" t="n">
         <f aca="false">E31</f>
-        <v>311.089415000174</v>
+        <v>301.952046531851</v>
       </c>
       <c r="F166" s="16" t="n">
         <f aca="false">F31</f>
-        <v>262.5014472923</v>
+        <v>255.463532941025</v>
       </c>
       <c r="G166" s="16" t="n">
         <f aca="false">G31</f>
-        <v>269.196810127164</v>
+        <v>262.15889577589</v>
       </c>
       <c r="H166" s="22" t="n">
         <f aca="false">H163*H165</f>
-        <v>265.455241780265</v>
+        <v>259.2443011516</v>
       </c>
       <c r="I166" s="22" t="n">
         <f aca="false">I163*I165</f>
-        <v>261.943505715596</v>
+        <v>256.554138753469</v>
       </c>
       <c r="J166" s="22" t="n">
         <f aca="false">J163*J165</f>
-        <v>258.636965443944</v>
+        <v>254.069452746496</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45567,27 +45567,27 @@
       </c>
       <c r="E167" s="13" t="n">
         <f aca="false">E32</f>
-        <v>3.85959815252081</v>
+        <v>3.74623341312837</v>
       </c>
       <c r="F167" s="13" t="n">
         <f aca="false">F32</f>
-        <v>3.25678101584663</v>
+        <v>3.16946360831683</v>
       </c>
       <c r="G167" s="13" t="n">
         <f aca="false">G32</f>
-        <v>3.33984848385381</v>
+        <v>3.252531076324</v>
       </c>
       <c r="H167" s="24" t="n">
         <f aca="false">$G167*H166/$G166</f>
-        <v>3.29342790641561</v>
+        <v>3.21637052734728</v>
       </c>
       <c r="I167" s="24" t="n">
         <f aca="false">$G167*I166/$G166</f>
-        <v>3.24985879292671</v>
+        <v>3.18299444535554</v>
       </c>
       <c r="J167" s="24" t="n">
         <f aca="false">$G167*J166/$G166</f>
-        <v>3.20883548545192</v>
+        <v>3.15216765067947</v>
       </c>
     </row>
   </sheetData>
@@ -45654,7 +45654,7 @@
       </c>
       <c r="B6" s="26" t="n">
         <f aca="false">tp_wA*B8+tp_wB*B9+tp_wC*B10</f>
-        <v>188.684289175905</v>
+        <v>184.838050297798</v>
       </c>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
@@ -45668,7 +45668,7 @@
       </c>
       <c r="B7" s="10" t="n">
         <f aca="false">B6/px-1</f>
-        <v>0.300374150075154</v>
+        <v>0.273866645746369</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>558</v>
@@ -45680,7 +45680,7 @@
       </c>
       <c r="B8" s="16" t="n">
         <f aca="false">F44</f>
-        <v>270.773933406267</v>
+        <v>266.43319753493</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>560</v>
@@ -45692,7 +45692,7 @@
       </c>
       <c r="B9" s="16" t="n">
         <f aca="false">F51</f>
-        <v>189.461747286632</v>
+        <v>185.121011415296</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>562</v>
@@ -45704,7 +45704,7 @@
       </c>
       <c r="B10" s="16" t="n">
         <f aca="false">F58</f>
-        <v>63.606177553543</v>
+        <v>61.7379266483555</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>564</v>
@@ -46200,7 +46200,7 @@
       </c>
       <c r="C44" s="30" t="n">
         <f aca="false">PL!E12</f>
-        <v>7.07166188055019</v>
+        <v>6.95829714115775</v>
       </c>
       <c r="D44" s="29" t="str">
         <f aca="false">"規則值："&amp;D38</f>
@@ -46212,11 +46212,11 @@
       </c>
       <c r="F44" s="26" t="n">
         <f aca="false">C44*E44</f>
-        <v>270.773933406267</v>
+        <v>266.43319753493</v>
       </c>
       <c r="G44" s="32" t="n">
         <f aca="false">F44/px-1</f>
-        <v>0.866119458347807</v>
+        <v>0.836203980254517</v>
       </c>
       <c r="H44" s="29"/>
     </row>
@@ -46229,7 +46229,7 @@
       </c>
       <c r="C45" s="18" t="n">
         <f aca="false">PL!E12</f>
-        <v>7.07166188055019</v>
+        <v>6.95829714115775</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>622</v>
@@ -46240,11 +46240,11 @@
       </c>
       <c r="F45" s="16" t="n">
         <f aca="false">C45*E45</f>
-        <v>116.540987791467</v>
+        <v>114.67273688628</v>
       </c>
       <c r="G45" s="27" t="n">
         <f aca="false">F45/px-1</f>
-        <v>-0.196822964910633</v>
+        <v>-0.209698574181394</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46256,7 +46256,7 @@
       </c>
       <c r="C46" s="18" t="n">
         <f aca="false">PL!E12</f>
-        <v>7.07166188055019</v>
+        <v>6.95829714115775</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>623</v>
@@ -46267,11 +46267,11 @@
       </c>
       <c r="F46" s="16" t="n">
         <f aca="false">C46*E46</f>
-        <v>270.773933406267</v>
+        <v>266.43319753493</v>
       </c>
       <c r="G46" s="27" t="n">
         <f aca="false">F46/px-1</f>
-        <v>0.866119458347807</v>
+        <v>0.836203980254517</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46283,7 +46283,7 @@
       </c>
       <c r="C47" s="18" t="n">
         <f aca="false">PL!E12</f>
-        <v>7.07166188055019</v>
+        <v>6.95829714115775</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>624</v>
@@ -46294,11 +46294,11 @@
       </c>
       <c r="F47" s="16" t="n">
         <f aca="false">C47*E47</f>
-        <v>306.980842234684</v>
+        <v>302.059678897658</v>
       </c>
       <c r="G47" s="27" t="n">
         <f aca="false">F47/px-1</f>
-        <v>1.11565018769596</v>
+        <v>1.08173452031467</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46310,7 +46310,7 @@
       </c>
       <c r="C48" s="18" t="n">
         <f aca="false">PL!F12</f>
-        <v>9.37229177092922</v>
+        <v>9.24448376254262</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>622</v>
@@ -46321,11 +46321,11 @@
       </c>
       <c r="F48" s="16" t="n">
         <f aca="false">C48*E48</f>
-        <v>154.455368384914</v>
+        <v>152.349092406702</v>
       </c>
       <c r="G48" s="27" t="n">
         <f aca="false">F48/px-1</f>
-        <v>0.0644753162295906</v>
+        <v>0.0499592860558402</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46337,7 +46337,7 @@
       </c>
       <c r="C49" s="18" t="n">
         <f aca="false">PL!F12</f>
-        <v>9.37229177092922</v>
+        <v>9.24448376254262</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>623</v>
@@ -46348,11 +46348,11 @@
       </c>
       <c r="F49" s="16" t="n">
         <f aca="false">C49*E49</f>
-        <v>358.86505190888</v>
+        <v>353.971283267757</v>
       </c>
       <c r="G49" s="27" t="n">
         <f aca="false">F49/px-1</f>
-        <v>1.47322571956499</v>
+        <v>1.43949885091493</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46364,7 +46364,7 @@
       </c>
       <c r="C50" s="18" t="n">
         <f aca="false">PL!F12</f>
-        <v>9.37229177092922</v>
+        <v>9.24448376254262</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>624</v>
@@ -46375,11 +46375,11 @@
       </c>
       <c r="F50" s="16" t="n">
         <f aca="false">C50*E50</f>
-        <v>406.851185776038</v>
+        <v>401.303040131975</v>
       </c>
       <c r="G50" s="27" t="n">
         <f aca="false">F50/px-1</f>
-        <v>1.80393649742273</v>
+        <v>1.76569979415558</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46391,7 +46391,7 @@
       </c>
       <c r="C51" s="30" t="n">
         <f aca="false">PL!E22</f>
-        <v>4.94807383877337</v>
+        <v>4.83470909938093</v>
       </c>
       <c r="D51" s="29" t="str">
         <f aca="false">"規則值："&amp;D39</f>
@@ -46403,11 +46403,11 @@
       </c>
       <c r="F51" s="26" t="n">
         <f aca="false">C51*E51</f>
-        <v>189.461747286632</v>
+        <v>185.121011415296</v>
       </c>
       <c r="G51" s="32" t="n">
         <f aca="false">F51/px-1</f>
-        <v>0.30573223491821</v>
+        <v>0.27581675682492</v>
       </c>
       <c r="H51" s="29"/>
     </row>
@@ -46420,7 +46420,7 @@
       </c>
       <c r="C52" s="18" t="n">
         <f aca="false">PL!E22</f>
-        <v>4.94807383877337</v>
+        <v>4.83470909938093</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>622</v>
@@ -46431,11 +46431,11 @@
       </c>
       <c r="F52" s="16" t="n">
         <f aca="false">C52*E52</f>
-        <v>81.5442568629851</v>
+        <v>79.6760059577977</v>
       </c>
       <c r="G52" s="27" t="n">
         <f aca="false">F52/px-1</f>
-        <v>-0.438013391709268</v>
+        <v>-0.450889000980029</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46447,7 +46447,7 @@
       </c>
       <c r="C53" s="18" t="n">
         <f aca="false">PL!E22</f>
-        <v>4.94807383877337</v>
+        <v>4.83470909938093</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>623</v>
@@ -46458,11 +46458,11 @@
       </c>
       <c r="F53" s="16" t="n">
         <f aca="false">C53*E53</f>
-        <v>189.461747286632</v>
+        <v>185.121011415296</v>
       </c>
       <c r="G53" s="27" t="n">
         <f aca="false">F53/px-1</f>
-        <v>0.30573223491821</v>
+        <v>0.27581675682492</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46474,7 +46474,7 @@
       </c>
       <c r="C54" s="18" t="n">
         <f aca="false">PL!E22</f>
-        <v>4.94807383877337</v>
+        <v>4.83470909938093</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>624</v>
@@ -46485,11 +46485,11 @@
       </c>
       <c r="F54" s="16" t="n">
         <f aca="false">C54*E54</f>
-        <v>214.795885341152</v>
+        <v>209.874722004126</v>
       </c>
       <c r="G54" s="27" t="n">
         <f aca="false">F54/px-1</f>
-        <v>0.480330016134748</v>
+        <v>0.446414348753454</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46501,7 +46501,7 @@
       </c>
       <c r="C55" s="18" t="n">
         <f aca="false">PL!F22</f>
-        <v>6.5864430824055</v>
+        <v>6.47307834301306</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>622</v>
@@ -46512,11 +46512,11 @@
       </c>
       <c r="F55" s="16" t="n">
         <f aca="false">C55*E55</f>
-        <v>108.544581998043</v>
+        <v>106.676331092855</v>
       </c>
       <c r="G55" s="27" t="n">
         <f aca="false">F55/px-1</f>
-        <v>-0.251932584438024</v>
+        <v>-0.264808193708785</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46528,7 +46528,7 @@
       </c>
       <c r="C56" s="18" t="n">
         <f aca="false">PL!F22</f>
-        <v>6.5864430824055</v>
+        <v>6.47307834301306</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>623</v>
@@ -46539,11 +46539,11 @@
       </c>
       <c r="F56" s="16" t="n">
         <f aca="false">C56*E56</f>
-        <v>252.194905625307</v>
+        <v>247.85416975397</v>
       </c>
       <c r="G56" s="27" t="n">
         <f aca="false">F56/px-1</f>
-        <v>0.738076537734712</v>
+        <v>0.708161059641421</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46555,7 +46555,7 @@
       </c>
       <c r="C57" s="18" t="n">
         <f aca="false">PL!F22</f>
-        <v>6.5864430824055</v>
+        <v>6.47307834301306</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>624</v>
@@ -46566,11 +46566,11 @@
       </c>
       <c r="F57" s="16" t="n">
         <f aca="false">C57*E57</f>
-        <v>285.917494207223</v>
+        <v>280.996330870197</v>
       </c>
       <c r="G57" s="27" t="n">
         <f aca="false">F57/px-1</f>
-        <v>0.970485831889889</v>
+        <v>0.936570164508594</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46582,7 +46582,7 @@
       </c>
       <c r="C58" s="30" t="n">
         <f aca="false">PL!E32</f>
-        <v>3.85959815252081</v>
+        <v>3.74623341312837</v>
       </c>
       <c r="D58" s="29" t="str">
         <f aca="false">"規則值："&amp;D40</f>
@@ -46594,11 +46594,11 @@
       </c>
       <c r="F58" s="26" t="n">
         <f aca="false">C58*E58</f>
-        <v>63.606177553543</v>
+        <v>61.7379266483555</v>
       </c>
       <c r="G58" s="32" t="n">
         <f aca="false">F58/px-1</f>
-        <v>-0.561639024441468</v>
+        <v>-0.574514633712229</v>
       </c>
       <c r="H58" s="29"/>
     </row>
@@ -46611,7 +46611,7 @@
       </c>
       <c r="C59" s="18" t="n">
         <f aca="false">PL!E32</f>
-        <v>3.85959815252081</v>
+        <v>3.74623341312837</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>622</v>
@@ -46622,11 +46622,11 @@
       </c>
       <c r="F59" s="16" t="n">
         <f aca="false">C59*E59</f>
-        <v>63.606177553543</v>
+        <v>61.7379266483555</v>
       </c>
       <c r="G59" s="27" t="n">
         <f aca="false">F59/px-1</f>
-        <v>-0.561639024441468</v>
+        <v>-0.574514633712229</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46638,7 +46638,7 @@
       </c>
       <c r="C60" s="18" t="n">
         <f aca="false">PL!E32</f>
-        <v>3.85959815252081</v>
+        <v>3.74623341312837</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>623</v>
@@ -46649,11 +46649,11 @@
       </c>
       <c r="F60" s="16" t="n">
         <f aca="false">C60*E60</f>
-        <v>147.784013260022</v>
+        <v>143.443277388685</v>
       </c>
       <c r="G60" s="27" t="n">
         <f aca="false">F60/px-1</f>
-        <v>0.0184976792558362</v>
+        <v>-0.0114177988374549</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46665,7 +46665,7 @@
       </c>
       <c r="C61" s="18" t="n">
         <f aca="false">PL!E32</f>
-        <v>3.85959815252081</v>
+        <v>3.74623341312837</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>624</v>
@@ -46676,11 +46676,11 @@
       </c>
       <c r="F61" s="16" t="n">
         <f aca="false">C61*E61</f>
-        <v>167.545155800928</v>
+        <v>162.623992463903</v>
       </c>
       <c r="G61" s="27" t="n">
         <f aca="false">F61/px-1</f>
-        <v>0.154687496905089</v>
+        <v>0.120771829523794</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46692,7 +46692,7 @@
       </c>
       <c r="C62" s="18" t="n">
         <f aca="false">PL!F32</f>
-        <v>3.25678101584663</v>
+        <v>3.16946360831683</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>622</v>
@@ -46703,11 +46703,11 @@
       </c>
       <c r="F62" s="16" t="n">
         <f aca="false">C62*E62</f>
-        <v>53.6717511411525</v>
+        <v>52.2327602650613</v>
       </c>
       <c r="G62" s="27" t="n">
         <f aca="false">F62/px-1</f>
-        <v>-0.630105092066489</v>
+        <v>-0.640022327601232</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46719,7 +46719,7 @@
       </c>
       <c r="C63" s="18" t="n">
         <f aca="false">PL!F32</f>
-        <v>3.25678101584663</v>
+        <v>3.16946360831683</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>623</v>
@@ -46730,11 +46730,11 @@
       </c>
       <c r="F63" s="16" t="n">
         <f aca="false">C63*E63</f>
-        <v>124.702145096768</v>
+        <v>121.358761562451</v>
       </c>
       <c r="G63" s="27" t="n">
         <f aca="false">F63/px-1</f>
-        <v>-0.140577911118073</v>
+        <v>-0.163619837612328</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46746,7 +46746,7 @@
       </c>
       <c r="C64" s="18" t="n">
         <f aca="false">PL!F32</f>
-        <v>3.25678101584663</v>
+        <v>3.16946360831683</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>624</v>
@@ -46757,11 +46757,11 @@
       </c>
       <c r="F64" s="16" t="n">
         <f aca="false">C64*E64</f>
-        <v>141.376863897902</v>
+        <v>137.586415237033</v>
       </c>
       <c r="G64" s="27" t="n">
         <f aca="false">F64/px-1</f>
-        <v>-0.0256591047697977</v>
+        <v>-0.0517821141486325</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46818,15 +46818,15 @@
       </c>
       <c r="B70" s="20" t="n">
         <f aca="false">px/PL!E12</f>
-        <v>20.5185149475375</v>
+        <v>20.852803071853</v>
       </c>
       <c r="C70" s="20" t="n">
         <f aca="false">px/PL!E22</f>
-        <v>29.3245421810379</v>
+        <v>30.0121469601097</v>
       </c>
       <c r="D70" s="20" t="n">
         <f aca="false">px/PL!E32</f>
-        <v>37.5945873808731</v>
+        <v>38.732236889327</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46835,15 +46835,15 @@
       </c>
       <c r="B71" s="20" t="n">
         <f aca="false">px/PL!F12</f>
-        <v>15.4818056827966</v>
+        <v>15.6958467045965</v>
       </c>
       <c r="C71" s="20" t="n">
         <f aca="false">px/PL!F22</f>
-        <v>22.0301000380021</v>
+        <v>22.4159190281728</v>
       </c>
       <c r="D71" s="20" t="n">
         <f aca="false">px/PL!F32</f>
-        <v>44.5531951009238</v>
+        <v>45.7806171426769</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46872,7 +46872,7 @@
       </c>
       <c r="B74" s="18" t="n">
         <f aca="false">B70/E38</f>
-        <v>0.535871374968333</v>
+        <v>0.544601803913632</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>634</v>
@@ -46919,15 +46919,15 @@
       </c>
       <c r="B81" s="13" t="n">
         <f aca="false">PL!E153</f>
-        <v>7.07166188055019</v>
+        <v>6.95829714115775</v>
       </c>
       <c r="C81" s="13" t="n">
         <f aca="false">PL!E160</f>
-        <v>4.94807383877337</v>
+        <v>4.83470909938093</v>
       </c>
       <c r="D81" s="13" t="n">
         <f aca="false">PL!E167</f>
-        <v>3.85959815252081</v>
+        <v>3.74623341312837</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46936,15 +46936,15 @@
       </c>
       <c r="B82" s="13" t="n">
         <f aca="false">PL!F153</f>
-        <v>9.37229177092922</v>
+        <v>9.24448376254262</v>
       </c>
       <c r="C82" s="13" t="n">
         <f aca="false">PL!F160</f>
-        <v>6.5864430824055</v>
+        <v>6.47307834301306</v>
       </c>
       <c r="D82" s="13" t="n">
         <f aca="false">PL!F167</f>
-        <v>3.25678101584663</v>
+        <v>3.16946360831683</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46953,15 +46953,15 @@
       </c>
       <c r="B83" s="13" t="n">
         <f aca="false">PL!G153</f>
-        <v>10.1763599975624</v>
+        <v>10.040953461406</v>
       </c>
       <c r="C83" s="13" t="n">
         <f aca="false">PL!G160</f>
-        <v>6.52600843630556</v>
+        <v>6.41831193388275</v>
       </c>
       <c r="D83" s="13" t="n">
         <f aca="false">PL!G167</f>
-        <v>3.33984848385381</v>
+        <v>3.252531076324</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46970,15 +46970,15 @@
       </c>
       <c r="B84" s="13" t="n">
         <f aca="false">PL!H153</f>
-        <v>10.8678894822928</v>
+        <v>10.7243237682053</v>
       </c>
       <c r="C84" s="13" t="n">
         <f aca="false">PL!H160</f>
-        <v>6.25337674225542</v>
+        <v>6.15457243319236</v>
       </c>
       <c r="D84" s="13" t="n">
         <f aca="false">PL!H167</f>
-        <v>3.29342790641561</v>
+        <v>3.21637052734728</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46987,15 +46987,15 @@
       </c>
       <c r="B85" s="13" t="n">
         <f aca="false">PL!I153</f>
-        <v>11.5631871803066</v>
+        <v>11.4109931481796</v>
       </c>
       <c r="C85" s="13" t="n">
         <f aca="false">PL!I160</f>
-        <v>6.07841734028583</v>
+        <v>5.98571218337979</v>
       </c>
       <c r="D85" s="13" t="n">
         <f aca="false">PL!I167</f>
-        <v>3.24985879292671</v>
+        <v>3.18299444535554</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47004,15 +47004,15 @@
       </c>
       <c r="B86" s="13" t="n">
         <f aca="false">PL!J153</f>
-        <v>12.256978411125</v>
+        <v>12.0956527370704</v>
       </c>
       <c r="C86" s="13" t="n">
         <f aca="false">PL!J160</f>
-        <v>5.99016625707762</v>
+        <v>5.90124123575588</v>
       </c>
       <c r="D86" s="13" t="n">
         <f aca="false">PL!J167</f>
-        <v>3.20883548545192</v>
+        <v>3.15216765067947</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47041,15 +47041,15 @@
       </c>
       <c r="B89" s="13" t="n">
         <f aca="false">B81*(1-$B$88)</f>
-        <v>6.23863996471037</v>
+        <v>6.13862927334689</v>
       </c>
       <c r="C89" s="13" t="n">
         <f aca="false">C81*(1-$B$88)</f>
-        <v>4.36520463228196</v>
+        <v>4.26519394091847</v>
       </c>
       <c r="D89" s="13" t="n">
         <f aca="false">D81*(1-$B$88)</f>
-        <v>3.40494832597472</v>
+        <v>3.30493763461124</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47058,15 +47058,15 @@
       </c>
       <c r="B90" s="13" t="n">
         <f aca="false">B82*(1-$B$88)</f>
-        <v>8.26826211302061</v>
+        <v>8.15550952920099</v>
       </c>
       <c r="C90" s="13" t="n">
         <f aca="false">C82*(1-$B$88)</f>
-        <v>5.81057857873547</v>
+        <v>5.71056788737198</v>
       </c>
       <c r="D90" s="13" t="n">
         <f aca="false">D82*(1-$B$88)</f>
-        <v>2.8731413555918</v>
+        <v>2.79610969352541</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47075,15 +47075,15 @@
       </c>
       <c r="B91" s="13" t="n">
         <f aca="false">B83*(1-$B$88)</f>
-        <v>8.97761335997774</v>
+        <v>8.85815733362679</v>
       </c>
       <c r="C91" s="13" t="n">
         <f aca="false">C83*(1-$B$88)</f>
-        <v>5.75726296427585</v>
+        <v>5.66225280748054</v>
       </c>
       <c r="D91" s="13" t="n">
         <f aca="false">D83*(1-$B$88)</f>
-        <v>2.94642370907963</v>
+        <v>2.86939204701323</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47092,15 +47092,15 @@
       </c>
       <c r="B92" s="13" t="n">
         <f aca="false">B84*(1-$B$88)</f>
-        <v>9.58768261287577</v>
+        <v>9.46102853684706</v>
       </c>
       <c r="C92" s="13" t="n">
         <f aca="false">C84*(1-$B$88)</f>
-        <v>5.5167465183714</v>
+        <v>5.42958107952289</v>
       </c>
       <c r="D92" s="13" t="n">
         <f aca="false">D84*(1-$B$88)</f>
-        <v>2.90547134533789</v>
+        <v>2.83749110918523</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47109,15 +47109,15 @@
       </c>
       <c r="B93" s="13" t="n">
         <f aca="false">B85*(1-$B$88)</f>
-        <v>10.2010761941116</v>
+        <v>10.0668101916845</v>
       </c>
       <c r="C93" s="13" t="n">
         <f aca="false">C85*(1-$B$88)</f>
-        <v>5.36239684275535</v>
+        <v>5.28061209306313</v>
       </c>
       <c r="D93" s="13" t="n">
         <f aca="false">D85*(1-$B$88)</f>
-        <v>2.8670345510977</v>
+        <v>2.80804663594878</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47126,15 +47126,15 @@
       </c>
       <c r="B94" s="13" t="n">
         <f aca="false">B86*(1-$B$88)</f>
-        <v>10.8131407657583</v>
+        <v>10.6708188031856</v>
       </c>
       <c r="C94" s="13" t="n">
         <f aca="false">C86*(1-$B$88)</f>
-        <v>5.28454148938417</v>
+        <v>5.20609158591716</v>
       </c>
       <c r="D94" s="13" t="n">
         <f aca="false">D86*(1-$B$88)</f>
-        <v>2.83084367407052</v>
+        <v>2.78085115113933</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47143,15 +47143,15 @@
       </c>
       <c r="B95" s="13" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(B89:B94,1/(1+tp_r)^{1;2;3;4;5;6})+B94*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>144.034188947135</v>
+        <v>142.117616352256</v>
       </c>
       <c r="C95" s="13" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(C89:C94,1/(1+tp_r)^{1;2;3;4;5;6})+C94*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>74.8817293154931</v>
+        <v>73.7146038107182</v>
       </c>
       <c r="D95" s="13" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(D89:D94,1/(1+tp_r)^{1;2;3;4;5;6})+D94*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>40.7437952005783</v>
+        <v>39.930923503431</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>653</v>
@@ -47163,15 +47163,15 @@
       </c>
       <c r="B96" s="13" t="n">
         <f aca="false">B95*(1+tp_r)</f>
-        <v>158.437607841848</v>
+        <v>156.329377987481</v>
       </c>
       <c r="C96" s="13" t="n">
         <f aca="false">C95*(1+tp_r)</f>
-        <v>82.3699022470424</v>
+        <v>81.0860641917901</v>
       </c>
       <c r="D96" s="13" t="n">
         <f aca="false">D95*(1+tp_r)</f>
-        <v>44.8181747206361</v>
+        <v>43.9240158537741</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47180,7 +47180,7 @@
       </c>
       <c r="B97" s="33" t="n">
         <f aca="false">tp_wA*B96+tp_wB*C96+tp_wC*D96</f>
-        <v>97.6798684202028</v>
+        <v>96.2266486628942</v>
       </c>
       <c r="E97" s="8" t="s">
         <v>656</v>
@@ -47329,7 +47329,7 @@
       </c>
       <c r="B107" s="13" t="n">
         <f aca="false">tp_wA*(2/12*B81+10/12*B82)+tp_wB*(2/12*C81+10/12*C82)+tp_wC*(2/12*D81+10/12*D82)</f>
-        <v>6.52479691538502</v>
+        <v>6.41216258072115</v>
       </c>
       <c r="E107" s="5" t="s">
         <v>683</v>
@@ -47341,7 +47341,7 @@
       </c>
       <c r="B108" s="33" t="n">
         <f aca="false">B106*B107</f>
-        <v>169.709967769164</v>
+        <v>166.780348724557</v>
       </c>
       <c r="E108" s="5" t="s">
         <v>685</v>
@@ -47371,7 +47371,7 @@
       </c>
       <c r="B112" s="33" t="n">
         <f aca="false">tp_w_dcf*B97+(1-tp_w_dcf)*tp_comp_adj</f>
-        <v>159.929027934149</v>
+        <v>157.284742099862</v>
       </c>
       <c r="E112" s="8" t="s">
         <v>688</v>
@@ -47383,7 +47383,7 @@
       </c>
       <c r="B113" s="13" t="n">
         <f aca="false">B108</f>
-        <v>169.709967769164</v>
+        <v>166.780348724557</v>
       </c>
       <c r="E113" s="5" t="s">
         <v>690</v>
@@ -47407,7 +47407,7 @@
       </c>
       <c r="B115" s="10" t="n">
         <f aca="false">B112/px-1</f>
-        <v>0.10219867632081</v>
+        <v>0.083974790488369</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>693</v>
@@ -47419,7 +47419,7 @@
       </c>
       <c r="B116" s="10" t="n">
         <f aca="false">B113/px-1</f>
-        <v>0.169606945342277</v>
+        <v>0.149416600444914</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47428,7 +47428,7 @@
       </c>
       <c r="B117" s="10" t="n">
         <f aca="false">B107/cons_feps-1</f>
-        <v>-0.198805200411147</v>
+        <v>-0.212635829066433</v>
       </c>
       <c r="E117" s="5" t="s">
         <v>696</v>
@@ -47453,7 +47453,7 @@
       </c>
       <c r="B119" s="34" t="str">
         <f aca="false">TEXT(D96,"#,##0.0")&amp;"～"&amp;TEXT(B96,"#,##0.0")</f>
-        <v>44.8～158.4</v>
+        <v>43.9～156.3</v>
       </c>
       <c r="E119" s="8" t="s">
         <v>699</v>
@@ -47465,15 +47465,15 @@
       </c>
       <c r="B120" s="27" t="n">
         <f aca="false">IF(px/B82&lt;MIN(B16:B25),0,IF(px/B82&gt;MAX(B16:B25),1,PERCENTRANK(B16:B25,px/B82)))</f>
-        <v>0.317</v>
+        <v>0.322</v>
       </c>
       <c r="C120" s="27" t="n">
         <f aca="false">IF(px/C82&lt;MIN(B16:B25),0,IF(px/C82&gt;MAX(B16:B25),1,PERCENTRANK(B16:B25,px/C82)))</f>
-        <v>0.551</v>
+        <v>0.557</v>
       </c>
       <c r="D120" s="27" t="n">
         <f aca="false">IF(px/D82&lt;MIN(B16:B25),0,IF(px/D82&gt;MAX(B16:B25),1,PERCENTRANK(B16:B25,px/D82)))</f>
-        <v>0.831</v>
+        <v>0.837</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>701</v>
@@ -47992,7 +47992,7 @@
       </c>
       <c r="B144" s="33" t="n">
         <f aca="false">Val!$B$108*B143</f>
-        <v>222.178187448096</v>
+        <v>218.34283553683</v>
       </c>
       <c r="E144" s="5" t="s">
         <v>748</v>
@@ -48158,27 +48158,27 @@
       </c>
       <c r="C8" s="19" t="n">
         <f aca="false">PL!E5</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">C8/B8-1</f>
-        <v>0.0672498386684064</v>
+        <v>0.0526388611997435</v>
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">PL!E15</f>
-        <v>1115.01704209625</v>
+        <v>1095.3652774009</v>
       </c>
       <c r="F8" s="10" t="n">
         <f aca="false">E8/B8-1</f>
-        <v>-0.170991046768584</v>
+        <v>-0.185602024237247</v>
       </c>
       <c r="G8" s="19" t="n">
         <f aca="false">PL!E25</f>
-        <v>950.773977388857</v>
+        <v>931.122212693506</v>
       </c>
       <c r="H8" s="10" t="n">
         <f aca="false">G8/B8-1</f>
-        <v>-0.293104849525013</v>
+        <v>-0.307715826993676</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>764</v>
@@ -48194,27 +48194,27 @@
       </c>
       <c r="C9" s="18" t="n">
         <f aca="false">PL!E12</f>
-        <v>7.07166188055019</v>
+        <v>6.95829714115775</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">C9/B9-1</f>
-        <v>0.0967217556684539</v>
+        <v>0.0791403754897257</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">PL!E22</f>
-        <v>4.94807383877337</v>
+        <v>4.83470909938093</v>
       </c>
       <c r="F9" s="10" t="n">
         <f aca="false">E9/B9-1</f>
-        <v>-0.232618821530185</v>
+        <v>-0.250200201708913</v>
       </c>
       <c r="G9" s="18" t="n">
         <f aca="false">PL!E32</f>
-        <v>3.85959815252081</v>
+        <v>3.74623341312837</v>
       </c>
       <c r="H9" s="10" t="n">
         <f aca="false">G9/B9-1</f>
-        <v>-0.40142708552717</v>
+        <v>-0.419008465705898</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>764</v>
@@ -48230,27 +48230,27 @@
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">PL!F5</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">C10/B10-1</f>
-        <v>0.0902283339977745</v>
+        <v>0.0767926131155901</v>
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">PL!F15</f>
-        <v>1362.23504530487</v>
+        <v>1342.58328060951</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">E10/B10-1</f>
-        <v>-0.173902337595594</v>
+        <v>-0.18581972067343</v>
       </c>
       <c r="G10" s="19" t="n">
         <f aca="false">PL!F25</f>
-        <v>863.953429441008</v>
+        <v>848.232017684726</v>
       </c>
       <c r="H10" s="10" t="n">
         <f aca="false">G10/B10-1</f>
-        <v>-0.476074330235896</v>
+        <v>-0.485608236698165</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>764</v>
@@ -48266,27 +48266,27 @@
       </c>
       <c r="C11" s="18" t="n">
         <f aca="false">PL!F12</f>
-        <v>9.37229177092922</v>
+        <v>9.24448376254262</v>
       </c>
       <c r="D11" s="10" t="n">
         <f aca="false">C11/B11-1</f>
-        <v>0.104832225737265</v>
+        <v>0.0897658567184512</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">PL!F22</f>
-        <v>6.5864430824055</v>
+        <v>6.47307834301306</v>
       </c>
       <c r="F11" s="10" t="n">
         <f aca="false">E11/B11-1</f>
-        <v>-0.223571486218849</v>
+        <v>-0.236935241894016</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">PL!F32</f>
-        <v>3.25678101584663</v>
+        <v>3.16946360831683</v>
       </c>
       <c r="H11" s="10" t="n">
         <f aca="false">G11/B11-1</f>
-        <v>-0.616081455163665</v>
+        <v>-0.626374677788892</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>764</v>
@@ -48307,27 +48307,27 @@
       </c>
       <c r="C13" s="19" t="n">
         <f aca="false">PL!G5</f>
-        <v>1927.10446122904</v>
+        <v>1903.63175356863</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">C13/B13-1</f>
-        <v>0.133590859546493</v>
+        <v>0.119783384452135</v>
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">PL!G15</f>
-        <v>1347.1557164714</v>
+        <v>1328.48654001082</v>
       </c>
       <c r="F13" s="10" t="n">
         <f aca="false">E13/B13-1</f>
-        <v>-0.207555460899177</v>
+        <v>-0.218537329405403</v>
       </c>
       <c r="G13" s="19" t="n">
         <f aca="false">PL!G25</f>
-        <v>876.907241873864</v>
+        <v>861.185830117582</v>
       </c>
       <c r="H13" s="10" t="n">
         <f aca="false">G13/B13-1</f>
-        <v>-0.484172210662433</v>
+        <v>-0.493420099930834</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>770</v>
@@ -48346,27 +48346,27 @@
       </c>
       <c r="C14" s="19" t="n">
         <f aca="false">PL!G5</f>
-        <v>1927.10446122904</v>
+        <v>1903.63175356863</v>
       </c>
       <c r="D14" s="10" t="n">
         <f aca="false">C14/B14-1</f>
-        <v>-0.124043426714074</v>
+        <v>-0.134712839286987</v>
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false">PL!G15</f>
-        <v>1347.1557164714</v>
+        <v>1328.48654001082</v>
       </c>
       <c r="F14" s="10" t="n">
         <f aca="false">E14/B14-1</f>
-        <v>-0.387656492513</v>
+        <v>-0.396142481813266</v>
       </c>
       <c r="G14" s="19" t="n">
         <f aca="false">PL!G25</f>
-        <v>876.907241873864</v>
+        <v>861.185830117582</v>
       </c>
       <c r="H14" s="10" t="n">
         <f aca="false">G14/B14-1</f>
-        <v>-0.601405799148244</v>
+        <v>-0.608551895401099</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>37</v>
@@ -48474,11 +48474,11 @@
       </c>
       <c r="C4" s="19" t="n">
         <f aca="false">PL!E63</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="D4" s="18" t="n">
         <f aca="false">PL!E71</f>
-        <v>7.07166188055019</v>
+        <v>6.95829714115775</v>
       </c>
       <c r="E4" s="10" t="n">
         <f aca="false">D4/D$4-1</f>
@@ -48486,11 +48486,11 @@
       </c>
       <c r="F4" s="19" t="n">
         <f aca="false">PL!F63</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G4" s="18" t="n">
         <f aca="false">PL!F71</f>
-        <v>9.37229177092922</v>
+        <v>9.24448376254262</v>
       </c>
       <c r="H4" s="10" t="n">
         <f aca="false">G4/G$4-1</f>
@@ -48506,27 +48506,27 @@
       </c>
       <c r="C5" s="19" t="n">
         <f aca="false">E83</f>
-        <v>1391.19051304085</v>
+        <v>1371.5387483455</v>
       </c>
       <c r="D5" s="18" t="n">
         <f aca="false">E91</f>
-        <v>6.77833747180235</v>
+        <v>6.66497273240991</v>
       </c>
       <c r="E5" s="10" t="n">
         <f aca="false">D5/D$4-1</f>
-        <v>-0.0414788508984847</v>
+        <v>-0.0421546253052131</v>
       </c>
       <c r="F5" s="19" t="n">
         <f aca="false">F83</f>
-        <v>1730.27218834834</v>
+        <v>1708.11668461362</v>
       </c>
       <c r="G5" s="18" t="n">
         <f aca="false">F91</f>
-        <v>8.92485910998814</v>
+        <v>8.79705110160154</v>
       </c>
       <c r="H5" s="10" t="n">
         <f aca="false">G5/G$4-1</f>
-        <v>-0.0477399415081073</v>
+        <v>-0.0483999617971114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48538,27 +48538,27 @@
       </c>
       <c r="C6" s="19" t="n">
         <f aca="false">E128</f>
-        <v>1358.5103071639</v>
+        <v>1338.85854246855</v>
       </c>
       <c r="D6" s="18" t="n">
         <f aca="false">E136</f>
-        <v>6.56175840600029</v>
+        <v>6.44839366660785</v>
       </c>
       <c r="E6" s="10" t="n">
         <f aca="false">D6/D$4-1</f>
-        <v>-0.0721051830761782</v>
+        <v>-0.0732799224013967</v>
       </c>
       <c r="F6" s="19" t="n">
         <f aca="false">F128</f>
-        <v>1675.45857030927</v>
+        <v>1653.30306657454</v>
       </c>
       <c r="G6" s="18" t="n">
         <f aca="false">F136</f>
-        <v>8.56159694962014</v>
+        <v>8.43378894123354</v>
       </c>
       <c r="H6" s="10" t="n">
         <f aca="false">G6/G$4-1</f>
-        <v>-0.0864991019404322</v>
+        <v>-0.0876949802858551</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48570,27 +48570,27 @@
       </c>
       <c r="C7" s="19" t="n">
         <f aca="false">E173</f>
-        <v>1200.58314698996</v>
+        <v>1180.93138229461</v>
       </c>
       <c r="D7" s="18" t="n">
         <f aca="false">E181</f>
-        <v>5.51513963792938</v>
+        <v>5.40177489853694</v>
       </c>
       <c r="E7" s="10" t="n">
         <f aca="false">D7/D$4-1</f>
-        <v>-0.220106994496138</v>
+        <v>-0.223692982786566</v>
       </c>
       <c r="F7" s="19" t="n">
         <f aca="false">F173</f>
-        <v>1618.99706290502</v>
+        <v>1596.8415591703</v>
       </c>
       <c r="G7" s="18" t="n">
         <f aca="false">F181</f>
-        <v>8.18741385623854</v>
+        <v>8.05960584785194</v>
       </c>
       <c r="H7" s="10" t="n">
         <f aca="false">G7/G$4-1</f>
-        <v>-0.12642349850502</v>
+        <v>-0.128171344677097</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48599,27 +48599,27 @@
       </c>
       <c r="C8" s="19" t="n">
         <f aca="false">E218</f>
-        <v>1670.31891902806</v>
+        <v>1650.6671543327</v>
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">E226</f>
-        <v>8.628184123171</v>
+        <v>8.51481938377856</v>
       </c>
       <c r="E8" s="10" t="n">
         <f aca="false">D8/D$4-1</f>
-        <v>0.220106994496138</v>
+        <v>0.223692982786566</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">F218</f>
-        <v>1976.57598261964</v>
+        <v>1954.42047888491</v>
       </c>
       <c r="G8" s="18" t="n">
         <f aca="false">F226</f>
-        <v>10.5571696856199</v>
+        <v>10.4293616772333</v>
       </c>
       <c r="H8" s="10" t="n">
         <f aca="false">G8/G$4-1</f>
-        <v>0.12642349850502</v>
+        <v>0.128171344677097</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48628,27 +48628,27 @@
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">E263</f>
-        <v>1304.96887410953</v>
+        <v>1285.31710941418</v>
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">E271</f>
-        <v>6.2069273013164</v>
+        <v>6.09356256192397</v>
       </c>
       <c r="E9" s="10" t="n">
         <f aca="false">D9/D$4-1</f>
-        <v>-0.122281663608966</v>
+        <v>-0.12427387932587</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">F263</f>
-        <v>1615.08926786843</v>
+        <v>1592.93376413371</v>
       </c>
       <c r="G9" s="18" t="n">
         <f aca="false">F271</f>
-        <v>8.16151602066316</v>
+        <v>8.03370801227656</v>
       </c>
       <c r="H9" s="10" t="n">
         <f aca="false">G9/G$4-1</f>
-        <v>-0.129186732536606</v>
+        <v>-0.130972781321977</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48660,27 +48660,27 @@
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">E308</f>
-        <v>1398.59042050839</v>
+        <v>1377.10449110814</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">E316</f>
-        <v>6.83769868255672</v>
+        <v>6.71246196988306</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">D10/D$4-1</f>
-        <v>-0.0330846131991911</v>
+        <v>-0.0353297892124496</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">F308</f>
-        <v>1727.73856845789</v>
+        <v>1703.51521770793</v>
       </c>
       <c r="G10" s="18" t="n">
         <f aca="false">F316</f>
-        <v>8.92877590529232</v>
+        <v>8.78758337126905</v>
       </c>
       <c r="H10" s="10" t="n">
         <f aca="false">G10/G$4-1</f>
-        <v>-0.0473220292834445</v>
+        <v>-0.0494241109627847</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48692,27 +48692,27 @@
       </c>
       <c r="C11" s="19" t="n">
         <f aca="false">E353</f>
-        <v>1488.10905086704</v>
+        <v>1471.0775214644</v>
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">E361</f>
-        <v>7.39820944529488</v>
+        <v>7.30142223754789</v>
       </c>
       <c r="E11" s="10" t="n">
         <f aca="false">D11/D$4-1</f>
-        <v>0.0461769199744715</v>
+        <v>0.0493116475812141</v>
       </c>
       <c r="F11" s="19" t="n">
         <f aca="false">F353</f>
-        <v>1897.85502891153</v>
+        <v>1878.65359234144</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">F361</f>
-        <v>9.99128060485078</v>
+        <v>9.88216219355519</v>
       </c>
       <c r="H11" s="10" t="n">
         <f aca="false">G11/G$4-1</f>
-        <v>0.0660445544217403</v>
+        <v>0.068979344589944</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48724,27 +48724,27 @@
       </c>
       <c r="C12" s="19" t="n">
         <f aca="false">E398</f>
-        <v>1486.74485023908</v>
+        <v>1467.09308554373</v>
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">E406</f>
-        <v>7.41159753025012</v>
+        <v>7.29823279085768</v>
       </c>
       <c r="E12" s="10" t="n">
         <f aca="false">D12/D$4-1</f>
-        <v>0.0480701220507851</v>
+        <v>0.0488532816009308</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">F398</f>
-        <v>1907.41375884049</v>
+        <v>1885.25825510576</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">F406</f>
-        <v>10.0988160916652</v>
+        <v>9.97100808327863</v>
       </c>
       <c r="H12" s="10" t="n">
         <f aca="false">G12/G$4-1</f>
-        <v>0.0775183208646499</v>
+        <v>0.0785900369774877</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48753,27 +48753,27 @@
       </c>
       <c r="C13" s="19" t="n">
         <f aca="false">E443</f>
-        <v>1409.80412439397</v>
+        <v>1390.15235969862</v>
       </c>
       <c r="D13" s="18" t="n">
         <f aca="false">E451</f>
-        <v>6.90169405570022</v>
+        <v>6.78832931630778</v>
       </c>
       <c r="E13" s="10" t="n">
         <f aca="false">D13/D$4-1</f>
-        <v>-0.024035061025393</v>
+        <v>-0.0244266408004656</v>
       </c>
       <c r="F13" s="19" t="n">
         <f aca="false">F443</f>
-        <v>1742.97290472325</v>
+        <v>1720.81740098853</v>
       </c>
       <c r="G13" s="18" t="n">
         <f aca="false">F451</f>
-        <v>9.00902961056122</v>
+        <v>8.88122160217462</v>
       </c>
       <c r="H13" s="10" t="n">
         <f aca="false">G13/G$4-1</f>
-        <v>-0.0387591604323249</v>
+        <v>-0.0392950184887436</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48782,27 +48782,27 @@
       </c>
       <c r="C14" s="19" t="n">
         <f aca="false">E488</f>
-        <v>1420.06288783998</v>
+        <v>1400.41112314463</v>
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">E496</f>
-        <v>6.96968118564021</v>
+        <v>6.85631644624777</v>
       </c>
       <c r="E14" s="10" t="n">
         <f aca="false">D14/D$4-1</f>
-        <v>-0.0144210366152358</v>
+        <v>-0.0146559844802794</v>
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">F488</f>
-        <v>1764.89835193888</v>
+        <v>1742.74284820416</v>
       </c>
       <c r="G14" s="18" t="n">
         <f aca="false">F496</f>
-        <v>9.15433447470842</v>
+        <v>9.02652646632182</v>
       </c>
       <c r="H14" s="10" t="n">
         <f aca="false">G14/G$4-1</f>
-        <v>-0.0232554962593948</v>
+        <v>-0.0235770110932459</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48811,27 +48811,27 @@
       </c>
       <c r="C15" s="19" t="n">
         <f aca="false">E533</f>
-        <v>1466.22732334705</v>
+        <v>1446.5755586517</v>
       </c>
       <c r="D15" s="18" t="n">
         <f aca="false">E541</f>
-        <v>7.27562327037015</v>
+        <v>7.16225853097771</v>
       </c>
       <c r="E15" s="10" t="n">
         <f aca="false">D15/D$4-1</f>
-        <v>0.0288420732304711</v>
+        <v>0.0293119689605581</v>
       </c>
       <c r="F15" s="19" t="n">
         <f aca="false">F533</f>
-        <v>1863.56286440922</v>
+        <v>1841.4073606745</v>
       </c>
       <c r="G15" s="18" t="n">
         <f aca="false">F541</f>
-        <v>9.80820636337083</v>
+        <v>9.68039835498423</v>
       </c>
       <c r="H15" s="10" t="n">
         <f aca="false">G15/G$4-1</f>
-        <v>0.0465109925187901</v>
+        <v>0.0471540221864928</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48843,27 +48843,27 @@
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">E578</f>
-        <v>1422.62757870149</v>
+        <v>1402.97581400614</v>
       </c>
       <c r="D16" s="18" t="n">
         <f aca="false">E586</f>
-        <v>6.98667796812521</v>
+        <v>6.87331322873277</v>
       </c>
       <c r="E16" s="10" t="n">
         <f aca="false">D16/D$4-1</f>
-        <v>-0.0120175305126966</v>
+        <v>-0.0122133204002333</v>
       </c>
       <c r="F16" s="19" t="n">
         <f aca="false">F578</f>
-        <v>1770.37971374279</v>
+        <v>1748.22421000807</v>
       </c>
       <c r="G16" s="18" t="n">
         <f aca="false">F586</f>
-        <v>9.19066069074522</v>
+        <v>9.06285268235862</v>
       </c>
       <c r="H16" s="10" t="n">
         <f aca="false">G16/G$4-1</f>
-        <v>-0.0193795802161625</v>
+        <v>-0.0196475092443718</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48875,27 +48875,27 @@
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">E623</f>
-        <v>1448.27448731652</v>
+        <v>1428.62272262117</v>
       </c>
       <c r="D17" s="18" t="n">
         <f aca="false">E631</f>
-        <v>7.15664579297517</v>
+        <v>7.04328105358273</v>
       </c>
       <c r="E17" s="10" t="n">
         <f aca="false">D17/D$4-1</f>
-        <v>0.0120175305126962</v>
+        <v>0.0122133204002324</v>
       </c>
       <c r="F17" s="19" t="n">
         <f aca="false">F623</f>
-        <v>1825.19333178187</v>
+        <v>1803.03782804715</v>
       </c>
       <c r="G17" s="18" t="n">
         <f aca="false">F631</f>
-        <v>9.55392285111322</v>
+        <v>9.42611484272663</v>
       </c>
       <c r="H17" s="10" t="n">
         <f aca="false">G17/G$4-1</f>
-        <v>0.0193795802161625</v>
+        <v>0.019647509244372</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48904,27 +48904,27 @@
       </c>
       <c r="C18" s="19" t="n">
         <f aca="false">E668</f>
-        <v>1391.61489698153</v>
+        <v>1371.96313228618</v>
       </c>
       <c r="D18" s="18" t="n">
         <f aca="false">E676</f>
-        <v>6.78114995951307</v>
+        <v>6.66778522012063</v>
       </c>
       <c r="E18" s="10" t="n">
         <f aca="false">D18/D$4-1</f>
-        <v>-0.0410811384854443</v>
+        <v>-0.0417504333522588</v>
       </c>
       <c r="F18" s="19" t="n">
         <f aca="false">F668</f>
-        <v>1738.19003614323</v>
+        <v>1716.03453240851</v>
       </c>
       <c r="G18" s="18" t="n">
         <f aca="false">F676</f>
-        <v>8.97733246603233</v>
+        <v>8.84952445764573</v>
       </c>
       <c r="H18" s="10" t="n">
         <f aca="false">G18/G$4-1</f>
-        <v>-0.0421411661683397</v>
+        <v>-0.0427237815590325</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48936,27 +48936,27 @@
       </c>
       <c r="C19" s="19" t="n">
         <f aca="false">E713</f>
-        <v>1450.032811632</v>
+        <v>1430.38104693665</v>
       </c>
       <c r="D19" s="18" t="n">
         <f aca="false">E721</f>
-        <v>7.1682986032132</v>
+        <v>7.05493386382076</v>
       </c>
       <c r="E19" s="10" t="n">
         <f aca="false">D19/D$4-1</f>
-        <v>0.0136653483007714</v>
+        <v>0.0138879844741622</v>
       </c>
       <c r="F19" s="19" t="n">
         <f aca="false">F713</f>
-        <v>1821.9538778077</v>
+        <v>1799.79837407298</v>
       </c>
       <c r="G19" s="18" t="n">
         <f aca="false">F721</f>
-        <v>9.53245426189823</v>
+        <v>9.40464625351163</v>
       </c>
       <c r="H19" s="10" t="n">
         <f aca="false">G19/G$4-1</f>
-        <v>0.0170889356502748</v>
+        <v>0.0173251957689586</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48968,27 +48968,27 @@
       </c>
       <c r="C20" s="19" t="n">
         <f aca="false">E758</f>
-        <v>1424.7030909327</v>
+        <v>1405.05132623735</v>
       </c>
       <c r="D20" s="18" t="n">
         <f aca="false">E766</f>
-        <v>7.00043285393558</v>
+        <v>6.88706811454314</v>
       </c>
       <c r="E20" s="10" t="n">
         <f aca="false">D20/D$4-1</f>
-        <v>-0.0100724593197137</v>
+        <v>-0.0102365600619866</v>
       </c>
       <c r="F20" s="19" t="n">
         <f aca="false">F758</f>
-        <v>1793.02375412174</v>
+        <v>1770.86825038702</v>
       </c>
       <c r="G20" s="18" t="n">
         <f aca="false">F766</f>
-        <v>9.34072783321432</v>
+        <v>9.21291982482772</v>
       </c>
       <c r="H20" s="10" t="n">
         <f aca="false">G20/G$4-1</f>
-        <v>-0.00336779290341838</v>
+        <v>-0.00341435374063781</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48997,27 +48997,27 @@
       </c>
       <c r="C21" s="19" t="n">
         <f aca="false">E803</f>
-        <v>1427.82684110013</v>
+        <v>1408.17507640478</v>
       </c>
       <c r="D21" s="18" t="n">
         <f aca="false">E811</f>
-        <v>7.02113464803101</v>
+        <v>6.90776990863857</v>
       </c>
       <c r="E21" s="10" t="n">
         <f aca="false">D21/D$4-1</f>
-        <v>-0.00714502946728135</v>
+        <v>-0.00726143645408828</v>
       </c>
       <c r="F21" s="19" t="n">
         <f aca="false">F803</f>
-        <v>1770.59327443953</v>
+        <v>1748.43777070481</v>
       </c>
       <c r="G21" s="18" t="n">
         <f aca="false">F811</f>
-        <v>9.19207600545792</v>
+        <v>9.06426799707132</v>
       </c>
       <c r="H21" s="10" t="n">
         <f aca="false">G21/G$4-1</f>
-        <v>-0.0192285696898906</v>
+        <v>-0.019494410948236</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49026,27 +49026,27 @@
       </c>
       <c r="C22" s="19" t="n">
         <f aca="false">E848</f>
-        <v>1442.70695079077</v>
+        <v>1423.05518609542</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">E856</f>
-        <v>7.11974847769797</v>
+        <v>7.00638373830553</v>
       </c>
       <c r="E22" s="10" t="n">
         <f aca="false">D22/D$4-1</f>
-        <v>0.00679990049864099</v>
+        <v>0.00691068463623745</v>
       </c>
       <c r="F22" s="19" t="n">
         <f aca="false">F848</f>
-        <v>1823.70740444445</v>
+        <v>1801.55190070972</v>
       </c>
       <c r="G22" s="18" t="n">
         <f aca="false">F856</f>
-        <v>9.54407527684149</v>
+        <v>9.41626726845489</v>
       </c>
       <c r="H22" s="10" t="n">
         <f aca="false">G22/G$4-1</f>
-        <v>0.0183288687666663</v>
+        <v>0.018582271365797</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49055,27 +49055,27 @@
       </c>
       <c r="C23" s="19" t="n">
         <f aca="false">E893</f>
-        <v>1350.97655956445</v>
+        <v>1341.15067721677</v>
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">E901</f>
-        <v>6.58435568612882</v>
+        <v>6.5276733164326</v>
       </c>
       <c r="E23" s="10" t="n">
         <f aca="false">D23/D$4-1</f>
-        <v>-0.0689097135373019</v>
+        <v>-0.0618863805309557</v>
       </c>
       <c r="F23" s="19" t="n">
         <f aca="false">F893</f>
-        <v>1649.31487358448</v>
+        <v>1638.86305647696</v>
       </c>
       <c r="G23" s="18" t="n">
         <f aca="false">F901</f>
-        <v>8.51580635716922</v>
+        <v>8.45551317022446</v>
       </c>
       <c r="H23" s="10" t="n">
         <f aca="false">G23/G$4-1</f>
-        <v>-0.0913848431838876</v>
+        <v>-0.0853450135869096</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49084,27 +49084,27 @@
       </c>
       <c r="C24" s="19" t="n">
         <f aca="false">E938</f>
-        <v>1519.92550645357</v>
+        <v>1490.44785941054</v>
       </c>
       <c r="D24" s="18" t="n">
         <f aca="false">E946</f>
-        <v>7.55896807497156</v>
+        <v>7.3889209658829</v>
       </c>
       <c r="E24" s="10" t="n">
         <f aca="false">D24/D$4-1</f>
-        <v>0.0689097135373014</v>
+        <v>0.0618863805309557</v>
       </c>
       <c r="F24" s="19" t="n">
         <f aca="false">F938</f>
-        <v>1957.0206678418</v>
+        <v>1921.90960796019</v>
       </c>
       <c r="G24" s="18" t="n">
         <f aca="false">F946</f>
-        <v>10.2908625781393</v>
+        <v>10.0883181138138</v>
       </c>
       <c r="H24" s="10" t="n">
         <f aca="false">G24/G$4-1</f>
-        <v>0.0980091987809555</v>
+        <v>0.0912797699629588</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49113,27 +49113,27 @@
       </c>
       <c r="C25" s="19" t="n">
         <f aca="false">E983</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="D25" s="18" t="n">
         <f aca="false">E991</f>
-        <v>6.9373517128298</v>
+        <v>6.81976899345718</v>
       </c>
       <c r="E25" s="10" t="n">
         <f aca="false">D25/D$4-1</f>
-        <v>-0.0189927304202416</v>
+        <v>-0.0199083403439598</v>
       </c>
       <c r="F25" s="19" t="n">
         <f aca="false">F983</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G25" s="18" t="n">
         <f aca="false">F991</f>
-        <v>9.10531946895113</v>
+        <v>8.97275608756609</v>
       </c>
       <c r="H25" s="10" t="n">
         <f aca="false">G25/G$4-1</f>
-        <v>-0.0284852743067801</v>
+        <v>-0.0293934936721437</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49142,27 +49142,27 @@
       </c>
       <c r="C26" s="19" t="n">
         <f aca="false">E1028</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="D26" s="18" t="n">
         <f aca="false">E1036</f>
-        <v>7.18918327730553</v>
+        <v>7.07950927039575</v>
       </c>
       <c r="E26" s="10" t="n">
         <f aca="false">D26/D$4-1</f>
-        <v>0.0166186391177114</v>
+        <v>0.0174197978009645</v>
       </c>
       <c r="F26" s="19" t="n">
         <f aca="false">F1028</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G26" s="18" t="n">
         <f aca="false">F1036</f>
-        <v>9.60589253516006</v>
+        <v>9.48224547814709</v>
       </c>
       <c r="H26" s="10" t="n">
         <f aca="false">G26/G$4-1</f>
-        <v>0.024924615018433</v>
+        <v>0.0257193069631261</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49171,27 +49171,27 @@
       </c>
       <c r="C27" s="19" t="n">
         <f aca="false">E1073</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="D27" s="18" t="n">
         <f aca="false">E1081</f>
-        <v>7.22724890439857</v>
+        <v>7.10683667785112</v>
       </c>
       <c r="E27" s="10" t="n">
         <f aca="false">D27/D$4-1</f>
-        <v>0.0220014794932861</v>
+        <v>0.0213471103173752</v>
       </c>
       <c r="F27" s="19" t="n">
         <f aca="false">F1073</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G27" s="18" t="n">
         <f aca="false">F1081</f>
-        <v>9.65781901894711</v>
+        <v>9.52206563616774</v>
       </c>
       <c r="H27" s="10" t="n">
         <f aca="false">G27/G$4-1</f>
-        <v>0.0304650404614519</v>
+        <v>0.0300267576595077</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49200,27 +49200,27 @@
       </c>
       <c r="C28" s="19" t="n">
         <f aca="false">E1118</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="D28" s="18" t="n">
         <f aca="false">E1126</f>
-        <v>6.86421251541902</v>
+        <v>6.76024442556659</v>
       </c>
       <c r="E28" s="10" t="n">
         <f aca="false">D28/D$4-1</f>
-        <v>-0.0293353059910483</v>
+        <v>-0.0284628137565001</v>
       </c>
       <c r="F28" s="19" t="n">
         <f aca="false">F1118</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G28" s="18" t="n">
         <f aca="false">F1126</f>
-        <v>8.99158877357203</v>
+        <v>8.87437459770913</v>
       </c>
       <c r="H28" s="10" t="n">
         <f aca="false">G28/G$4-1</f>
-        <v>-0.0406200539486025</v>
+        <v>-0.0400356768793433</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49232,27 +49232,27 @@
       </c>
       <c r="C29" s="19" t="n">
         <f aca="false">E1163</f>
-        <v>1416.23169290067</v>
+        <v>1396.85794887797</v>
       </c>
       <c r="D29" s="18" t="n">
         <f aca="false">E1171</f>
-        <v>7.09650465915276</v>
+        <v>6.98281437081436</v>
       </c>
       <c r="E29" s="10" t="n">
         <f aca="false">D29/D$4-1</f>
-        <v>0.00351300430113888</v>
+        <v>0.00352345252857744</v>
       </c>
       <c r="F29" s="19" t="n">
         <f aca="false">F1163</f>
-        <v>1774.67898669534</v>
+        <v>1752.83692494137</v>
       </c>
       <c r="G29" s="18" t="n">
         <f aca="false">F1171</f>
-        <v>9.40848698818243</v>
+        <v>9.28031195418769</v>
       </c>
       <c r="H29" s="10" t="n">
         <f aca="false">G29/G$4-1</f>
-        <v>0.00386193880193497</v>
+        <v>0.00387562924716711</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49261,27 +49261,27 @@
       </c>
       <c r="C30" s="19" t="n">
         <f aca="false">E1208</f>
-        <v>1454.67037311735</v>
+        <v>1434.74058774934</v>
       </c>
       <c r="D30" s="18" t="n">
         <f aca="false">E1216</f>
-        <v>7.04703287882389</v>
+        <v>6.93399368837742</v>
       </c>
       <c r="E30" s="10" t="n">
         <f aca="false">D30/D$4-1</f>
-        <v>-0.00348277422511423</v>
+        <v>-0.0034927299434484</v>
       </c>
       <c r="F30" s="19" t="n">
         <f aca="false">F1208</f>
-        <v>1820.89405882932</v>
+        <v>1798.42511311385</v>
       </c>
       <c r="G30" s="18" t="n">
         <f aca="false">F1216</f>
-        <v>9.33655344632603</v>
+        <v>9.20911246354757</v>
       </c>
       <c r="H30" s="10" t="n">
         <f aca="false">G30/G$4-1</f>
-        <v>-0.00381318950334442</v>
+        <v>-0.00382620597359606</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49290,23 +49290,23 @@
       </c>
       <c r="C31" s="19" t="n">
         <f aca="false">E1253</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="D31" s="18" t="n">
         <f aca="false">E1261</f>
-        <v>6.86727858920481</v>
+        <v>6.75719028736707</v>
       </c>
       <c r="E31" s="10" t="n">
         <f aca="false">D31/D$4-1</f>
-        <v>-0.0289017341040462</v>
+        <v>-0.0289017341040464</v>
       </c>
       <c r="F31" s="19" t="n">
         <f aca="false">F1253</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G31" s="18" t="n">
         <f aca="false">F1261</f>
-        <v>9.10141628622029</v>
+        <v>8.97730215090844</v>
       </c>
       <c r="H31" s="10" t="n">
         <f aca="false">G31/G$4-1</f>
@@ -49322,27 +49322,27 @@
       </c>
       <c r="C32" s="19" t="n">
         <f aca="false">PL!E98</f>
-        <v>1115.01704209625</v>
+        <v>1095.3652774009</v>
       </c>
       <c r="D32" s="18" t="n">
         <f aca="false">PL!E106</f>
-        <v>4.94807383877337</v>
+        <v>4.83470909938093</v>
       </c>
       <c r="E32" s="10" t="n">
         <f aca="false">D32/D$4-1</f>
-        <v>-0.300295471933904</v>
+        <v>-0.30518789276991</v>
       </c>
       <c r="F32" s="19" t="n">
         <f aca="false">PL!F98</f>
-        <v>1362.23504530487</v>
+        <v>1342.58328060951</v>
       </c>
       <c r="G32" s="18" t="n">
         <f aca="false">PL!F106</f>
-        <v>6.5864430824055</v>
+        <v>6.47307834301306</v>
       </c>
       <c r="H32" s="10" t="n">
         <f aca="false">G32/G$4-1</f>
-        <v>-0.297243060354225</v>
+        <v>-0.299790176576318</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49354,27 +49354,27 @@
       </c>
       <c r="C33" s="19" t="n">
         <f aca="false">PL!E133</f>
-        <v>950.773977388857</v>
+        <v>931.122212693506</v>
       </c>
       <c r="D33" s="18" t="n">
         <f aca="false">PL!E141</f>
-        <v>3.85959815252081</v>
+        <v>3.74623341312837</v>
       </c>
       <c r="E33" s="10" t="n">
         <f aca="false">D33/D$4-1</f>
-        <v>-0.454216248215119</v>
+        <v>-0.461616349929969</v>
       </c>
       <c r="F33" s="19" t="n">
         <f aca="false">PL!F133</f>
-        <v>863.953429441008</v>
+        <v>848.232017684726</v>
       </c>
       <c r="G33" s="18" t="n">
         <f aca="false">PL!F141</f>
-        <v>3.25678101584663</v>
+        <v>3.16946360831683</v>
       </c>
       <c r="H33" s="10" t="n">
         <f aca="false">G33/G$4-1</f>
-        <v>-0.652509642737708</v>
+        <v>-0.657150827484921</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49957,15 +49957,15 @@
       </c>
       <c r="E82" s="16" t="n">
         <f aca="false">D82*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F82" s="16" t="n">
         <f aca="false">E82*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G82" s="16" t="n">
         <f aca="false">F82*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I82" s="8" t="s">
         <v>526</v>
@@ -49988,15 +49988,15 @@
       </c>
       <c r="E83" s="16" t="n">
         <f aca="false">E81+E82</f>
-        <v>1391.19051304085</v>
+        <v>1371.5387483455</v>
       </c>
       <c r="F83" s="16" t="n">
         <f aca="false">F81+F82</f>
-        <v>1730.27218834834</v>
+        <v>1708.11668461362</v>
       </c>
       <c r="G83" s="16" t="n">
         <f aca="false">G81+G82</f>
-        <v>1907.62724420936</v>
+        <v>1884.15453654895</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50016,15 +50016,15 @@
       </c>
       <c r="E84" s="10" t="n">
         <f aca="false">E81/E83</f>
-        <v>0.338588828586917</v>
+        <v>0.343440217580404</v>
       </c>
       <c r="F84" s="10" t="n">
         <f aca="false">F81/F83</f>
-        <v>0.400452247085864</v>
+        <v>0.40564640117136</v>
       </c>
       <c r="G84" s="10" t="n">
         <f aca="false">G81/G83</f>
-        <v>0.423862356892518</v>
+        <v>0.429142813988046</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50044,15 +50044,15 @@
       </c>
       <c r="E85" s="10" t="n">
         <f aca="false">$D85+gm_prem*(E84-$D84)+0</f>
-        <v>0.65372848008887</v>
+        <v>0.654116591208349</v>
       </c>
       <c r="F85" s="10" t="n">
         <f aca="false">$D85+gm_prem*(F84-$D84)+0</f>
-        <v>0.658677553568786</v>
+        <v>0.659093085895626</v>
       </c>
       <c r="G85" s="10" t="n">
         <f aca="false">$D85+gm_prem*(G84-$D84)+0</f>
-        <v>0.660550362353318</v>
+        <v>0.660972798920961</v>
       </c>
       <c r="I85" s="8" t="s">
         <v>528</v>
@@ -50075,15 +50075,15 @@
       </c>
       <c r="E86" s="16" t="n">
         <f aca="false">E83*E85</f>
-        <v>909.460859604253</v>
+        <v>897.146250777926</v>
       </c>
       <c r="F86" s="16" t="n">
         <f aca="false">F83*F85</f>
-        <v>1139.6914520294</v>
+        <v>1125.8078967318</v>
       </c>
       <c r="G86" s="16" t="n">
         <f aca="false">G83*G85</f>
-        <v>1260.08386739755</v>
+        <v>1245.37489762239</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50103,15 +50103,15 @@
       </c>
       <c r="E87" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E83</f>
-        <v>257.849075539572</v>
+        <v>256.097898468532</v>
       </c>
       <c r="F87" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F83</f>
-        <v>288.064787167187</v>
+        <v>286.090500850459</v>
       </c>
       <c r="G87" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G83</f>
-        <v>303.868971273381</v>
+        <v>301.777308357232</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>530</v>
@@ -50134,15 +50134,15 @@
       </c>
       <c r="E88" s="16" t="n">
         <f aca="false">E86-E87</f>
-        <v>651.611784064681</v>
+        <v>641.048352309394</v>
       </c>
       <c r="F88" s="16" t="n">
         <f aca="false">F86-F87</f>
-        <v>851.62666486221</v>
+        <v>839.717395881338</v>
       </c>
       <c r="G88" s="16" t="n">
         <f aca="false">G86-G87</f>
-        <v>956.214896124174</v>
+        <v>943.597589265153</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50162,15 +50162,15 @@
       </c>
       <c r="E89" s="10" t="n">
         <f aca="false">E88/E83</f>
-        <v>0.468384292414698</v>
+        <v>0.467393541073991</v>
       </c>
       <c r="F89" s="10" t="n">
         <f aca="false">F88/F83</f>
-        <v>0.492192309740089</v>
+        <v>0.491604234912841</v>
       </c>
       <c r="G89" s="10" t="n">
         <f aca="false">G88/G83</f>
-        <v>0.501258775280539</v>
+        <v>0.50080689824597</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50190,15 +50190,15 @@
       </c>
       <c r="E90" s="16" t="n">
         <f aca="false">(E88-fin)*(1-tax)</f>
-        <v>546.344193215949</v>
+        <v>537.206824747626</v>
       </c>
       <c r="F90" s="16" t="n">
         <f aca="false">(F88-fin)*(1-tax)</f>
-        <v>719.357065105811</v>
+        <v>709.055547437358</v>
       </c>
       <c r="G90" s="16" t="n">
         <f aca="false">(G88-fin)*(1-tax)</f>
-        <v>809.82588514741</v>
+        <v>798.911914714357</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50218,15 +50218,15 @@
       </c>
       <c r="E91" s="18" t="n">
         <f aca="false">E90/shares</f>
-        <v>6.77833747180235</v>
+        <v>6.66497273240991</v>
       </c>
       <c r="F91" s="18" t="n">
         <f aca="false">F90/shares</f>
-        <v>8.92485910998814</v>
+        <v>8.79705110160154</v>
       </c>
       <c r="G91" s="18" t="n">
         <f aca="false">G90/shares</f>
-        <v>10.0472801049072</v>
+        <v>9.91187356875089</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50832,15 +50832,15 @@
       </c>
       <c r="E127" s="16" t="n">
         <f aca="false">D127*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F127" s="16" t="n">
         <f aca="false">E127*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G127" s="16" t="n">
         <f aca="false">F127*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I127" s="8" t="s">
         <v>526</v>
@@ -50863,15 +50863,15 @@
       </c>
       <c r="E128" s="16" t="n">
         <f aca="false">E126+E127</f>
-        <v>1358.5103071639</v>
+        <v>1338.85854246855</v>
       </c>
       <c r="F128" s="16" t="n">
         <f aca="false">F126+F127</f>
-        <v>1675.45857030927</v>
+        <v>1653.30306657454</v>
       </c>
       <c r="G128" s="16" t="n">
         <f aca="false">G126+G127</f>
-        <v>1850.24841569193</v>
+        <v>1826.77570803152</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50891,15 +50891,15 @@
       </c>
       <c r="E129" s="10" t="n">
         <f aca="false">E126/E128</f>
-        <v>0.322677978932619</v>
+        <v>0.327414246068551</v>
       </c>
       <c r="F129" s="10" t="n">
         <f aca="false">F126/F128</f>
-        <v>0.380837687760559</v>
+        <v>0.385941199018772</v>
       </c>
       <c r="G129" s="10" t="n">
         <f aca="false">G126/G128</f>
-        <v>0.405995511151192</v>
+        <v>0.41121225117176</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50919,15 +50919,15 @@
       </c>
       <c r="E130" s="10" t="n">
         <f aca="false">$D130+gm_prem*(E129-$D129)+0</f>
-        <v>0.652455612116526</v>
+        <v>0.652834513487401</v>
       </c>
       <c r="F130" s="10" t="n">
         <f aca="false">$D130+gm_prem*(F129-$D129)+0</f>
-        <v>0.657108388822762</v>
+        <v>0.657516669723419</v>
       </c>
       <c r="G130" s="10" t="n">
         <f aca="false">$D130+gm_prem*(G129-$D129)+0</f>
-        <v>0.659121014694012</v>
+        <v>0.659538353895658</v>
       </c>
       <c r="I130" s="8" t="s">
         <v>528</v>
@@ -50950,15 +50950,15 @@
       </c>
       <c r="E131" s="16" t="n">
         <f aca="false">E128*E130</f>
-        <v>886.367674027231</v>
+        <v>874.053065200904</v>
       </c>
       <c r="F131" s="16" t="n">
         <f aca="false">F128*F130</f>
-        <v>1100.95788167521</v>
+        <v>1087.07432637761</v>
       </c>
       <c r="G131" s="16" t="n">
         <f aca="false">G128*G130</f>
-        <v>1219.53761318685</v>
+        <v>1204.82864341168</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50978,15 +50978,15 @@
       </c>
       <c r="E132" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E128</f>
-        <v>254.936928559604</v>
+        <v>253.185751488563</v>
       </c>
       <c r="F132" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F128</f>
-        <v>283.180322459877</v>
+        <v>281.206036143149</v>
       </c>
       <c r="G132" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G128</f>
-        <v>298.755919574433</v>
+        <v>296.664256658284</v>
       </c>
       <c r="I132" s="5" t="s">
         <v>530</v>
@@ -51009,15 +51009,15 @@
       </c>
       <c r="E133" s="16" t="n">
         <f aca="false">E131-E132</f>
-        <v>631.430745467627</v>
+        <v>620.86731371234</v>
       </c>
       <c r="F133" s="16" t="n">
         <f aca="false">F131-F132</f>
-        <v>817.777559215332</v>
+        <v>805.868290234461</v>
       </c>
       <c r="G133" s="16" t="n">
         <f aca="false">G131-G132</f>
-        <v>920.78169361242</v>
+        <v>908.164386753399</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51037,15 +51037,15 @@
       </c>
       <c r="E134" s="10" t="n">
         <f aca="false">E133/E128</f>
-        <v>0.464796433371078</v>
+        <v>0.463728836182801</v>
       </c>
       <c r="F134" s="10" t="n">
         <f aca="false">F133/F128</f>
-        <v>0.488091781979654</v>
+        <v>0.487429259962681</v>
       </c>
       <c r="G134" s="10" t="n">
         <f aca="false">G133/G128</f>
-        <v>0.497653010159763</v>
+        <v>0.49714060831913</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51065,15 +51065,15 @@
       </c>
       <c r="E135" s="16" t="n">
         <f aca="false">(E133-fin)*(1-tax)</f>
-        <v>528.887594829497</v>
+        <v>519.750226361174</v>
       </c>
       <c r="F135" s="16" t="n">
         <f aca="false">(F133-fin)*(1-tax)</f>
-        <v>690.077588721263</v>
+        <v>679.776071052809</v>
       </c>
       <c r="G135" s="16" t="n">
         <f aca="false">(G133-fin)*(1-tax)</f>
-        <v>779.176164974743</v>
+        <v>768.26219454169</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51093,15 +51093,15 @@
       </c>
       <c r="E136" s="18" t="n">
         <f aca="false">E135/shares</f>
-        <v>6.56175840600029</v>
+        <v>6.44839366660785</v>
       </c>
       <c r="F136" s="18" t="n">
         <f aca="false">F135/shares</f>
-        <v>8.56159694962014</v>
+        <v>8.43378894123354</v>
       </c>
       <c r="G136" s="18" t="n">
         <f aca="false">G135/shares</f>
-        <v>9.66701771843664</v>
+        <v>9.5316111822803</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51710,15 +51710,15 @@
       </c>
       <c r="E172" s="16" t="n">
         <f aca="false">D172*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F172" s="16" t="n">
         <f aca="false">E172*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G172" s="16" t="n">
         <f aca="false">F172*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I172" s="8" t="s">
         <v>526</v>
@@ -51741,15 +51741,15 @@
       </c>
       <c r="E173" s="16" t="n">
         <f aca="false">E171+E172</f>
-        <v>1200.58314698996</v>
+        <v>1180.93138229461</v>
       </c>
       <c r="F173" s="16" t="n">
         <f aca="false">F171+F172</f>
-        <v>1618.99706290502</v>
+        <v>1596.8415591703</v>
       </c>
       <c r="G173" s="16" t="n">
         <f aca="false">G171+G172</f>
-        <v>1717.01262269664</v>
+        <v>1693.53991503623</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51769,15 +51769,15 @@
       </c>
       <c r="E174" s="10" t="n">
         <f aca="false">E171/E173</f>
-        <v>0.233581656384174</v>
+        <v>0.237468666092979</v>
       </c>
       <c r="F174" s="10" t="n">
         <f aca="false">F171/F173</f>
-        <v>0.359244790356404</v>
+        <v>0.364229160439155</v>
       </c>
       <c r="G174" s="10" t="n">
         <f aca="false">G171/G173</f>
-        <v>0.359902280345332</v>
+        <v>0.36489057789761</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51797,15 +51797,15 @@
       </c>
       <c r="E175" s="10" t="n">
         <f aca="false">$D175+gm_prem*(E174-$D174)+0</f>
-        <v>0.645327906312651</v>
+        <v>0.645638867089355</v>
       </c>
       <c r="F175" s="10" t="n">
         <f aca="false">$D175+gm_prem*(F174-$D174)+0</f>
-        <v>0.655380957030429</v>
+        <v>0.655779706637049</v>
       </c>
       <c r="G175" s="10" t="n">
         <f aca="false">$D175+gm_prem*(G174-$D174)+0</f>
-        <v>0.655433556229544</v>
+        <v>0.655832620033726</v>
       </c>
       <c r="I175" s="8" t="s">
         <v>528</v>
@@ -51828,15 +51828,15 @@
       </c>
       <c r="E176" s="16" t="n">
         <f aca="false">E173*E175</f>
-        <v>774.769808601283</v>
+        <v>762.455199774955</v>
       </c>
       <c r="F176" s="16" t="n">
         <f aca="false">F173*F175</f>
-        <v>1061.05984451615</v>
+        <v>1047.17628921855</v>
       </c>
       <c r="G176" s="16" t="n">
         <f aca="false">G173*G175</f>
-        <v>1125.38768938507</v>
+        <v>1110.67871960991</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51856,15 +51856,15 @@
       </c>
       <c r="E177" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E173</f>
-        <v>240.863972462355</v>
+        <v>239.112795391314</v>
       </c>
       <c r="F177" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F173</f>
-        <v>278.149013633648</v>
+        <v>276.17472731692</v>
       </c>
       <c r="G177" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G173</f>
-        <v>286.883221658889</v>
+        <v>284.791558742741</v>
       </c>
       <c r="I177" s="5" t="s">
         <v>530</v>
@@ -51887,15 +51887,15 @@
       </c>
       <c r="E178" s="16" t="n">
         <f aca="false">E176-E177</f>
-        <v>533.905836138928</v>
+        <v>523.342404383641</v>
       </c>
       <c r="F178" s="16" t="n">
         <f aca="false">F176-F177</f>
-        <v>782.9108308825</v>
+        <v>771.001561901628</v>
       </c>
       <c r="G178" s="16" t="n">
         <f aca="false">G176-G177</f>
-        <v>838.504467726185</v>
+        <v>825.887160867165</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51915,15 +51915,15 @@
       </c>
       <c r="E179" s="10" t="n">
         <f aca="false">E178/E173</f>
-        <v>0.444705422925109</v>
+        <v>0.443160722316281</v>
       </c>
       <c r="F179" s="10" t="n">
         <f aca="false">F178/F173</f>
-        <v>0.483577672140859</v>
+        <v>0.482829093139479</v>
       </c>
       <c r="G179" s="10" t="n">
         <f aca="false">G178/G173</f>
-        <v>0.4883507882483</v>
+        <v>0.487669144101334</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51943,15 +51943,15 @@
       </c>
       <c r="E180" s="16" t="n">
         <f aca="false">(E178-fin)*(1-tax)</f>
-        <v>444.528548260172</v>
+        <v>435.39117979185</v>
       </c>
       <c r="F180" s="16" t="n">
         <f aca="false">(F178-fin)*(1-tax)</f>
-        <v>659.917868713362</v>
+        <v>649.616351044909</v>
       </c>
       <c r="G180" s="16" t="n">
         <f aca="false">(G178-fin)*(1-tax)</f>
-        <v>708.00636458315</v>
+        <v>697.092394150098</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51971,15 +51971,15 @@
       </c>
       <c r="E181" s="18" t="n">
         <f aca="false">E180/shares</f>
-        <v>5.51513963792938</v>
+        <v>5.40177489853694</v>
       </c>
       <c r="F181" s="18" t="n">
         <f aca="false">F180/shares</f>
-        <v>8.18741385623854</v>
+        <v>8.05960584785194</v>
       </c>
       <c r="G181" s="18" t="n">
         <f aca="false">G180/shares</f>
-        <v>8.78403418745886</v>
+        <v>8.64862765130252</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52588,15 +52588,15 @@
       </c>
       <c r="E217" s="16" t="n">
         <f aca="false">D217*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F217" s="16" t="n">
         <f aca="false">E217*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G217" s="16" t="n">
         <f aca="false">F217*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I217" s="8" t="s">
         <v>526</v>
@@ -52619,15 +52619,15 @@
       </c>
       <c r="E218" s="16" t="n">
         <f aca="false">E216+E217</f>
-        <v>1670.31891902806</v>
+        <v>1650.6671543327</v>
       </c>
       <c r="F218" s="16" t="n">
         <f aca="false">F216+F217</f>
-        <v>1976.57598261964</v>
+        <v>1954.42047888491</v>
       </c>
       <c r="G218" s="16" t="n">
         <f aca="false">G216+G217</f>
-        <v>2137.19629976143</v>
+        <v>2113.72359210103</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52647,15 +52647,15 @@
       </c>
       <c r="E219" s="10" t="n">
         <f aca="false">E216/E218</f>
-        <v>0.449117808337736</v>
+        <v>0.454464711537923</v>
       </c>
       <c r="F219" s="10" t="n">
         <f aca="false">F216/F218</f>
-        <v>0.475162699751521</v>
+        <v>0.4805491910837</v>
       </c>
       <c r="G219" s="10" t="n">
         <f aca="false">G216/G218</f>
-        <v>0.485748751984512</v>
+        <v>0.49114294756162</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52675,15 +52675,15 @@
       </c>
       <c r="E220" s="10" t="n">
         <f aca="false">$D220+gm_prem*(E219-$D219)+0</f>
-        <v>0.662570798468936</v>
+        <v>0.662998550724951</v>
       </c>
       <c r="F220" s="10" t="n">
         <f aca="false">$D220+gm_prem*(F219-$D219)+0</f>
-        <v>0.664654389782039</v>
+        <v>0.665085309088613</v>
       </c>
       <c r="G220" s="10" t="n">
         <f aca="false">$D220+gm_prem*(G219-$D219)+0</f>
-        <v>0.665501273960678</v>
+        <v>0.665932809606847</v>
       </c>
       <c r="I220" s="8" t="s">
         <v>528</v>
@@ -52706,15 +52706,15 @@
       </c>
       <c r="E221" s="16" t="n">
         <f aca="false">E218*E220</f>
-        <v>1106.70453987819</v>
+        <v>1094.38993105186</v>
       </c>
       <c r="F221" s="16" t="n">
         <f aca="false">F218*F220</f>
-        <v>1313.73990358589</v>
+        <v>1299.85634828829</v>
       </c>
       <c r="G221" s="16" t="n">
         <f aca="false">G218*G220</f>
-        <v>1422.30686019528</v>
+        <v>1407.59789042011</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52734,15 +52734,15 @@
       </c>
       <c r="E222" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E218</f>
-        <v>282.722325958478</v>
+        <v>280.971148887437</v>
       </c>
       <c r="F222" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F218</f>
-        <v>310.013022540685</v>
+        <v>308.038736223957</v>
       </c>
       <c r="G222" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G218</f>
-        <v>324.325966995415</v>
+        <v>322.234304079266</v>
       </c>
       <c r="I222" s="5" t="s">
         <v>530</v>
@@ -52765,15 +52765,15 @@
       </c>
       <c r="E223" s="16" t="n">
         <f aca="false">E221-E222</f>
-        <v>823.982213919711</v>
+        <v>813.418782164424</v>
       </c>
       <c r="F223" s="16" t="n">
         <f aca="false">F221-F222</f>
-        <v>1003.7268810452</v>
+        <v>991.817612064331</v>
       </c>
       <c r="G223" s="16" t="n">
         <f aca="false">G221-G222</f>
-        <v>1097.98089319987</v>
+        <v>1085.36358634085</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52793,15 +52793,15 @@
       </c>
       <c r="E224" s="10" t="n">
         <f aca="false">E223/E218</f>
-        <v>0.493308316473586</v>
+        <v>0.492781830685457</v>
       </c>
       <c r="F224" s="10" t="n">
         <f aca="false">F223/F218</f>
-        <v>0.507810926506818</v>
+        <v>0.50747401737737</v>
       </c>
       <c r="G224" s="10" t="n">
         <f aca="false">G223/G218</f>
-        <v>0.513748266044831</v>
+        <v>0.513484161503824</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52821,15 +52821,15 @@
       </c>
       <c r="E225" s="16" t="n">
         <f aca="false">(E223-fin)*(1-tax)</f>
-        <v>695.44461504055</v>
+        <v>686.307246572227</v>
       </c>
       <c r="F225" s="16" t="n">
         <f aca="false">(F223-fin)*(1-tax)</f>
-        <v>850.9237521041</v>
+        <v>840.622234435647</v>
       </c>
       <c r="G225" s="16" t="n">
         <f aca="false">(G223-fin)*(1-tax)</f>
-        <v>932.453472617884</v>
+        <v>921.539502184832</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52849,15 +52849,15 @@
       </c>
       <c r="E226" s="18" t="n">
         <f aca="false">E225/shares</f>
-        <v>8.628184123171</v>
+        <v>8.51481938377856</v>
       </c>
       <c r="F226" s="18" t="n">
         <f aca="false">F225/shares</f>
-        <v>10.5571696856199</v>
+        <v>10.4293616772333</v>
       </c>
       <c r="G226" s="18" t="n">
         <f aca="false">G225/shares</f>
-        <v>11.5686858076659</v>
+        <v>11.4332792715096</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53466,15 +53466,15 @@
       </c>
       <c r="E262" s="16" t="n">
         <f aca="false">D262*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F262" s="16" t="n">
         <f aca="false">E262*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G262" s="16" t="n">
         <f aca="false">F262*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I262" s="8" t="s">
         <v>526</v>
@@ -53497,15 +53497,15 @@
       </c>
       <c r="E263" s="16" t="n">
         <f aca="false">E261+E262</f>
-        <v>1304.96887410953</v>
+        <v>1285.31710941418</v>
       </c>
       <c r="F263" s="16" t="n">
         <f aca="false">F261+F262</f>
-        <v>1615.08926786843</v>
+        <v>1592.93376413371</v>
       </c>
       <c r="G263" s="16" t="n">
         <f aca="false">G261+G262</f>
-        <v>1702.00606280147</v>
+        <v>1678.53335514106</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53525,15 +53525,15 @@
       </c>
       <c r="E264" s="10" t="n">
         <f aca="false">E261/E263</f>
-        <v>0.294888203738195</v>
+        <v>0.299396875994133</v>
       </c>
       <c r="F264" s="10" t="n">
         <f aca="false">F261/F263</f>
-        <v>0.357694448788461</v>
+        <v>0.362669483453717</v>
       </c>
       <c r="G264" s="10" t="n">
         <f aca="false">G261/G263</f>
-        <v>0.354258549116226</v>
+        <v>0.359212521186032</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53553,15 +53553,15 @@
       </c>
       <c r="E265" s="10" t="n">
         <f aca="false">$D265+gm_prem*(E264-$D264)+0</f>
-        <v>0.650232430100972</v>
+        <v>0.650593123881448</v>
       </c>
       <c r="F265" s="10" t="n">
         <f aca="false">$D265+gm_prem*(F264-$D264)+0</f>
-        <v>0.655256929704994</v>
+        <v>0.655654932478214</v>
       </c>
       <c r="G265" s="10" t="n">
         <f aca="false">$D265+gm_prem*(G264-$D264)+0</f>
-        <v>0.654982057731215</v>
+        <v>0.655378375496799</v>
       </c>
       <c r="I265" s="8" t="s">
         <v>528</v>
@@ -53584,15 +53584,15 @@
       </c>
       <c r="E266" s="16" t="n">
         <f aca="false">E263*E265</f>
-        <v>848.533082218373</v>
+        <v>836.218473392046</v>
       </c>
       <c r="F266" s="16" t="n">
         <f aca="false">F263*F265</f>
-        <v>1058.29843486295</v>
+        <v>1044.41487956535</v>
       </c>
       <c r="G266" s="16" t="n">
         <f aca="false">G263*G265</f>
-        <v>1114.78343328471</v>
+        <v>1100.07446350954</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53612,15 +53612,15 @@
       </c>
       <c r="E267" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E263</f>
-        <v>250.165828794827</v>
+        <v>248.414651723786</v>
       </c>
       <c r="F267" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F263</f>
-        <v>277.800788363679</v>
+        <v>275.826502046951</v>
       </c>
       <c r="G267" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G263</f>
-        <v>285.545980754013</v>
+        <v>283.454317837865</v>
       </c>
       <c r="I267" s="5" t="s">
         <v>530</v>
@@ -53643,15 +53643,15 @@
       </c>
       <c r="E268" s="16" t="n">
         <f aca="false">E266-E267</f>
-        <v>598.367253423546</v>
+        <v>587.80382166826</v>
       </c>
       <c r="F268" s="16" t="n">
         <f aca="false">F266-F267</f>
-        <v>780.497646499275</v>
+        <v>768.588377518404</v>
       </c>
       <c r="G268" s="16" t="n">
         <f aca="false">G266-G267</f>
-        <v>829.237452530697</v>
+        <v>816.620145671676</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53671,15 +53671,15 @@
       </c>
       <c r="E269" s="10" t="n">
         <f aca="false">E268/E263</f>
-        <v>0.458529904655275</v>
+        <v>0.457322023773703</v>
       </c>
       <c r="F269" s="10" t="n">
         <f aca="false">F268/F263</f>
-        <v>0.483253565005335</v>
+        <v>0.482498641703654</v>
       </c>
       <c r="G269" s="10" t="n">
         <f aca="false">G268/G263</f>
-        <v>0.487211808849722</v>
+        <v>0.486508143058646</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53699,15 +53699,15 @@
       </c>
       <c r="E270" s="16" t="n">
         <f aca="false">(E268-fin)*(1-tax)</f>
-        <v>500.287674211367</v>
+        <v>491.150305743045</v>
       </c>
       <c r="F270" s="16" t="n">
         <f aca="false">(F268-fin)*(1-tax)</f>
-        <v>657.830464221873</v>
+        <v>647.528946553419</v>
       </c>
       <c r="G270" s="16" t="n">
         <f aca="false">(G268-fin)*(1-tax)</f>
-        <v>699.990396439053</v>
+        <v>689.076426006</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53727,15 +53727,15 @@
       </c>
       <c r="E271" s="18" t="n">
         <f aca="false">E270/shares</f>
-        <v>6.2069273013164</v>
+        <v>6.09356256192397</v>
       </c>
       <c r="F271" s="18" t="n">
         <f aca="false">F270/shares</f>
-        <v>8.16151602066316</v>
+        <v>8.03370801227656</v>
       </c>
       <c r="G271" s="18" t="n">
         <f aca="false">G270/shares</f>
-        <v>8.68458234388004</v>
+        <v>8.54917580772369</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54344,15 +54344,15 @@
       </c>
       <c r="E307" s="16" t="n">
         <f aca="false">D307*(1+el*eqgA_27)</f>
-        <v>1006.02951526544</v>
+        <v>984.543585865186</v>
       </c>
       <c r="F307" s="16" t="n">
         <f aca="false">E307*(1+el*eqgA_28)</f>
-        <v>1134.20301068312</v>
+        <v>1109.97965993316</v>
       </c>
       <c r="G307" s="16" t="n">
         <f aca="false">F307*(1+el*eqgA_29)</f>
-        <v>1201.634411751</v>
+        <v>1175.97091804229</v>
       </c>
       <c r="I307" s="8" t="s">
         <v>526</v>
@@ -54375,15 +54375,15 @@
       </c>
       <c r="E308" s="16" t="n">
         <f aca="false">E306+E307</f>
-        <v>1398.59042050839</v>
+        <v>1377.10449110814</v>
       </c>
       <c r="F308" s="16" t="n">
         <f aca="false">F306+F307</f>
-        <v>1727.73856845789</v>
+        <v>1703.51521770793</v>
       </c>
       <c r="G308" s="16" t="n">
         <f aca="false">G306+G307</f>
-        <v>1833.59729261006</v>
+        <v>1807.93379890135</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54403,15 +54403,15 @@
       </c>
       <c r="E309" s="10" t="n">
         <f aca="false">E306/E308</f>
-        <v>0.280683250425992</v>
+        <v>0.285062540843986</v>
       </c>
       <c r="F309" s="10" t="n">
         <f aca="false">F306/F308</f>
-        <v>0.343533199183332</v>
+        <v>0.348418113090512</v>
       </c>
       <c r="G309" s="10" t="n">
         <f aca="false">G306/G308</f>
-        <v>0.344657402912877</v>
+        <v>0.349549790619048</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54431,15 +54431,15 @@
       </c>
       <c r="E310" s="10" t="n">
         <f aca="false">$D310+gm_prem*(E309-$D309)+0</f>
-        <v>0.654696033835996</v>
+        <v>0.655046377069436</v>
       </c>
       <c r="F310" s="10" t="n">
         <f aca="false">$D310+gm_prem*(F309-$D309)+0</f>
-        <v>0.659724029736584</v>
+        <v>0.660114822849158</v>
       </c>
       <c r="G310" s="10" t="n">
         <f aca="false">$D310+gm_prem*(G309-$D309)+0</f>
-        <v>0.659813966034947</v>
+        <v>0.660205357051441</v>
       </c>
       <c r="I310" s="8" t="s">
         <v>528</v>
@@ -54462,15 +54462,15 @@
       </c>
       <c r="E311" s="16" t="n">
         <f aca="false">E308*E310</f>
-        <v>915.651601267859</v>
+        <v>902.067307746433</v>
       </c>
       <c r="F311" s="16" t="n">
         <f aca="false">F308*F310</f>
-        <v>1139.83065071436</v>
+        <v>1124.51564615811</v>
       </c>
       <c r="G311" s="16" t="n">
         <f aca="false">G308*G310</f>
-        <v>1209.83310174799</v>
+        <v>1193.60757922903</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54490,15 +54490,15 @@
       </c>
       <c r="E312" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E308</f>
-        <v>258.508484426553</v>
+        <v>256.593864162215</v>
       </c>
       <c r="F312" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F308</f>
-        <v>287.83901522621</v>
+        <v>285.680462186587</v>
       </c>
       <c r="G312" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G308</f>
-        <v>297.27213094781</v>
+        <v>294.985246159487</v>
       </c>
       <c r="I312" s="5" t="s">
         <v>530</v>
@@ -54521,15 +54521,15 @@
       </c>
       <c r="E313" s="16" t="n">
         <f aca="false">E311-E312</f>
-        <v>657.143116841306</v>
+        <v>645.473443584218</v>
       </c>
       <c r="F313" s="16" t="n">
         <f aca="false">F311-F312</f>
-        <v>851.991635488145</v>
+        <v>838.835183971527</v>
       </c>
       <c r="G313" s="16" t="n">
         <f aca="false">G311-G312</f>
-        <v>912.560970800178</v>
+        <v>898.622333069547</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54549,15 +54549,15 @@
       </c>
       <c r="E314" s="10" t="n">
         <f aca="false">E313/E308</f>
-        <v>0.469861016638764</v>
+        <v>0.468717840768071</v>
       </c>
       <c r="F314" s="10" t="n">
         <f aca="false">F313/F308</f>
-        <v>0.493125320602525</v>
+        <v>0.492414259204667</v>
       </c>
       <c r="G314" s="10" t="n">
         <f aca="false">G313/G308</f>
-        <v>0.497688873384612</v>
+        <v>0.497043826281484</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54577,15 +54577,15 @@
       </c>
       <c r="E315" s="16" t="n">
         <f aca="false">(E313-fin)*(1-tax)</f>
-        <v>551.12879606773</v>
+        <v>541.034528700349</v>
       </c>
       <c r="F315" s="16" t="n">
         <f aca="false">(F313-fin)*(1-tax)</f>
-        <v>719.672764697246</v>
+        <v>708.29243413537</v>
       </c>
       <c r="G315" s="16" t="n">
         <f aca="false">(G313-fin)*(1-tax)</f>
-        <v>772.065239742154</v>
+        <v>760.008318105158</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54605,15 +54605,15 @@
       </c>
       <c r="E316" s="18" t="n">
         <f aca="false">E315/shares</f>
-        <v>6.83769868255672</v>
+        <v>6.71246196988306</v>
       </c>
       <c r="F316" s="18" t="n">
         <f aca="false">F315/shares</f>
-        <v>8.92877590529232</v>
+        <v>8.78758337126905</v>
       </c>
       <c r="G316" s="18" t="n">
         <f aca="false">G315/shares</f>
-        <v>9.57879448560695</v>
+        <v>9.42920767798377</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55222,15 +55222,15 @@
       </c>
       <c r="E352" s="16" t="n">
         <f aca="false">D352*(1+el*eqgA_27)</f>
-        <v>797.462420637237</v>
+        <v>780.430891234599</v>
       </c>
       <c r="F352" s="16" t="n">
         <f aca="false">E352*(1+el*eqgA_28)</f>
-        <v>899.063362126864</v>
+        <v>879.861925556772</v>
       </c>
       <c r="G352" s="16" t="n">
         <f aca="false">F352*(1+el*eqgA_29)</f>
-        <v>952.515082485547</v>
+        <v>932.17206917986</v>
       </c>
       <c r="I352" s="8" t="s">
         <v>526</v>
@@ -55253,15 +55253,15 @@
       </c>
       <c r="E353" s="16" t="n">
         <f aca="false">E351+E352</f>
-        <v>1488.10905086704</v>
+        <v>1471.0775214644</v>
       </c>
       <c r="F353" s="16" t="n">
         <f aca="false">F351+F352</f>
-        <v>1897.85502891153</v>
+        <v>1878.65359234144</v>
       </c>
       <c r="G353" s="16" t="n">
         <f aca="false">G351+G352</f>
-        <v>2060.68613068471</v>
+        <v>2040.34311737903</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55281,15 +55281,15 @@
       </c>
       <c r="E354" s="10" t="n">
         <f aca="false">E351/E353</f>
-        <v>0.464110227558524</v>
+        <v>0.469483504541819</v>
       </c>
       <c r="F354" s="10" t="n">
         <f aca="false">F351/F353</f>
-        <v>0.526273952208825</v>
+        <v>0.531652919333486</v>
       </c>
       <c r="G354" s="10" t="n">
         <f aca="false">G351/G353</f>
-        <v>0.53776799469745</v>
+        <v>0.543129750462116</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55309,15 +55309,15 @@
       </c>
       <c r="E355" s="10" t="n">
         <f aca="false">$D355+gm_prem*(E354-$D354)+0</f>
-        <v>0.655770192006599</v>
+        <v>0.656200054165262</v>
       </c>
       <c r="F355" s="10" t="n">
         <f aca="false">$D355+gm_prem*(F354-$D354)+0</f>
-        <v>0.660743289978623</v>
+        <v>0.661173607348596</v>
       </c>
       <c r="G355" s="10" t="n">
         <f aca="false">$D355+gm_prem*(G354-$D354)+0</f>
-        <v>0.661662813377713</v>
+        <v>0.662091753838886</v>
       </c>
       <c r="I355" s="8" t="s">
         <v>528</v>
@@ -55340,15 +55340,15 @@
       </c>
       <c r="E356" s="16" t="n">
         <f aca="false">E353*E355</f>
-        <v>975.857558013833</v>
+        <v>965.321149266237</v>
       </c>
       <c r="F356" s="16" t="n">
         <f aca="false">F353*F355</f>
-        <v>1253.99497570548</v>
+        <v>1242.11617260679</v>
       </c>
       <c r="G356" s="16" t="n">
         <f aca="false">G353*G355</f>
-        <v>1363.47938271728</v>
+        <v>1350.89435301858</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55368,15 +55368,15 @@
       </c>
       <c r="E357" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E353</f>
-        <v>266.485527473079</v>
+        <v>264.967840678177</v>
       </c>
       <c r="F357" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F353</f>
-        <v>302.998165031391</v>
+        <v>301.287116890226</v>
       </c>
       <c r="G357" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G353</f>
-        <v>317.508113440498</v>
+        <v>315.695338913169</v>
       </c>
       <c r="I357" s="5" t="s">
         <v>530</v>
@@ -55399,15 +55399,15 @@
       </c>
       <c r="E358" s="16" t="n">
         <f aca="false">E356-E357</f>
-        <v>709.372030540754</v>
+        <v>700.35330858806</v>
       </c>
       <c r="F358" s="16" t="n">
         <f aca="false">F356-F357</f>
-        <v>950.996810674088</v>
+        <v>940.82905571656</v>
       </c>
       <c r="G358" s="16" t="n">
         <f aca="false">G356-G357</f>
-        <v>1045.97126927678</v>
+        <v>1035.19901410541</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55427,15 +55427,15 @@
       </c>
       <c r="E359" s="10" t="n">
         <f aca="false">E358/E353</f>
-        <v>0.476693579766513</v>
+        <v>0.476081850459443</v>
       </c>
       <c r="F359" s="10" t="n">
         <f aca="false">F358/F353</f>
-        <v>0.501090334186121</v>
+        <v>0.500799646913069</v>
       </c>
       <c r="G359" s="10" t="n">
         <f aca="false">G358/G353</f>
-        <v>0.507583980743944</v>
+        <v>0.507365160931952</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55455,15 +55455,15 @@
       </c>
       <c r="E360" s="16" t="n">
         <f aca="false">(E358-fin)*(1-tax)</f>
-        <v>596.306806417753</v>
+        <v>588.505611928672</v>
       </c>
       <c r="F360" s="16" t="n">
         <f aca="false">(F358-fin)*(1-tax)</f>
-        <v>805.312241233086</v>
+        <v>796.517133194824</v>
       </c>
       <c r="G360" s="16" t="n">
         <f aca="false">(G358-fin)*(1-tax)</f>
-        <v>887.465147924417</v>
+        <v>878.14714720118</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55483,15 +55483,15 @@
       </c>
       <c r="E361" s="18" t="n">
         <f aca="false">E360/shares</f>
-        <v>7.39820944529488</v>
+        <v>7.30142223754789</v>
       </c>
       <c r="F361" s="18" t="n">
         <f aca="false">F360/shares</f>
-        <v>9.99128060485078</v>
+        <v>9.88216219355519</v>
       </c>
       <c r="G361" s="18" t="n">
         <f aca="false">G360/shares</f>
-        <v>11.0105284210772</v>
+        <v>10.8949226285221</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56100,15 +56100,15 @@
       </c>
       <c r="E397" s="16" t="n">
         <f aca="false">D397*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F397" s="16" t="n">
         <f aca="false">E397*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G397" s="16" t="n">
         <f aca="false">F397*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I397" s="8" t="s">
         <v>526</v>
@@ -56131,15 +56131,15 @@
       </c>
       <c r="E398" s="16" t="n">
         <f aca="false">E396+E397</f>
-        <v>1486.74485023908</v>
+        <v>1467.09308554373</v>
       </c>
       <c r="F398" s="16" t="n">
         <f aca="false">F396+F397</f>
-        <v>1907.41375884049</v>
+        <v>1885.25825510576</v>
       </c>
       <c r="G398" s="16" t="n">
         <f aca="false">G396+G397</f>
-        <v>2012.26610681658</v>
+        <v>1988.79339915617</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56159,15 +56159,15 @@
       </c>
       <c r="E399" s="10" t="n">
         <f aca="false">E396/E398</f>
-        <v>0.381098278738848</v>
+        <v>0.386203103901871</v>
       </c>
       <c r="F399" s="10" t="n">
         <f aca="false">F396/F398</f>
-        <v>0.456132264095287</v>
+        <v>0.461492718056075</v>
       </c>
       <c r="G399" s="10" t="n">
         <f aca="false">G396/G398</f>
-        <v>0.453821807819884</v>
+        <v>0.459178033674914</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56187,15 +56187,15 @@
       </c>
       <c r="E400" s="10" t="n">
         <f aca="false">$D400+gm_prem*(E399-$D399)+0</f>
-        <v>0.657129236101025</v>
+        <v>0.657537622114067</v>
       </c>
       <c r="F400" s="10" t="n">
         <f aca="false">$D400+gm_prem*(F399-$D399)+0</f>
-        <v>0.66313195492954</v>
+        <v>0.663560791246403</v>
       </c>
       <c r="G400" s="10" t="n">
         <f aca="false">$D400+gm_prem*(G399-$D399)+0</f>
-        <v>0.662947118427508</v>
+        <v>0.66337561649591</v>
       </c>
       <c r="I400" s="8" t="s">
         <v>528</v>
@@ -56218,15 +56218,15 @@
       </c>
       <c r="E401" s="16" t="n">
         <f aca="false">E398*E400</f>
-        <v>976.983507714739</v>
+        <v>964.668898888412</v>
       </c>
       <c r="F401" s="16" t="n">
         <f aca="false">F398*F400</f>
-        <v>1264.86701475939</v>
+        <v>1250.98345946179</v>
       </c>
       <c r="G401" s="16" t="n">
         <f aca="false">G398*G400</f>
-        <v>1334.02601702339</v>
+        <v>1319.31704724822</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56246,15 +56246,15 @@
       </c>
       <c r="E402" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E398</f>
-        <v>266.363962977624</v>
+        <v>264.612785906584</v>
       </c>
       <c r="F402" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F398</f>
-        <v>303.849947501787</v>
+        <v>301.875661185059</v>
       </c>
       <c r="G402" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G398</f>
-        <v>313.193384616314</v>
+        <v>311.101721700166</v>
       </c>
       <c r="I402" s="5" t="s">
         <v>530</v>
@@ -56277,15 +56277,15 @@
       </c>
       <c r="E403" s="16" t="n">
         <f aca="false">E401-E402</f>
-        <v>710.619544737114</v>
+        <v>700.056112981828</v>
       </c>
       <c r="F403" s="16" t="n">
         <f aca="false">F401-F402</f>
-        <v>961.017067257606</v>
+        <v>949.107798276735</v>
       </c>
       <c r="G403" s="16" t="n">
         <f aca="false">G401-G402</f>
-        <v>1020.83263240708</v>
+        <v>1008.21532554806</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56305,15 +56305,15 @@
       </c>
       <c r="E404" s="10" t="n">
         <f aca="false">E403/E398</f>
-        <v>0.477970073091453</v>
+        <v>0.477172252994687</v>
       </c>
       <c r="F404" s="10" t="n">
         <f aca="false">F403/F398</f>
-        <v>0.503832512900508</v>
+        <v>0.503436489778685</v>
       </c>
       <c r="G404" s="10" t="n">
         <f aca="false">G403/G398</f>
-        <v>0.507304987620172</v>
+        <v>0.506948246095263</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56333,15 +56333,15 @@
       </c>
       <c r="E405" s="16" t="n">
         <f aca="false">(E403-fin)*(1-tax)</f>
-        <v>597.385906197604</v>
+        <v>588.248537729281</v>
       </c>
       <c r="F405" s="16" t="n">
         <f aca="false">(F403-fin)*(1-tax)</f>
-        <v>813.979763177829</v>
+        <v>803.678245509375</v>
       </c>
       <c r="G405" s="16" t="n">
         <f aca="false">(G403-fin)*(1-tax)</f>
-        <v>865.720227032122</v>
+        <v>854.806256599069</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56361,15 +56361,15 @@
       </c>
       <c r="E406" s="18" t="n">
         <f aca="false">E405/shares</f>
-        <v>7.41159753025012</v>
+        <v>7.29823279085768</v>
       </c>
       <c r="F406" s="18" t="n">
         <f aca="false">F405/shares</f>
-        <v>10.0988160916652</v>
+        <v>9.97100808327863</v>
       </c>
       <c r="G406" s="18" t="n">
         <f aca="false">G405/shares</f>
-        <v>10.7407453540366</v>
+        <v>10.6053388178802</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56978,15 +56978,15 @@
       </c>
       <c r="E442" s="16" t="n">
         <f aca="false">D442*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F442" s="16" t="n">
         <f aca="false">E442*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G442" s="16" t="n">
         <f aca="false">F442*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I442" s="8" t="s">
         <v>526</v>
@@ -57009,15 +57009,15 @@
       </c>
       <c r="E443" s="16" t="n">
         <f aca="false">E441+E442</f>
-        <v>1409.80412439397</v>
+        <v>1390.15235969862</v>
       </c>
       <c r="F443" s="16" t="n">
         <f aca="false">F441+F442</f>
-        <v>1742.97290472325</v>
+        <v>1720.81740098853</v>
       </c>
       <c r="G443" s="16" t="n">
         <f aca="false">G441+G442</f>
-        <v>1884.52363843527</v>
+        <v>1861.05093077486</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57037,15 +57037,15 @@
       </c>
       <c r="E444" s="10" t="n">
         <f aca="false">E441/E443</f>
-        <v>0.347321425035083</v>
+        <v>0.352231303345057</v>
       </c>
       <c r="F444" s="10" t="n">
         <f aca="false">F441/F443</f>
-        <v>0.404821039017363</v>
+        <v>0.410033105118444</v>
       </c>
       <c r="G444" s="10" t="n">
         <f aca="false">G441/G443</f>
-        <v>0.416799109339401</v>
+        <v>0.422056033523936</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57065,15 +57065,15 @@
       </c>
       <c r="E445" s="10" t="n">
         <f aca="false">$D445+gm_prem*(E444-$D444)+0</f>
-        <v>0.654427087804724</v>
+        <v>0.654819878069522</v>
       </c>
       <c r="F445" s="10" t="n">
         <f aca="false">$D445+gm_prem*(F444-$D444)+0</f>
-        <v>0.659027056923306</v>
+        <v>0.659444022211392</v>
       </c>
       <c r="G445" s="10" t="n">
         <f aca="false">$D445+gm_prem*(G444-$D444)+0</f>
-        <v>0.659985302549069</v>
+        <v>0.660405856483832</v>
       </c>
       <c r="I445" s="8" t="s">
         <v>528</v>
@@ -57096,15 +57096,15 @@
       </c>
       <c r="E446" s="16" t="n">
         <f aca="false">E443*E445</f>
-        <v>922.614007502234</v>
+        <v>910.299398675907</v>
       </c>
       <c r="F446" s="16" t="n">
         <f aca="false">F443*F445</f>
-        <v>1148.66630369683</v>
+        <v>1134.78274839923</v>
       </c>
       <c r="G446" s="16" t="n">
         <f aca="false">G443*G445</f>
-        <v>1243.75790367357</v>
+        <v>1229.0489338984</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57124,15 +57124,15 @@
       </c>
       <c r="E447" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E443</f>
-        <v>259.507742326812</v>
+        <v>257.756565255772</v>
       </c>
       <c r="F447" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F443</f>
-        <v>289.196553379857</v>
+        <v>287.222267063128</v>
       </c>
       <c r="G447" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G443</f>
-        <v>301.810199182571</v>
+        <v>299.718536266422</v>
       </c>
       <c r="I447" s="5" t="s">
         <v>530</v>
@@ -57155,15 +57155,15 @@
       </c>
       <c r="E448" s="16" t="n">
         <f aca="false">E446-E447</f>
-        <v>663.106265175422</v>
+        <v>652.542833420135</v>
       </c>
       <c r="F448" s="16" t="n">
         <f aca="false">F446-F447</f>
-        <v>859.469750316974</v>
+        <v>847.560481336103</v>
       </c>
       <c r="G448" s="16" t="n">
         <f aca="false">G446-G447</f>
-        <v>941.947704491</v>
+        <v>929.33039763198</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57183,15 +57183,15 @@
       </c>
       <c r="E449" s="10" t="n">
         <f aca="false">E448/E443</f>
-        <v>0.470353472302736</v>
+        <v>0.469403823881294</v>
       </c>
       <c r="F449" s="10" t="n">
         <f aca="false">F448/F443</f>
-        <v>0.493105628887237</v>
+        <v>0.492533653395891</v>
       </c>
       <c r="G449" s="10" t="n">
         <f aca="false">G448/G443</f>
-        <v>0.499833318765429</v>
+        <v>0.499357853277583</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57211,15 +57211,15 @@
       </c>
       <c r="E450" s="16" t="n">
         <f aca="false">(E448-fin)*(1-tax)</f>
-        <v>556.28691937674</v>
+        <v>547.149550908417</v>
       </c>
       <c r="F450" s="16" t="n">
         <f aca="false">(F448-fin)*(1-tax)</f>
-        <v>726.141334024182</v>
+        <v>715.839816355729</v>
       </c>
       <c r="G450" s="16" t="n">
         <f aca="false">(G448-fin)*(1-tax)</f>
-        <v>797.484764384715</v>
+        <v>786.570793951663</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57239,15 +57239,15 @@
       </c>
       <c r="E451" s="18" t="n">
         <f aca="false">E450/shares</f>
-        <v>6.90169405570022</v>
+        <v>6.78832931630778</v>
       </c>
       <c r="F451" s="18" t="n">
         <f aca="false">F450/shares</f>
-        <v>9.00902961056122</v>
+        <v>8.88122160217462</v>
       </c>
       <c r="G451" s="18" t="n">
         <f aca="false">G450/shares</f>
-        <v>9.89416731932529</v>
+        <v>9.75876078316895</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57856,15 +57856,15 @@
       </c>
       <c r="E487" s="16" t="n">
         <f aca="false">D487*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F487" s="16" t="n">
         <f aca="false">E487*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G487" s="16" t="n">
         <f aca="false">F487*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I487" s="8" t="s">
         <v>526</v>
@@ -57887,15 +57887,15 @@
       </c>
       <c r="E488" s="16" t="n">
         <f aca="false">E486+E487</f>
-        <v>1420.06288783998</v>
+        <v>1400.41112314463</v>
       </c>
       <c r="F488" s="16" t="n">
         <f aca="false">F486+F487</f>
-        <v>1764.89835193888</v>
+        <v>1742.74284820416</v>
       </c>
       <c r="G488" s="16" t="n">
         <f aca="false">G486+G487</f>
-        <v>1901.55596755277</v>
+        <v>1878.08325989237</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57915,15 +57915,15 @@
       </c>
       <c r="E489" s="10" t="n">
         <f aca="false">E486/E488</f>
-        <v>0.352036480378182</v>
+        <v>0.356976556875887</v>
       </c>
       <c r="F489" s="10" t="n">
         <f aca="false">F486/F488</f>
-        <v>0.412214986027707</v>
+        <v>0.417455478434178</v>
       </c>
       <c r="G489" s="10" t="n">
         <f aca="false">G486/G488</f>
-        <v>0.4220228680301</v>
+        <v>0.427297404904384</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57943,15 +57943,15 @@
       </c>
       <c r="E490" s="10" t="n">
         <f aca="false">$D490+gm_prem*(E489-$D489)+0</f>
-        <v>0.654804292232171</v>
+        <v>0.655199498351988</v>
       </c>
       <c r="F490" s="10" t="n">
         <f aca="false">$D490+gm_prem*(F489-$D489)+0</f>
-        <v>0.659618572684133</v>
+        <v>0.660037812076651</v>
       </c>
       <c r="G490" s="10" t="n">
         <f aca="false">$D490+gm_prem*(G489-$D489)+0</f>
-        <v>0.660403203244325</v>
+        <v>0.660825166194268</v>
       </c>
       <c r="I490" s="8" t="s">
         <v>528</v>
@@ -57974,15 +57974,15 @@
       </c>
       <c r="E491" s="16" t="n">
         <f aca="false">E488*E490</f>
-        <v>929.863274197235</v>
+        <v>917.548665370907</v>
       </c>
       <c r="F491" s="16" t="n">
         <f aca="false">F488*F490</f>
-        <v>1164.15973183851</v>
+        <v>1150.27617654091</v>
       </c>
       <c r="G491" s="16" t="n">
         <f aca="false">G488*G490</f>
-        <v>1255.79365212021</v>
+        <v>1241.08468234504</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58002,15 +58002,15 @@
       </c>
       <c r="E492" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E488</f>
-        <v>260.421905080254</v>
+        <v>258.670728009213</v>
       </c>
       <c r="F492" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F488</f>
-        <v>291.150339262781</v>
+        <v>289.176052946052</v>
       </c>
       <c r="G492" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G488</f>
-        <v>303.327957240403</v>
+        <v>301.236294324255</v>
       </c>
       <c r="I492" s="5" t="s">
         <v>530</v>
@@ -58033,15 +58033,15 @@
       </c>
       <c r="E493" s="16" t="n">
         <f aca="false">E491-E492</f>
-        <v>669.441369116981</v>
+        <v>658.877937361694</v>
       </c>
       <c r="F493" s="16" t="n">
         <f aca="false">F491-F492</f>
-        <v>873.009392575725</v>
+        <v>861.100123594854</v>
       </c>
       <c r="G493" s="16" t="n">
         <f aca="false">G491-G492</f>
-        <v>952.465694879811</v>
+        <v>939.84838802079</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58061,15 +58061,15 @@
       </c>
       <c r="E494" s="10" t="n">
         <f aca="false">E493/E488</f>
-        <v>0.471416706153942</v>
+        <v>0.470488934622412</v>
       </c>
       <c r="F494" s="10" t="n">
         <f aca="false">F493/F488</f>
-        <v>0.494651372764133</v>
+        <v>0.494106244350501</v>
       </c>
       <c r="G494" s="10" t="n">
         <f aca="false">G493/G488</f>
-        <v>0.500887542166637</v>
+        <v>0.500429564594838</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58089,15 +58089,15 @@
       </c>
       <c r="E495" s="16" t="n">
         <f aca="false">(E493-fin)*(1-tax)</f>
-        <v>561.766784286188</v>
+        <v>552.629415817866</v>
       </c>
       <c r="F495" s="16" t="n">
         <f aca="false">(F493-fin)*(1-tax)</f>
-        <v>737.853124578002</v>
+        <v>727.551606909549</v>
       </c>
       <c r="G495" s="16" t="n">
         <f aca="false">(G493-fin)*(1-tax)</f>
-        <v>806.582826071036</v>
+        <v>795.668855637983</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58117,15 +58117,15 @@
       </c>
       <c r="E496" s="18" t="n">
         <f aca="false">E495/shares</f>
-        <v>6.96968118564021</v>
+        <v>6.85631644624777</v>
       </c>
       <c r="F496" s="18" t="n">
         <f aca="false">F495/shares</f>
-        <v>9.15433447470842</v>
+        <v>9.02652646632182</v>
       </c>
       <c r="G496" s="18" t="n">
         <f aca="false">G495/shares</f>
-        <v>10.0070443906201</v>
+        <v>9.87163785446379</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58734,15 +58734,15 @@
       </c>
       <c r="E532" s="16" t="n">
         <f aca="false">D532*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F532" s="16" t="n">
         <f aca="false">E532*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G532" s="16" t="n">
         <f aca="false">F532*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I532" s="8" t="s">
         <v>526</v>
@@ -58765,15 +58765,15 @@
       </c>
       <c r="E533" s="16" t="n">
         <f aca="false">E531+E532</f>
-        <v>1466.22732334705</v>
+        <v>1446.5755586517</v>
       </c>
       <c r="F533" s="16" t="n">
         <f aca="false">F531+F532</f>
-        <v>1863.56286440922</v>
+        <v>1841.4073606745</v>
       </c>
       <c r="G533" s="16" t="n">
         <f aca="false">G531+G532</f>
-        <v>1978.20144858156</v>
+        <v>1954.72874092115</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58793,15 +58793,15 @@
       </c>
       <c r="E534" s="10" t="n">
         <f aca="false">E531/E533</f>
-        <v>0.372437730331858</v>
+        <v>0.377497306097796</v>
       </c>
       <c r="F534" s="10" t="n">
         <f aca="false">F531/F533</f>
-        <v>0.443334688479673</v>
+        <v>0.448668816905631</v>
       </c>
       <c r="G534" s="10" t="n">
         <f aca="false">G531/G533</f>
-        <v>0.444416611263499</v>
+        <v>0.449753239808031</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58821,15 +58821,15 @@
       </c>
       <c r="E535" s="10" t="n">
         <f aca="false">$D535+gm_prem*(E534-$D534)+0</f>
-        <v>0.656436392228466</v>
+        <v>0.656841158289741</v>
       </c>
       <c r="F535" s="10" t="n">
         <f aca="false">$D535+gm_prem*(F534-$D534)+0</f>
-        <v>0.662108148880291</v>
+        <v>0.662534879154367</v>
       </c>
       <c r="G535" s="10" t="n">
         <f aca="false">$D535+gm_prem*(G534-$D534)+0</f>
-        <v>0.662194702702997</v>
+        <v>0.662621632986559</v>
       </c>
       <c r="I535" s="8" t="s">
         <v>528</v>
@@ -58852,15 +58852,15 @@
       </c>
       <c r="E536" s="16" t="n">
         <f aca="false">E533*E535</f>
-        <v>962.484974324737</v>
+        <v>950.17036549841</v>
       </c>
       <c r="F536" s="16" t="n">
         <f aca="false">F533*F535</f>
-        <v>1233.88015847604</v>
+        <v>1219.99660317844</v>
       </c>
       <c r="G536" s="16" t="n">
         <f aca="false">G533*G535</f>
-        <v>1309.95452013011</v>
+        <v>1295.24555035494</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58880,15 +58880,15 @@
       </c>
       <c r="E537" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E533</f>
-        <v>264.535637470741</v>
+        <v>262.784460399701</v>
       </c>
       <c r="F537" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F533</f>
-        <v>299.942375735939</v>
+        <v>297.968089419211</v>
       </c>
       <c r="G537" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G533</f>
-        <v>310.157868500649</v>
+        <v>308.066205584501</v>
       </c>
       <c r="I537" s="5" t="s">
         <v>530</v>
@@ -58911,15 +58911,15 @@
       </c>
       <c r="E538" s="16" t="n">
         <f aca="false">E536-E537</f>
-        <v>697.949336853996</v>
+        <v>687.38590509871</v>
       </c>
       <c r="F538" s="16" t="n">
         <f aca="false">F536-F537</f>
-        <v>933.937782740104</v>
+        <v>922.028513759233</v>
       </c>
       <c r="G538" s="16" t="n">
         <f aca="false">G536-G537</f>
-        <v>999.796651629456</v>
+        <v>987.179344770436</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58939,15 +58939,15 @@
       </c>
       <c r="E539" s="10" t="n">
         <f aca="false">E538/E533</f>
-        <v>0.47601713986665</v>
+        <v>0.475181473230059</v>
       </c>
       <c r="F539" s="10" t="n">
         <f aca="false">F538/F533</f>
-        <v>0.501157111775876</v>
+        <v>0.500719467864784</v>
       </c>
       <c r="G539" s="10" t="n">
         <f aca="false">G538/G533</f>
-        <v>0.505406894907667</v>
+        <v>0.505021143908302</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58967,15 +58967,15 @@
       </c>
       <c r="E540" s="16" t="n">
         <f aca="false">(E538-fin)*(1-tax)</f>
-        <v>586.426176378707</v>
+        <v>577.288807910384</v>
       </c>
       <c r="F540" s="16" t="n">
         <f aca="false">(F538-fin)*(1-tax)</f>
-        <v>790.55618207019</v>
+        <v>780.254664401736</v>
       </c>
       <c r="G540" s="16" t="n">
         <f aca="false">(G538-fin)*(1-tax)</f>
-        <v>847.52410365948</v>
+        <v>836.610133226427</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58995,15 +58995,15 @@
       </c>
       <c r="E541" s="18" t="n">
         <f aca="false">E540/shares</f>
-        <v>7.27562327037015</v>
+        <v>7.16225853097771</v>
       </c>
       <c r="F541" s="18" t="n">
         <f aca="false">F540/shares</f>
-        <v>9.80820636337083</v>
+        <v>9.68039835498423</v>
       </c>
       <c r="G541" s="18" t="n">
         <f aca="false">G540/shares</f>
-        <v>10.5149912114469</v>
+        <v>10.3795846752906</v>
       </c>
     </row>
     <row r="542" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59612,15 +59612,15 @@
       </c>
       <c r="E577" s="16" t="n">
         <f aca="false">D577*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F577" s="16" t="n">
         <f aca="false">E577*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G577" s="16" t="n">
         <f aca="false">F577*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I577" s="8" t="s">
         <v>526</v>
@@ -59643,15 +59643,15 @@
       </c>
       <c r="E578" s="16" t="n">
         <f aca="false">E576+E577</f>
-        <v>1422.62757870149</v>
+        <v>1402.97581400614</v>
       </c>
       <c r="F578" s="16" t="n">
         <f aca="false">F576+F577</f>
-        <v>1770.37971374279</v>
+        <v>1748.22421000807</v>
       </c>
       <c r="G578" s="16" t="n">
         <f aca="false">G576+G577</f>
-        <v>1905.81404983215</v>
+        <v>1882.34134217174</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59671,15 +59671,15 @@
       </c>
       <c r="E579" s="10" t="n">
         <f aca="false">E576/E578</f>
-        <v>0.353204618928454</v>
+        <v>0.358152027138346</v>
       </c>
       <c r="F579" s="10" t="n">
         <f aca="false">F576/F578</f>
-        <v>0.414034856815587</v>
+        <v>0.419281981734673</v>
       </c>
       <c r="G579" s="10" t="n">
         <f aca="false">G576/G578</f>
-        <v>0.423314218665144</v>
+        <v>0.428592926984729</v>
       </c>
     </row>
     <row r="580" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59699,15 +59699,15 @@
       </c>
       <c r="E580" s="10" t="n">
         <f aca="false">$D580+gm_prem*(E579-$D579)+0</f>
-        <v>0.654897743316193</v>
+        <v>0.655293535972985</v>
       </c>
       <c r="F580" s="10" t="n">
         <f aca="false">$D580+gm_prem*(F579-$D579)+0</f>
-        <v>0.659764162347164</v>
+        <v>0.660183932340691</v>
       </c>
       <c r="G580" s="10" t="n">
         <f aca="false">$D580+gm_prem*(G579-$D579)+0</f>
-        <v>0.660506511295128</v>
+        <v>0.660928807960695</v>
       </c>
       <c r="I580" s="8" t="s">
         <v>528</v>
@@ -59730,15 +59730,15 @@
       </c>
       <c r="E581" s="16" t="n">
         <f aca="false">E578*E580</f>
-        <v>931.675590870985</v>
+        <v>919.360982044658</v>
       </c>
       <c r="F581" s="16" t="n">
         <f aca="false">F578*F580</f>
-        <v>1168.03308887392</v>
+        <v>1154.14953357632</v>
       </c>
       <c r="G581" s="16" t="n">
         <f aca="false">G578*G580</f>
-        <v>1258.80258923187</v>
+        <v>1244.09361945671</v>
       </c>
     </row>
     <row r="582" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59758,15 +59758,15 @@
       </c>
       <c r="E582" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E578</f>
-        <v>260.650445768614</v>
+        <v>258.899268697574</v>
       </c>
       <c r="F582" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F578</f>
-        <v>291.638785733512</v>
+        <v>289.664499416783</v>
       </c>
       <c r="G582" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G578</f>
-        <v>303.707396754861</v>
+        <v>301.615733838713</v>
       </c>
       <c r="I582" s="5" t="s">
         <v>530</v>
@@ -59789,15 +59789,15 @@
       </c>
       <c r="E583" s="16" t="n">
         <f aca="false">E581-E582</f>
-        <v>671.02514510237</v>
+        <v>660.461713347084</v>
       </c>
       <c r="F583" s="16" t="n">
         <f aca="false">F581-F582</f>
-        <v>876.394303140413</v>
+        <v>864.485034159541</v>
       </c>
       <c r="G583" s="16" t="n">
         <f aca="false">G581-G582</f>
-        <v>955.095192477013</v>
+        <v>942.477885617993</v>
       </c>
     </row>
     <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59817,15 +59817,15 @@
       </c>
       <c r="E584" s="10" t="n">
         <f aca="false">E583/E578</f>
-        <v>0.471680118639941</v>
+        <v>0.470757732780271</v>
       </c>
       <c r="F584" s="10" t="n">
         <f aca="false">F583/F578</f>
-        <v>0.495031826414014</v>
+        <v>0.494493228734975</v>
       </c>
       <c r="G584" s="10" t="n">
         <f aca="false">G583/G578</f>
-        <v>0.501148153756727</v>
+        <v>0.500694461999444</v>
       </c>
     </row>
     <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59845,15 +59845,15 @@
       </c>
       <c r="E585" s="16" t="n">
         <f aca="false">(E583-fin)*(1-tax)</f>
-        <v>563.13675051355</v>
+        <v>553.999382045227</v>
       </c>
       <c r="F585" s="16" t="n">
         <f aca="false">(F583-fin)*(1-tax)</f>
-        <v>740.781072216457</v>
+        <v>730.479554548003</v>
       </c>
       <c r="G585" s="16" t="n">
         <f aca="false">(G583-fin)*(1-tax)</f>
-        <v>808.857341492616</v>
+        <v>797.943371059564</v>
       </c>
     </row>
     <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59873,15 +59873,15 @@
       </c>
       <c r="E586" s="18" t="n">
         <f aca="false">E585/shares</f>
-        <v>6.98667796812521</v>
+        <v>6.87331322873277</v>
       </c>
       <c r="F586" s="18" t="n">
         <f aca="false">F585/shares</f>
-        <v>9.19066069074522</v>
+        <v>9.06285268235862</v>
       </c>
       <c r="G586" s="18" t="n">
         <f aca="false">G585/shares</f>
-        <v>10.0352636584438</v>
+        <v>9.8998571222875</v>
       </c>
     </row>
     <row r="587" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60490,15 +60490,15 @@
       </c>
       <c r="E622" s="16" t="n">
         <f aca="false">D622*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F622" s="16" t="n">
         <f aca="false">E622*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G622" s="16" t="n">
         <f aca="false">F622*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I622" s="8" t="s">
         <v>526</v>
@@ -60521,15 +60521,15 @@
       </c>
       <c r="E623" s="16" t="n">
         <f aca="false">E621+E622</f>
-        <v>1448.27448731652</v>
+        <v>1428.62272262117</v>
       </c>
       <c r="F623" s="16" t="n">
         <f aca="false">F621+F622</f>
-        <v>1825.19333178187</v>
+        <v>1803.03782804715</v>
       </c>
       <c r="G623" s="16" t="n">
         <f aca="false">G621+G622</f>
-        <v>1948.39487262592</v>
+        <v>1924.92216496551</v>
       </c>
     </row>
     <row r="624" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60549,15 +60549,15 @@
       </c>
       <c r="E624" s="10" t="n">
         <f aca="false">E621/E623</f>
-        <v>0.364658457393638</v>
+        <v>0.369674604823885</v>
       </c>
       <c r="F624" s="10" t="n">
         <f aca="false">F621/F623</f>
-        <v>0.431632373190123</v>
+        <v>0.436936217905682</v>
       </c>
       <c r="G624" s="10" t="n">
         <f aca="false">G621/G623</f>
-        <v>0.435917287687602</v>
+        <v>0.441232909921186</v>
       </c>
     </row>
     <row r="625" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60577,15 +60577,15 @@
       </c>
       <c r="E625" s="10" t="n">
         <f aca="false">$D625+gm_prem*(E624-$D624)+0</f>
-        <v>0.655814050393408</v>
+        <v>0.656215342187828</v>
       </c>
       <c r="F625" s="10" t="n">
         <f aca="false">$D625+gm_prem*(F624-$D624)+0</f>
-        <v>0.661171963657127</v>
+        <v>0.661596271234371</v>
       </c>
       <c r="G625" s="10" t="n">
         <f aca="false">$D625+gm_prem*(G624-$D624)+0</f>
-        <v>0.661514756816925</v>
+        <v>0.661940006595612</v>
       </c>
       <c r="I625" s="8" t="s">
         <v>528</v>
@@ -60608,15 +60608,15 @@
       </c>
       <c r="E626" s="16" t="n">
         <f aca="false">E623*E625</f>
-        <v>949.798757608486</v>
+        <v>937.484148782159</v>
       </c>
       <c r="F626" s="16" t="n">
         <f aca="false">F623*F625</f>
-        <v>1206.76665922811</v>
+        <v>1192.88310393051</v>
       </c>
       <c r="G626" s="16" t="n">
         <f aca="false">G623*G625</f>
-        <v>1288.89196034848</v>
+        <v>1274.18299057331</v>
       </c>
     </row>
     <row r="627" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60636,15 +60636,15 @@
       </c>
       <c r="E627" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E623</f>
-        <v>262.935852652218</v>
+        <v>261.184675581178</v>
       </c>
       <c r="F627" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F623</f>
-        <v>296.523250440822</v>
+        <v>294.548964124094</v>
       </c>
       <c r="G627" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G623</f>
-        <v>307.501791899443</v>
+        <v>305.410128983294</v>
       </c>
       <c r="I627" s="5" t="s">
         <v>530</v>
@@ -60667,15 +60667,15 @@
       </c>
       <c r="E628" s="16" t="n">
         <f aca="false">E626-E627</f>
-        <v>686.862904956268</v>
+        <v>676.299473200981</v>
       </c>
       <c r="F628" s="16" t="n">
         <f aca="false">F626-F627</f>
-        <v>910.24340878729</v>
+        <v>898.334139806419</v>
       </c>
       <c r="G628" s="16" t="n">
         <f aca="false">G626-G627</f>
-        <v>981.390168449039</v>
+        <v>968.772861590018</v>
       </c>
     </row>
     <row r="629" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60695,15 +60695,15 @@
       </c>
       <c r="E629" s="10" t="n">
         <f aca="false">E628/E623</f>
-        <v>0.474262932180032</v>
+        <v>0.473392633682976</v>
       </c>
       <c r="F629" s="10" t="n">
         <f aca="false">F628/F623</f>
-        <v>0.498710680637132</v>
+        <v>0.498233662007744</v>
       </c>
       <c r="G629" s="10" t="n">
         <f aca="false">G628/G623</f>
-        <v>0.503691619310404</v>
+        <v>0.50327897887101</v>
       </c>
     </row>
     <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60723,15 +60723,15 @@
       </c>
       <c r="E630" s="16" t="n">
         <f aca="false">(E628-fin)*(1-tax)</f>
-        <v>576.836412787172</v>
+        <v>567.699044318849</v>
       </c>
       <c r="F630" s="16" t="n">
         <f aca="false">(F628-fin)*(1-tax)</f>
-        <v>770.060548601006</v>
+        <v>759.759030932552</v>
       </c>
       <c r="G630" s="16" t="n">
         <f aca="false">(G628-fin)*(1-tax)</f>
-        <v>831.602495708419</v>
+        <v>820.688525275366</v>
       </c>
     </row>
     <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60751,15 +60751,15 @@
       </c>
       <c r="E631" s="18" t="n">
         <f aca="false">E630/shares</f>
-        <v>7.15664579297517</v>
+        <v>7.04328105358273</v>
       </c>
       <c r="F631" s="18" t="n">
         <f aca="false">F630/shares</f>
-        <v>9.55392285111322</v>
+        <v>9.42611484272663</v>
       </c>
       <c r="G631" s="18" t="n">
         <f aca="false">G630/shares</f>
-        <v>10.3174563366809</v>
+        <v>10.1820498005246</v>
       </c>
     </row>
     <row r="632" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61368,15 +61368,15 @@
       </c>
       <c r="E667" s="16" t="n">
         <f aca="false">D667*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F667" s="16" t="n">
         <f aca="false">E667*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G667" s="16" t="n">
         <f aca="false">F667*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I667" s="8" t="s">
         <v>526</v>
@@ -61399,15 +61399,15 @@
       </c>
       <c r="E668" s="16" t="n">
         <f aca="false">E666+E667</f>
-        <v>1391.61489698153</v>
+        <v>1371.96313228618</v>
       </c>
       <c r="F668" s="16" t="n">
         <f aca="false">F666+F667</f>
-        <v>1738.19003614323</v>
+        <v>1716.03453240851</v>
       </c>
       <c r="G668" s="16" t="n">
         <f aca="false">G666+G667</f>
-        <v>1857.07384838491</v>
+        <v>1833.6011407245</v>
       </c>
     </row>
     <row r="669" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61427,15 +61427,15 @@
       </c>
       <c r="E669" s="10" t="n">
         <f aca="false">E666/E668</f>
-        <v>0.338790531141222</v>
+        <v>0.343643308626508</v>
       </c>
       <c r="F669" s="10" t="n">
         <f aca="false">F666/F668</f>
-        <v>0.403183322373738</v>
+        <v>0.408388771003079</v>
       </c>
       <c r="G669" s="10" t="n">
         <f aca="false">G666/G668</f>
-        <v>0.408178697167995</v>
+        <v>0.413403966185904</v>
       </c>
     </row>
     <row r="670" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61455,15 +61455,15 @@
       </c>
       <c r="E670" s="10" t="n">
         <f aca="false">$D670+gm_prem*(E669-$D669)+0</f>
-        <v>0.653744616293215</v>
+        <v>0.654132838492038</v>
       </c>
       <c r="F670" s="10" t="n">
         <f aca="false">$D670+gm_prem*(F669-$D669)+0</f>
-        <v>0.658896039591816</v>
+        <v>0.659312475482163</v>
       </c>
       <c r="G670" s="10" t="n">
         <f aca="false">$D670+gm_prem*(G669-$D669)+0</f>
-        <v>0.659295669575357</v>
+        <v>0.659713691096789</v>
       </c>
       <c r="I670" s="8" t="s">
         <v>528</v>
@@ -61486,15 +61486,15 @@
       </c>
       <c r="E671" s="16" t="n">
         <f aca="false">E668*E670</f>
-        <v>909.760746855111</v>
+        <v>897.446138028784</v>
       </c>
       <c r="F671" s="16" t="n">
         <f aca="false">F668*F670</f>
-        <v>1145.28653087273</v>
+        <v>1131.40297557513</v>
       </c>
       <c r="G671" s="16" t="n">
         <f aca="false">G668*G670</f>
-        <v>1224.36074632181</v>
+        <v>1209.65177654664</v>
       </c>
     </row>
     <row r="672" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61514,15 +61514,15 @@
       </c>
       <c r="E672" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E668</f>
-        <v>257.886892572177</v>
+        <v>256.135715501136</v>
       </c>
       <c r="F672" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F668</f>
-        <v>288.770349935994</v>
+        <v>286.796063619266</v>
       </c>
       <c r="G672" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G668</f>
-        <v>299.364136771064</v>
+        <v>297.272473854916</v>
       </c>
       <c r="I672" s="5" t="s">
         <v>530</v>
@@ -61545,15 +61545,15 @@
       </c>
       <c r="E673" s="16" t="n">
         <f aca="false">E671-E672</f>
-        <v>651.873854282934</v>
+        <v>641.310422527647</v>
       </c>
       <c r="F673" s="16" t="n">
         <f aca="false">F671-F672</f>
-        <v>856.516180936734</v>
+        <v>844.606911955863</v>
       </c>
       <c r="G673" s="16" t="n">
         <f aca="false">G671-G672</f>
-        <v>924.996609550746</v>
+        <v>912.379302691725</v>
       </c>
     </row>
     <row r="674" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61573,15 +61573,15 @@
       </c>
       <c r="E674" s="10" t="n">
         <f aca="false">E673/E668</f>
-        <v>0.468429775864627</v>
+        <v>0.467439982486262</v>
       </c>
       <c r="F674" s="10" t="n">
         <f aca="false">F673/F668</f>
-        <v>0.492763255528268</v>
+        <v>0.492185265508866</v>
       </c>
       <c r="G674" s="10" t="n">
         <f aca="false">G673/G668</f>
-        <v>0.498093605892525</v>
+        <v>0.497588751679781</v>
       </c>
     </row>
     <row r="675" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61601,15 +61601,15 @@
       </c>
       <c r="E675" s="16" t="n">
         <f aca="false">(E673-fin)*(1-tax)</f>
-        <v>546.570883954738</v>
+        <v>537.433515486415</v>
       </c>
       <c r="F675" s="16" t="n">
         <f aca="false">(F673-fin)*(1-tax)</f>
-        <v>723.586496510275</v>
+        <v>713.284978841821</v>
       </c>
       <c r="G675" s="16" t="n">
         <f aca="false">(G673-fin)*(1-tax)</f>
-        <v>782.822067261395</v>
+        <v>771.908096828342</v>
       </c>
     </row>
     <row r="676" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61629,15 +61629,15 @@
       </c>
       <c r="E676" s="18" t="n">
         <f aca="false">E675/shares</f>
-        <v>6.78114995951307</v>
+        <v>6.66778522012063</v>
       </c>
       <c r="F676" s="18" t="n">
         <f aca="false">F675/shares</f>
-        <v>8.97733246603233</v>
+        <v>8.84952445764573</v>
       </c>
       <c r="G676" s="18" t="n">
         <f aca="false">G675/shares</f>
-        <v>9.71225139419455</v>
+        <v>9.5768448580382</v>
       </c>
     </row>
     <row r="677" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62246,15 +62246,15 @@
       </c>
       <c r="E712" s="16" t="n">
         <f aca="false">D712*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F712" s="16" t="n">
         <f aca="false">E712*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G712" s="16" t="n">
         <f aca="false">F712*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I712" s="8" t="s">
         <v>526</v>
@@ -62277,15 +62277,15 @@
       </c>
       <c r="E713" s="16" t="n">
         <f aca="false">E711+E712</f>
-        <v>1450.032811632</v>
+        <v>1430.38104693665</v>
       </c>
       <c r="F713" s="16" t="n">
         <f aca="false">F711+F712</f>
-        <v>1821.9538778077</v>
+        <v>1799.79837407298</v>
       </c>
       <c r="G713" s="16" t="n">
         <f aca="false">G711+G712</f>
-        <v>1942.85437793201</v>
+        <v>1919.3816702716</v>
       </c>
     </row>
     <row r="714" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62305,15 +62305,15 @@
       </c>
       <c r="E714" s="10" t="n">
         <f aca="false">E711/E713</f>
-        <v>0.365428878913784</v>
+        <v>0.370449444836885</v>
       </c>
       <c r="F714" s="10" t="n">
         <f aca="false">F711/F713</f>
-        <v>0.430621809316973</v>
+        <v>0.435922760380166</v>
       </c>
       <c r="G714" s="10" t="n">
         <f aca="false">G711/G713</f>
-        <v>0.434308676507066</v>
+        <v>0.439619970636798</v>
       </c>
     </row>
     <row r="715" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62333,15 +62333,15 @@
       </c>
       <c r="E715" s="10" t="n">
         <f aca="false">$D715+gm_prem*(E714-$D714)+0</f>
-        <v>0.65587568411502</v>
+        <v>0.656277329388868</v>
       </c>
       <c r="F715" s="10" t="n">
         <f aca="false">$D715+gm_prem*(F714-$D714)+0</f>
-        <v>0.661091118547275</v>
+        <v>0.66151519463233</v>
       </c>
       <c r="G715" s="10" t="n">
         <f aca="false">$D715+gm_prem*(G714-$D714)+0</f>
-        <v>0.661386067922482</v>
+        <v>0.661810971452861</v>
       </c>
       <c r="I715" s="8" t="s">
         <v>528</v>
@@ -62364,15 +62364,15 @@
       </c>
       <c r="E716" s="16" t="n">
         <f aca="false">E713*E715</f>
-        <v>951.041262318366</v>
+        <v>938.726653492039</v>
       </c>
       <c r="F716" s="16" t="n">
         <f aca="false">F713*F715</f>
-        <v>1204.47752702144</v>
+        <v>1190.59397172384</v>
       </c>
       <c r="G716" s="16" t="n">
         <f aca="false">G713*G715</f>
-        <v>1284.97681756643</v>
+        <v>1270.26784779126</v>
       </c>
     </row>
     <row r="717" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62392,15 +62392,15 @@
       </c>
       <c r="E717" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E713</f>
-        <v>263.092537676309</v>
+        <v>261.341360605269</v>
       </c>
       <c r="F717" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F713</f>
-        <v>296.23458132585</v>
+        <v>294.260295009121</v>
       </c>
       <c r="G717" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G713</f>
-        <v>307.008076071851</v>
+        <v>304.916413155702</v>
       </c>
       <c r="I717" s="5" t="s">
         <v>530</v>
@@ -62423,15 +62423,15 @@
       </c>
       <c r="E718" s="16" t="n">
         <f aca="false">E716-E717</f>
-        <v>687.948724642057</v>
+        <v>677.385292886771</v>
       </c>
       <c r="F718" s="16" t="n">
         <f aca="false">F716-F717</f>
-        <v>908.242945695589</v>
+        <v>896.333676714718</v>
       </c>
       <c r="G718" s="16" t="n">
         <f aca="false">G716-G717</f>
-        <v>977.968741494582</v>
+        <v>965.351434635561</v>
       </c>
     </row>
     <row r="719" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62451,15 +62451,15 @@
       </c>
       <c r="E719" s="10" t="n">
         <f aca="false">E718/E713</f>
-        <v>0.474436660414446</v>
+        <v>0.473569818572107</v>
       </c>
       <c r="F719" s="10" t="n">
         <f aca="false">F718/F713</f>
-        <v>0.498499416894377</v>
+        <v>0.498018939024985</v>
       </c>
       <c r="G719" s="10" t="n">
         <f aca="false">G718/G713</f>
-        <v>0.503366980357807</v>
+        <v>0.502949178679486</v>
       </c>
     </row>
     <row r="720" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62479,15 +62479,15 @@
       </c>
       <c r="E720" s="16" t="n">
         <f aca="false">(E718-fin)*(1-tax)</f>
-        <v>577.775646815379</v>
+        <v>568.638278347057</v>
       </c>
       <c r="F720" s="16" t="n">
         <f aca="false">(F718-fin)*(1-tax)</f>
-        <v>768.330148026685</v>
+        <v>758.028630358231</v>
       </c>
       <c r="G720" s="16" t="n">
         <f aca="false">(G718-fin)*(1-tax)</f>
-        <v>828.642961392813</v>
+        <v>817.728990959761</v>
       </c>
     </row>
     <row r="721" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62507,15 +62507,15 @@
       </c>
       <c r="E721" s="18" t="n">
         <f aca="false">E720/shares</f>
-        <v>7.1682986032132</v>
+        <v>7.05493386382076</v>
       </c>
       <c r="F721" s="18" t="n">
         <f aca="false">F720/shares</f>
-        <v>9.53245426189823</v>
+        <v>9.40464625351163</v>
       </c>
       <c r="G721" s="18" t="n">
         <f aca="false">G720/shares</f>
-        <v>10.2807382336981</v>
+        <v>10.1453316975418</v>
       </c>
     </row>
     <row r="722" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63124,15 +63124,15 @@
       </c>
       <c r="E757" s="16" t="n">
         <f aca="false">D757*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F757" s="16" t="n">
         <f aca="false">E757*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G757" s="16" t="n">
         <f aca="false">F757*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I757" s="8" t="s">
         <v>526</v>
@@ -63155,15 +63155,15 @@
       </c>
       <c r="E758" s="16" t="n">
         <f aca="false">E756+E757</f>
-        <v>1424.7030909327</v>
+        <v>1405.05132623735</v>
       </c>
       <c r="F758" s="16" t="n">
         <f aca="false">F756+F757</f>
-        <v>1793.02375412174</v>
+        <v>1770.86825038702</v>
       </c>
       <c r="G758" s="16" t="n">
         <f aca="false">G756+G757</f>
-        <v>1941.31756554069</v>
+        <v>1917.84485788029</v>
       </c>
     </row>
     <row r="759" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63183,15 +63183,15 @@
       </c>
       <c r="E759" s="10" t="n">
         <f aca="false">E756/E758</f>
-        <v>0.354146872604361</v>
+        <v>0.35910015144767</v>
       </c>
       <c r="F759" s="10" t="n">
         <f aca="false">F756/F758</f>
-        <v>0.421434992107952</v>
+        <v>0.42670760600204</v>
       </c>
       <c r="G759" s="10" t="n">
         <f aca="false">G756/G758</f>
-        <v>0.433860856196244</v>
+        <v>0.439170925465374</v>
       </c>
     </row>
     <row r="760" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63211,15 +63211,15 @@
       </c>
       <c r="E760" s="10" t="n">
         <f aca="false">$D760+gm_prem*(E759-$D759)+0</f>
-        <v>0.654973123610266</v>
+        <v>0.655369385917731</v>
       </c>
       <c r="F760" s="10" t="n">
         <f aca="false">$D760+gm_prem*(F759-$D759)+0</f>
-        <v>0.660356173170553</v>
+        <v>0.66077798228208</v>
       </c>
       <c r="G760" s="10" t="n">
         <f aca="false">$D760+gm_prem*(G759-$D759)+0</f>
-        <v>0.661350242297616</v>
+        <v>0.661775047839147</v>
       </c>
       <c r="I760" s="8" t="s">
         <v>528</v>
@@ -63242,15 +63242,15 @@
       </c>
       <c r="E761" s="16" t="n">
         <f aca="false">E758*E760</f>
-        <v>933.142233685392</v>
+        <v>920.827624859065</v>
       </c>
       <c r="F761" s="16" t="n">
         <f aca="false">F758*F760</f>
-        <v>1184.03430467573</v>
+        <v>1170.15074937813</v>
       </c>
       <c r="G761" s="16" t="n">
         <f aca="false">G758*G760</f>
-        <v>1283.89084234696</v>
+        <v>1269.18187257179</v>
       </c>
     </row>
     <row r="762" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63270,15 +63270,15 @@
       </c>
       <c r="E762" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E758</f>
-        <v>260.835395542149</v>
+        <v>259.084218471109</v>
       </c>
       <c r="F762" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F758</f>
-        <v>293.656605757416</v>
+        <v>291.682319440688</v>
       </c>
       <c r="G762" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G758</f>
-        <v>306.871130069093</v>
+        <v>304.779467152945</v>
       </c>
       <c r="I762" s="5" t="s">
         <v>530</v>
@@ -63301,15 +63301,15 @@
       </c>
       <c r="E763" s="16" t="n">
         <f aca="false">E761-E762</f>
-        <v>672.306838143243</v>
+        <v>661.743406387957</v>
       </c>
       <c r="F763" s="16" t="n">
         <f aca="false">F761-F762</f>
-        <v>890.377698918315</v>
+        <v>878.468429937443</v>
       </c>
       <c r="G763" s="16" t="n">
         <f aca="false">G761-G762</f>
-        <v>977.019712277864</v>
+        <v>964.402405418844</v>
       </c>
     </row>
     <row r="764" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63329,15 +63329,15 @@
       </c>
       <c r="E764" s="10" t="n">
         <f aca="false">E763/E758</f>
-        <v>0.471892594619913</v>
+        <v>0.470974543086671</v>
       </c>
       <c r="F764" s="10" t="n">
         <f aca="false">F763/F758</f>
-        <v>0.49657886398412</v>
+        <v>0.496066508474279</v>
       </c>
       <c r="G764" s="10" t="n">
         <f aca="false">G763/G758</f>
-        <v>0.503276604312672</v>
+        <v>0.502857361718381</v>
       </c>
     </row>
     <row r="765" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63357,15 +63357,15 @@
       </c>
       <c r="E765" s="16" t="n">
         <f aca="false">(E763-fin)*(1-tax)</f>
-        <v>564.245414993905</v>
+        <v>555.108046525583</v>
       </c>
       <c r="F765" s="16" t="n">
         <f aca="false">(F763-fin)*(1-tax)</f>
-        <v>752.876709564342</v>
+        <v>742.575191895888</v>
       </c>
       <c r="G765" s="16" t="n">
         <f aca="false">(G763-fin)*(1-tax)</f>
-        <v>827.822051120352</v>
+        <v>816.9080806873</v>
       </c>
     </row>
     <row r="766" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63385,15 +63385,15 @@
       </c>
       <c r="E766" s="18" t="n">
         <f aca="false">E765/shares</f>
-        <v>7.00043285393558</v>
+        <v>6.88706811454314</v>
       </c>
       <c r="F766" s="18" t="n">
         <f aca="false">F765/shares</f>
-        <v>9.34072783321432</v>
+        <v>9.21291982482772</v>
       </c>
       <c r="G766" s="18" t="n">
         <f aca="false">G765/shares</f>
-        <v>10.2705534327432</v>
+        <v>10.1351468965868</v>
       </c>
     </row>
     <row r="767" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64002,15 +64002,15 @@
       </c>
       <c r="E802" s="16" t="n">
         <f aca="false">D802*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F802" s="16" t="n">
         <f aca="false">E802*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G802" s="16" t="n">
         <f aca="false">F802*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I802" s="8" t="s">
         <v>526</v>
@@ -64033,15 +64033,15 @@
       </c>
       <c r="E803" s="16" t="n">
         <f aca="false">E801+E802</f>
-        <v>1427.82684110013</v>
+        <v>1408.17507640478</v>
       </c>
       <c r="F803" s="16" t="n">
         <f aca="false">F801+F802</f>
-        <v>1770.59327443953</v>
+        <v>1748.43777070481</v>
       </c>
       <c r="G803" s="16" t="n">
         <f aca="false">G801+G802</f>
-        <v>1868.67028891761</v>
+        <v>1845.1975812572</v>
       </c>
     </row>
     <row r="804" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64061,15 +64061,15 @@
       </c>
       <c r="E804" s="10" t="n">
         <f aca="false">E801/E803</f>
-        <v>0.355559847733252</v>
+        <v>0.360521857486051</v>
       </c>
       <c r="F804" s="10" t="n">
         <f aca="false">F801/F803</f>
-        <v>0.414105533196239</v>
+        <v>0.41935291279477</v>
       </c>
       <c r="G804" s="10" t="n">
         <f aca="false">G801/G803</f>
-        <v>0.411851373179907</v>
+        <v>0.417090523166004</v>
       </c>
     </row>
     <row r="805" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64089,15 +64089,15 @@
       </c>
       <c r="E805" s="10" t="n">
         <f aca="false">$D805+gm_prem*(E804-$D804)+0</f>
-        <v>0.655086161620577</v>
+        <v>0.655483122400801</v>
       </c>
       <c r="F805" s="10" t="n">
         <f aca="false">$D805+gm_prem*(F804-$D804)+0</f>
-        <v>0.659769816457616</v>
+        <v>0.660189606825499</v>
       </c>
       <c r="G805" s="10" t="n">
         <f aca="false">$D805+gm_prem*(G804-$D804)+0</f>
-        <v>0.659589483656309</v>
+        <v>0.660008615655197</v>
       </c>
       <c r="I805" s="8" t="s">
         <v>528</v>
@@ -64120,15 +64120,15 @@
       </c>
       <c r="E806" s="16" t="n">
         <f aca="false">E803*E805</f>
-        <v>935.349604795119</v>
+        <v>923.034995968792</v>
       </c>
       <c r="F806" s="16" t="n">
         <f aca="false">F803*F805</f>
-        <v>1168.18399969806</v>
+        <v>1154.30044440046</v>
       </c>
       <c r="G806" s="16" t="n">
         <f aca="false">G803*G805</f>
-        <v>1232.55527099105</v>
+        <v>1217.84630121589</v>
       </c>
     </row>
     <row r="807" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64148,15 +64148,15 @@
       </c>
       <c r="E807" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E803</f>
-        <v>261.113754241923</v>
+        <v>259.362577170883</v>
       </c>
       <c r="F807" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F803</f>
-        <v>291.657816217603</v>
+        <v>289.683529900875</v>
       </c>
       <c r="G807" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G803</f>
-        <v>300.39750049597</v>
+        <v>298.305837579822</v>
       </c>
       <c r="I807" s="5" t="s">
         <v>530</v>
@@ -64179,15 +64179,15 @@
       </c>
       <c r="E808" s="16" t="n">
         <f aca="false">E806-E807</f>
-        <v>674.235850553196</v>
+        <v>663.672418797909</v>
       </c>
       <c r="F808" s="16" t="n">
         <f aca="false">F806-F807</f>
-        <v>876.526183480455</v>
+        <v>864.616914499583</v>
       </c>
       <c r="G808" s="16" t="n">
         <f aca="false">G806-G807</f>
-        <v>932.157770495084</v>
+        <v>919.540463636064</v>
       </c>
     </row>
     <row r="809" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64207,15 +64207,15 @@
       </c>
       <c r="E809" s="10" t="n">
         <f aca="false">E808/E803</f>
-        <v>0.472211217176518</v>
+        <v>0.471299648685968</v>
       </c>
       <c r="F809" s="10" t="n">
         <f aca="false">F808/F803</f>
-        <v>0.495046601686609</v>
+        <v>0.494508257020237</v>
       </c>
       <c r="G809" s="10" t="n">
         <f aca="false">G808/G803</f>
-        <v>0.498834800351547</v>
+        <v>0.4983425476905</v>
       </c>
     </row>
     <row r="810" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64235,15 +64235,15 @@
       </c>
       <c r="E810" s="16" t="n">
         <f aca="false">(E808-fin)*(1-tax)</f>
-        <v>565.914010728514</v>
+        <v>556.776642260192</v>
       </c>
       <c r="F810" s="16" t="n">
         <f aca="false">(F808-fin)*(1-tax)</f>
-        <v>740.895148710593</v>
+        <v>730.59363104214</v>
       </c>
       <c r="G810" s="16" t="n">
         <f aca="false">(G808-fin)*(1-tax)</f>
-        <v>789.016471478248</v>
+        <v>778.102501045195</v>
       </c>
     </row>
     <row r="811" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64263,15 +64263,15 @@
       </c>
       <c r="E811" s="18" t="n">
         <f aca="false">E810/shares</f>
-        <v>7.02113464803101</v>
+        <v>6.90776990863857</v>
       </c>
       <c r="F811" s="18" t="n">
         <f aca="false">F810/shares</f>
-        <v>9.19207600545792</v>
+        <v>9.06426799707132</v>
       </c>
       <c r="G811" s="18" t="n">
         <f aca="false">G810/shares</f>
-        <v>9.78910361069095</v>
+        <v>9.6536970745346</v>
       </c>
     </row>
     <row r="812" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64880,15 +64880,15 @@
       </c>
       <c r="E847" s="16" t="n">
         <f aca="false">D847*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F847" s="16" t="n">
         <f aca="false">E847*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G847" s="16" t="n">
         <f aca="false">F847*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I847" s="8" t="s">
         <v>526</v>
@@ -64911,15 +64911,15 @@
       </c>
       <c r="E848" s="16" t="n">
         <f aca="false">E846+E847</f>
-        <v>1442.70695079077</v>
+        <v>1423.05518609542</v>
       </c>
       <c r="F848" s="16" t="n">
         <f aca="false">F846+F847</f>
-        <v>1823.70740444445</v>
+        <v>1801.55190070972</v>
       </c>
       <c r="G848" s="16" t="n">
         <f aca="false">G846+G847</f>
-        <v>1982.92438529168</v>
+        <v>1959.45167763127</v>
       </c>
     </row>
     <row r="849" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64939,15 +64939,15 @@
       </c>
       <c r="E849" s="10" t="n">
         <f aca="false">E846/E848</f>
-        <v>0.362206616953797</v>
+        <v>0.367208530637135</v>
       </c>
       <c r="F849" s="10" t="n">
         <f aca="false">F846/F848</f>
-        <v>0.431169276427821</v>
+        <v>0.436471800607353</v>
       </c>
       <c r="G849" s="10" t="n">
         <f aca="false">G846/G848</f>
-        <v>0.445739901854737</v>
+        <v>0.451079519324387</v>
       </c>
     </row>
     <row r="850" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64967,15 +64967,15 @@
       </c>
       <c r="E850" s="10" t="n">
         <f aca="false">$D850+gm_prem*(E849-$D849)+0</f>
-        <v>0.655617903158221</v>
+        <v>0.656018056252888</v>
       </c>
       <c r="F850" s="10" t="n">
         <f aca="false">$D850+gm_prem*(F849-$D849)+0</f>
-        <v>0.661134915916143</v>
+        <v>0.661559117850505</v>
       </c>
       <c r="G850" s="10" t="n">
         <f aca="false">$D850+gm_prem*(G849-$D849)+0</f>
-        <v>0.662300565950296</v>
+        <v>0.662727735347868</v>
       </c>
       <c r="I850" s="8" t="s">
         <v>528</v>
@@ -64998,15 +64998,15 @@
       </c>
       <c r="E851" s="16" t="n">
         <f aca="false">E848*E850</f>
-        <v>945.864505949237</v>
+        <v>933.54989712291</v>
       </c>
       <c r="F851" s="16" t="n">
         <f aca="false">F848*F850</f>
-        <v>1205.71664149303</v>
+        <v>1191.83308619543</v>
       </c>
       <c r="G851" s="16" t="n">
         <f aca="false">G848*G850</f>
-        <v>1313.29194261532</v>
+        <v>1298.58297284015</v>
       </c>
     </row>
     <row r="852" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65026,15 +65026,15 @@
       </c>
       <c r="E852" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E848</f>
-        <v>262.439727115544</v>
+        <v>260.688550044504</v>
       </c>
       <c r="F852" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F848</f>
-        <v>296.390838826757</v>
+        <v>294.416552510029</v>
       </c>
       <c r="G852" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G848</f>
-        <v>310.578731390214</v>
+        <v>308.487068474065</v>
       </c>
       <c r="I852" s="5" t="s">
         <v>530</v>
@@ -65057,15 +65057,15 @@
       </c>
       <c r="E853" s="16" t="n">
         <f aca="false">E851-E852</f>
-        <v>683.424778833693</v>
+        <v>672.861347078406</v>
       </c>
       <c r="F853" s="16" t="n">
         <f aca="false">F851-F852</f>
-        <v>909.325802666268</v>
+        <v>897.416533685397</v>
       </c>
       <c r="G853" s="16" t="n">
         <f aca="false">G851-G852</f>
-        <v>1002.71321122511</v>
+        <v>990.095904366086</v>
       </c>
     </row>
     <row r="854" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65085,15 +65085,15 @@
       </c>
       <c r="E854" s="10" t="n">
         <f aca="false">E853/E848</f>
-        <v>0.47371004794778</v>
+        <v>0.472828709422439</v>
       </c>
       <c r="F854" s="10" t="n">
         <f aca="false">F853/F848</f>
-        <v>0.498613867800397</v>
+        <v>0.498135265118845</v>
       </c>
       <c r="G854" s="10" t="n">
         <f aca="false">G853/G848</f>
-        <v>0.505673952402181</v>
+        <v>0.505292330333447</v>
       </c>
     </row>
     <row r="855" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65113,15 +65113,15 @@
       </c>
       <c r="E855" s="16" t="n">
         <f aca="false">(E853-fin)*(1-tax)</f>
-        <v>573.862433691144</v>
+        <v>564.725065222821</v>
       </c>
       <c r="F855" s="16" t="n">
         <f aca="false">(F853-fin)*(1-tax)</f>
-        <v>769.266819306322</v>
+        <v>758.965301637868</v>
       </c>
       <c r="G855" s="16" t="n">
         <f aca="false">(G853-fin)*(1-tax)</f>
-        <v>850.046927709717</v>
+        <v>839.132957276665</v>
       </c>
     </row>
     <row r="856" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65141,15 +65141,15 @@
       </c>
       <c r="E856" s="18" t="n">
         <f aca="false">E855/shares</f>
-        <v>7.11974847769797</v>
+        <v>7.00638373830553</v>
       </c>
       <c r="F856" s="18" t="n">
         <f aca="false">F855/shares</f>
-        <v>9.54407527684149</v>
+        <v>9.41626726845489</v>
       </c>
       <c r="G856" s="18" t="n">
         <f aca="false">G855/shares</f>
-        <v>10.5462911740105</v>
+        <v>10.4108846378541</v>
       </c>
     </row>
     <row r="857" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65758,15 +65758,15 @@
       </c>
       <c r="E892" s="16" t="n">
         <f aca="false">D892*(1+el_lo*eqgA_27)</f>
-        <v>835.67447344456</v>
+        <v>825.848591096884</v>
       </c>
       <c r="F892" s="16" t="n">
         <f aca="false">E892*(1+el_lo*eqgA_28)</f>
-        <v>888.909153276225</v>
+        <v>878.457336168706</v>
       </c>
       <c r="G892" s="16" t="n">
         <f aca="false">F892*(1+el_lo*eqgA_29)</f>
-        <v>915.333166024778</v>
+        <v>904.570654683235</v>
       </c>
       <c r="I892" s="8" t="s">
         <v>526</v>
@@ -65789,15 +65789,15 @@
       </c>
       <c r="E893" s="16" t="n">
         <f aca="false">E891+E892</f>
-        <v>1350.97655956445</v>
+        <v>1341.15067721677</v>
       </c>
       <c r="F893" s="16" t="n">
         <f aca="false">F891+F892</f>
-        <v>1649.31487358448</v>
+        <v>1638.86305647696</v>
       </c>
       <c r="G893" s="16" t="n">
         <f aca="false">G891+G892</f>
-        <v>1743.38176284741</v>
+        <v>1732.61925150587</v>
       </c>
     </row>
     <row r="894" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65817,15 +65817,15 @@
       </c>
       <c r="E894" s="10" t="n">
         <f aca="false">E891/E893</f>
-        <v>0.381429331598485</v>
+        <v>0.384223857075679</v>
       </c>
       <c r="F894" s="10" t="n">
         <f aca="false">F891/F893</f>
-        <v>0.46104338988689</v>
+        <v>0.463983685093792</v>
       </c>
       <c r="G894" s="10" t="n">
         <f aca="false">G891/G893</f>
-        <v>0.474966880157223</v>
+        <v>0.477917232019069</v>
       </c>
     </row>
     <row r="895" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65845,15 +65845,15 @@
       </c>
       <c r="E895" s="10" t="n">
         <f aca="false">$D895+gm_prem*(E894-$D894)+0</f>
-        <v>0.657155720329796</v>
+        <v>0.657379282367971</v>
       </c>
       <c r="F895" s="10" t="n">
         <f aca="false">$D895+gm_prem*(F894-$D894)+0</f>
-        <v>0.663524844992868</v>
+        <v>0.66376006860942</v>
       </c>
       <c r="G895" s="10" t="n">
         <f aca="false">$D895+gm_prem*(G894-$D894)+0</f>
-        <v>0.664638724214495</v>
+        <v>0.664874752363442</v>
       </c>
       <c r="I895" s="8" t="s">
         <v>528</v>
@@ -65876,15 +65876,15 @@
       </c>
       <c r="E896" s="16" t="n">
         <f aca="false">E893*E895</f>
-        <v>887.801974149243</v>
+        <v>881.64466973608</v>
       </c>
       <c r="F896" s="16" t="n">
         <f aca="false">F893*F895</f>
-        <v>1094.36139583957</v>
+        <v>1087.81185480859</v>
       </c>
       <c r="G896" s="16" t="n">
         <f aca="false">G893*G895</f>
-        <v>1158.71903067772</v>
+        <v>1151.9747957851</v>
       </c>
     </row>
     <row r="897" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65904,15 +65904,15 @@
       </c>
       <c r="E897" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E893</f>
-        <v>254.265593121811</v>
+        <v>253.39000458629</v>
       </c>
       <c r="F897" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F893</f>
-        <v>280.850646577512</v>
+        <v>279.91928073057</v>
       </c>
       <c r="G897" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G893</f>
-        <v>289.23298690038</v>
+        <v>288.27393495872</v>
       </c>
       <c r="I897" s="5" t="s">
         <v>530</v>
@@ -65935,15 +65935,15 @@
       </c>
       <c r="E898" s="16" t="n">
         <f aca="false">E896-E897</f>
-        <v>633.536381027432</v>
+        <v>628.254665149789</v>
       </c>
       <c r="F898" s="16" t="n">
         <f aca="false">F896-F897</f>
-        <v>813.510749262063</v>
+        <v>807.892574078023</v>
       </c>
       <c r="G898" s="16" t="n">
         <f aca="false">G896-G897</f>
-        <v>869.486043777343</v>
+        <v>863.70086082638</v>
       </c>
     </row>
     <row r="899" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65963,15 +65963,15 @@
       </c>
       <c r="E899" s="10" t="n">
         <f aca="false">E898/E893</f>
-        <v>0.468946982493674</v>
+        <v>0.46844450502279</v>
       </c>
       <c r="F899" s="10" t="n">
         <f aca="false">F898/F893</f>
-        <v>0.493241625532696</v>
+        <v>0.492959171228581</v>
       </c>
       <c r="G899" s="10" t="n">
         <f aca="false">G898/G893</f>
-        <v>0.498735309905523</v>
+        <v>0.498494323017426</v>
       </c>
     </row>
     <row r="900" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65991,15 +65991,15 @@
       </c>
       <c r="E900" s="16" t="n">
         <f aca="false">(E898-fin)*(1-tax)</f>
-        <v>530.708969588729</v>
+        <v>526.140285354568</v>
       </c>
       <c r="F900" s="16" t="n">
         <f aca="false">(F898-fin)*(1-tax)</f>
-        <v>686.386798111684</v>
+        <v>681.52707657749</v>
       </c>
       <c r="G900" s="16" t="n">
         <f aca="false">(G898-fin)*(1-tax)</f>
-        <v>734.805427867402</v>
+        <v>729.801244614818</v>
       </c>
     </row>
     <row r="901" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66019,15 +66019,15 @@
       </c>
       <c r="E901" s="18" t="n">
         <f aca="false">E900/shares</f>
-        <v>6.58435568612882</v>
+        <v>6.5276733164326</v>
       </c>
       <c r="F901" s="18" t="n">
         <f aca="false">F900/shares</f>
-        <v>8.51580635716922</v>
+        <v>8.45551317022446</v>
       </c>
       <c r="G901" s="18" t="n">
         <f aca="false">G900/shares</f>
-        <v>9.1165225658922</v>
+        <v>9.05443708337415</v>
       </c>
     </row>
     <row r="902" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66636,15 +66636,15 @@
       </c>
       <c r="E937" s="16" t="n">
         <f aca="false">D937*(1+el_hi*eqgA_27)</f>
-        <v>1004.62342033368</v>
+        <v>975.145773290652</v>
       </c>
       <c r="F937" s="16" t="n">
         <f aca="false">E937*(1+el_hi*eqgA_28)</f>
-        <v>1196.61494753355</v>
+        <v>1161.50388765194</v>
       </c>
       <c r="G937" s="16" t="n">
         <f aca="false">F937*(1+el_hi*eqgA_29)</f>
-        <v>1303.32788387422</v>
+        <v>1265.08565443324</v>
       </c>
       <c r="I937" s="8" t="s">
         <v>526</v>
@@ -66667,15 +66667,15 @@
       </c>
       <c r="E938" s="16" t="n">
         <f aca="false">E936+E937</f>
-        <v>1519.92550645357</v>
+        <v>1490.44785941054</v>
       </c>
       <c r="F938" s="16" t="n">
         <f aca="false">F936+F937</f>
-        <v>1957.0206678418</v>
+        <v>1921.90960796019</v>
       </c>
       <c r="G938" s="16" t="n">
         <f aca="false">G936+G937</f>
-        <v>2131.37648069686</v>
+        <v>2093.13425125588</v>
       </c>
     </row>
     <row r="939" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66695,15 +66695,15 @@
       </c>
       <c r="E939" s="10" t="n">
         <f aca="false">E936/E938</f>
-        <v>0.339031145889668</v>
+        <v>0.345736405917403</v>
       </c>
       <c r="F939" s="10" t="n">
         <f aca="false">F936/F938</f>
-        <v>0.388552728544676</v>
+        <v>0.395651136327534</v>
       </c>
       <c r="G939" s="10" t="n">
         <f aca="false">G936/G938</f>
-        <v>0.388504144773102</v>
+        <v>0.395602239238027</v>
       </c>
     </row>
     <row r="940" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66723,15 +66723,15 @@
       </c>
       <c r="E940" s="10" t="n">
         <f aca="false">$D940+gm_prem*(E939-$D939)+0</f>
-        <v>0.65376386547309</v>
+        <v>0.654300286275309</v>
       </c>
       <c r="F940" s="10" t="n">
         <f aca="false">$D940+gm_prem*(F939-$D939)+0</f>
-        <v>0.657725592085491</v>
+        <v>0.65829346470812</v>
       </c>
       <c r="G940" s="10" t="n">
         <f aca="false">$D940+gm_prem*(G939-$D939)+0</f>
-        <v>0.657721705383765</v>
+        <v>0.658289552940959</v>
       </c>
       <c r="I940" s="8" t="s">
         <v>528</v>
@@ -66754,15 +66754,15 @@
       </c>
       <c r="E941" s="16" t="n">
         <f aca="false">E938*E940</f>
-        <v>993.672374330228</v>
+        <v>975.200461090737</v>
       </c>
       <c r="F941" s="16" t="n">
         <f aca="false">F938*F940</f>
-        <v>1287.18257747979</v>
+        <v>1265.18053467994</v>
       </c>
       <c r="G941" s="16" t="n">
         <f aca="false">G938*G940</f>
-        <v>1401.85257369878</v>
+        <v>1377.88841050464</v>
       </c>
     </row>
     <row r="942" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66782,15 +66782,15 @@
       </c>
       <c r="E942" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E938</f>
-        <v>269.320705299022</v>
+        <v>266.693939692461</v>
       </c>
       <c r="F942" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F938</f>
-        <v>308.270440162624</v>
+        <v>305.141678753266</v>
       </c>
       <c r="G942" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G938</f>
-        <v>323.807360454909</v>
+        <v>320.39957920062</v>
       </c>
       <c r="I942" s="5" t="s">
         <v>530</v>
@@ -66813,15 +66813,15 @@
       </c>
       <c r="E943" s="16" t="n">
         <f aca="false">E941-E942</f>
-        <v>724.351669031206</v>
+        <v>708.506521398276</v>
       </c>
       <c r="F943" s="16" t="n">
         <f aca="false">F941-F942</f>
-        <v>978.912137317169</v>
+        <v>960.038855926674</v>
       </c>
       <c r="G943" s="16" t="n">
         <f aca="false">G941-G942</f>
-        <v>1078.04521324388</v>
+        <v>1057.48883130402</v>
       </c>
     </row>
     <row r="944" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66841,15 +66841,15 @@
       </c>
       <c r="E944" s="10" t="n">
         <f aca="false">E943/E938</f>
-        <v>0.476570506880519</v>
+        <v>0.475364848843814</v>
       </c>
       <c r="F944" s="10" t="n">
         <f aca="false">F943/F938</f>
-        <v>0.500205313823645</v>
+        <v>0.499523417724939</v>
       </c>
       <c r="G944" s="10" t="n">
         <f aca="false">G943/G938</f>
-        <v>0.505797649081408</v>
+        <v>0.505217871557703</v>
       </c>
     </row>
     <row r="945" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66869,15 +66869,15 @@
       </c>
       <c r="E945" s="16" t="n">
         <f aca="false">(E943-fin)*(1-tax)</f>
-        <v>609.264193711993</v>
+        <v>595.558141009509</v>
       </c>
       <c r="F945" s="16" t="n">
         <f aca="false">(F943-fin)*(1-tax)</f>
-        <v>829.458998779351</v>
+        <v>813.133610376573</v>
       </c>
       <c r="G945" s="16" t="n">
         <f aca="false">(G943-fin)*(1-tax)</f>
-        <v>915.209109455952</v>
+        <v>897.427839077979</v>
       </c>
     </row>
     <row r="946" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -66897,15 +66897,15 @@
       </c>
       <c r="E946" s="18" t="n">
         <f aca="false">E945/shares</f>
-        <v>7.55896807497156</v>
+        <v>7.3889209658829</v>
       </c>
       <c r="F946" s="18" t="n">
         <f aca="false">F945/shares</f>
-        <v>10.2908625781393</v>
+        <v>10.0883181138138</v>
       </c>
       <c r="G946" s="18" t="n">
         <f aca="false">G945/shares</f>
-        <v>11.3547398841084</v>
+        <v>11.1341327049787</v>
       </c>
     </row>
     <row r="947" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67514,15 +67514,15 @@
       </c>
       <c r="E982" s="16" t="n">
         <f aca="false">D982*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F982" s="16" t="n">
         <f aca="false">E982*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G982" s="16" t="n">
         <f aca="false">F982*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I982" s="8" t="s">
         <v>526</v>
@@ -67545,15 +67545,15 @@
       </c>
       <c r="E983" s="16" t="n">
         <f aca="false">E981+E982</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="F983" s="16" t="n">
         <f aca="false">F981+F982</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G983" s="16" t="n">
         <f aca="false">G981+G982</f>
-        <v>1927.10446122904</v>
+        <v>1903.63175356863</v>
       </c>
     </row>
     <row r="984" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67573,15 +67573,15 @@
       </c>
       <c r="E984" s="10" t="n">
         <f aca="false">E981/E983</f>
-        <v>0.358982699005556</v>
+        <v>0.363965498254324</v>
       </c>
       <c r="F984" s="10" t="n">
         <f aca="false">F981/F983</f>
-        <v>0.422967749886054</v>
+        <v>0.428245346110634</v>
       </c>
       <c r="G984" s="10" t="n">
         <f aca="false">G981/G983</f>
-        <v>0.429685371749146</v>
+        <v>0.434983601881163</v>
       </c>
     </row>
     <row r="985" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67632,15 +67632,15 @@
       </c>
       <c r="E986" s="16" t="n">
         <f aca="false">E983*E985</f>
-        <v>928.222028010325</v>
+        <v>915.514383890091</v>
       </c>
       <c r="F986" s="16" t="n">
         <f aca="false">F983*F985</f>
-        <v>1162.5231468816</v>
+        <v>1148.19648150931</v>
       </c>
       <c r="G986" s="16" t="n">
         <f aca="false">G983*G985</f>
-        <v>1246.14547626895</v>
+        <v>1230.96705234057</v>
       </c>
     </row>
     <row r="987" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67660,15 +67660,15 @@
       </c>
       <c r="E987" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E983</f>
-        <v>261.793149210416</v>
+        <v>260.041972139376</v>
       </c>
       <c r="F987" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F983</f>
-        <v>294.081018087167</v>
+        <v>292.106731770439</v>
       </c>
       <c r="G987" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G983</f>
-        <v>305.604594327152</v>
+        <v>303.512931411003</v>
       </c>
       <c r="I987" s="5" t="s">
         <v>530</v>
@@ -67691,15 +67691,15 @@
       </c>
       <c r="E988" s="16" t="n">
         <f aca="false">E986-E987</f>
-        <v>666.428878799909</v>
+        <v>655.472411750715</v>
       </c>
       <c r="F988" s="16" t="n">
         <f aca="false">F986-F987</f>
-        <v>868.442128794438</v>
+        <v>856.089749738872</v>
       </c>
       <c r="G988" s="16" t="n">
         <f aca="false">G986-G987</f>
-        <v>940.540881941796</v>
+        <v>927.454120929567</v>
       </c>
     </row>
     <row r="989" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67719,15 +67719,15 @@
       </c>
       <c r="E989" s="10" t="n">
         <f aca="false">E988/E983</f>
-        <v>0.464264446139228</v>
+        <v>0.462969876041426</v>
       </c>
       <c r="F989" s="10" t="n">
         <f aca="false">F988/F983</f>
-        <v>0.483061875144142</v>
+        <v>0.482132684417562</v>
       </c>
       <c r="G989" s="10" t="n">
         <f aca="false">G988/G983</f>
-        <v>0.488059106739835</v>
+        <v>0.487202485034683</v>
       </c>
     </row>
     <row r="990" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67747,15 +67747,15 @@
       </c>
       <c r="E990" s="16" t="n">
         <f aca="false">(E988-fin)*(1-tax)</f>
-        <v>559.160980161921</v>
+        <v>549.683636164368</v>
       </c>
       <c r="F990" s="16" t="n">
         <f aca="false">(F988-fin)*(1-tax)</f>
-        <v>733.902441407189</v>
+        <v>723.217633524124</v>
       </c>
       <c r="G990" s="16" t="n">
         <f aca="false">(G988-fin)*(1-tax)</f>
-        <v>796.267862879653</v>
+        <v>784.947814604075</v>
       </c>
     </row>
     <row r="991" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -67775,15 +67775,15 @@
       </c>
       <c r="E991" s="18" t="n">
         <f aca="false">E990/shares</f>
-        <v>6.9373517128298</v>
+        <v>6.81976899345718</v>
       </c>
       <c r="F991" s="18" t="n">
         <f aca="false">F990/shares</f>
-        <v>9.10531946895113</v>
+        <v>8.97275608756609</v>
       </c>
       <c r="G991" s="18" t="n">
         <f aca="false">G990/shares</f>
-        <v>9.87906956744346</v>
+        <v>9.73862493865131</v>
       </c>
     </row>
     <row r="992" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68392,15 +68392,15 @@
       </c>
       <c r="E1027" s="16" t="n">
         <f aca="false">D1027*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F1027" s="16" t="n">
         <f aca="false">E1027*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G1027" s="16" t="n">
         <f aca="false">F1027*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I1027" s="8" t="s">
         <v>526</v>
@@ -68423,15 +68423,15 @@
       </c>
       <c r="E1028" s="16" t="n">
         <f aca="false">E1026+E1027</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="F1028" s="16" t="n">
         <f aca="false">F1026+F1027</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G1028" s="16" t="n">
         <f aca="false">G1026+G1027</f>
-        <v>1927.10446122904</v>
+        <v>1903.63175356863</v>
       </c>
     </row>
     <row r="1029" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68451,15 +68451,15 @@
       </c>
       <c r="E1029" s="10" t="n">
         <f aca="false">E1026/E1028</f>
-        <v>0.358982699005556</v>
+        <v>0.363965498254324</v>
       </c>
       <c r="F1029" s="10" t="n">
         <f aca="false">F1026/F1028</f>
-        <v>0.422967749886054</v>
+        <v>0.428245346110634</v>
       </c>
       <c r="G1029" s="10" t="n">
         <f aca="false">G1026/G1028</f>
-        <v>0.429685371749146</v>
+        <v>0.434983601881163</v>
       </c>
     </row>
     <row r="1030" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68479,15 +68479,15 @@
       </c>
       <c r="E1030" s="10" t="n">
         <f aca="false">$D1030+gm_prem_hi*(E1029-$D1029)+0</f>
-        <v>0.66298877865275</v>
+        <v>0.663736198540066</v>
       </c>
       <c r="F1030" s="10" t="n">
         <f aca="false">$D1030+gm_prem_hi*(F1029-$D1029)+0</f>
-        <v>0.672586536284825</v>
+        <v>0.673378175718512</v>
       </c>
       <c r="G1030" s="10" t="n">
         <f aca="false">$D1030+gm_prem_hi*(G1029-$D1029)+0</f>
-        <v>0.673594179564289</v>
+        <v>0.674388914084091</v>
       </c>
       <c r="I1030" s="8" t="s">
         <v>528</v>
@@ -68510,15 +68510,15 @@
       </c>
       <c r="E1031" s="16" t="n">
         <f aca="false">E1028*E1030</f>
-        <v>951.68792719047</v>
+        <v>939.717224246312</v>
       </c>
       <c r="F1031" s="16" t="n">
         <f aca="false">F1028*F1030</f>
-        <v>1209.16701032426</v>
+        <v>1195.67117634201</v>
       </c>
       <c r="G1031" s="16" t="n">
         <f aca="false">G1028*G1030</f>
-        <v>1298.08634849625</v>
+        <v>1283.78815110514</v>
       </c>
     </row>
     <row r="1032" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68538,15 +68538,15 @@
       </c>
       <c r="E1032" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E1028</f>
-        <v>261.793149210416</v>
+        <v>260.041972139376</v>
       </c>
       <c r="F1032" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F1028</f>
-        <v>294.081018087167</v>
+        <v>292.106731770439</v>
       </c>
       <c r="G1032" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G1028</f>
-        <v>305.604594327152</v>
+        <v>303.512931411003</v>
       </c>
       <c r="I1032" s="5" t="s">
         <v>530</v>
@@ -68569,15 +68569,15 @@
       </c>
       <c r="E1033" s="16" t="n">
         <f aca="false">E1031-E1032</f>
-        <v>689.894777980054</v>
+        <v>679.675252106936</v>
       </c>
       <c r="F1033" s="16" t="n">
         <f aca="false">F1031-F1032</f>
-        <v>915.085992237089</v>
+        <v>903.564444571575</v>
       </c>
       <c r="G1033" s="16" t="n">
         <f aca="false">G1031-G1032</f>
-        <v>992.481754169102</v>
+        <v>980.275219694139</v>
       </c>
     </row>
     <row r="1034" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68597,15 +68597,15 @@
       </c>
       <c r="E1034" s="10" t="n">
         <f aca="false">E1033/E1028</f>
-        <v>0.480611850990061</v>
+        <v>0.480064700779575</v>
       </c>
       <c r="F1034" s="10" t="n">
         <f aca="false">F1033/F1028</f>
-        <v>0.50900703762705</v>
+        <v>0.508869486334157</v>
       </c>
       <c r="G1034" s="10" t="n">
         <f aca="false">G1033/G1028</f>
-        <v>0.515011912502207</v>
+        <v>0.514950025316857</v>
       </c>
     </row>
     <row r="1035" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68625,15 +68625,15 @@
       </c>
       <c r="E1035" s="16" t="n">
         <f aca="false">(E1033-fin)*(1-tax)</f>
-        <v>579.458982952747</v>
+        <v>570.6190930725</v>
       </c>
       <c r="F1035" s="16" t="n">
         <f aca="false">(F1033-fin)*(1-tax)</f>
-        <v>774.249383285082</v>
+        <v>764.283244554412</v>
       </c>
       <c r="G1035" s="16" t="n">
         <f aca="false">(G1033-fin)*(1-tax)</f>
-        <v>841.196717356273</v>
+        <v>830.63806503543</v>
       </c>
     </row>
     <row r="1036" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -68653,15 +68653,15 @@
       </c>
       <c r="E1036" s="18" t="n">
         <f aca="false">E1035/shares</f>
-        <v>7.18918327730553</v>
+        <v>7.07950927039575</v>
       </c>
       <c r="F1036" s="18" t="n">
         <f aca="false">F1035/shares</f>
-        <v>9.60589253516006</v>
+        <v>9.48224547814709</v>
       </c>
       <c r="G1036" s="18" t="n">
         <f aca="false">G1035/shares</f>
-        <v>10.4364891239165</v>
+        <v>10.3054909188164</v>
       </c>
     </row>
     <row r="1037" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69270,15 +69270,15 @@
       </c>
       <c r="E1072" s="16" t="n">
         <f aca="false">D1072*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F1072" s="16" t="n">
         <f aca="false">E1072*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G1072" s="16" t="n">
         <f aca="false">F1072*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I1072" s="8" t="s">
         <v>526</v>
@@ -69301,15 +69301,15 @@
       </c>
       <c r="E1073" s="16" t="n">
         <f aca="false">E1071+E1072</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="F1073" s="16" t="n">
         <f aca="false">F1071+F1072</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G1073" s="16" t="n">
         <f aca="false">G1071+G1072</f>
-        <v>1927.10446122904</v>
+        <v>1903.63175356863</v>
       </c>
     </row>
     <row r="1074" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69329,15 +69329,15 @@
       </c>
       <c r="E1074" s="10" t="n">
         <f aca="false">E1071/E1073</f>
-        <v>0.358982699005556</v>
+        <v>0.363965498254324</v>
       </c>
       <c r="F1074" s="10" t="n">
         <f aca="false">F1071/F1073</f>
-        <v>0.422967749886054</v>
+        <v>0.428245346110634</v>
       </c>
       <c r="G1074" s="10" t="n">
         <f aca="false">G1071/G1073</f>
-        <v>0.429685371749146</v>
+        <v>0.434983601881163</v>
       </c>
     </row>
     <row r="1075" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69357,15 +69357,15 @@
       </c>
       <c r="E1075" s="10" t="n">
         <f aca="false">$D1075+gm_prem*(E1074-$D1074)+0</f>
-        <v>0.655359989722361</v>
+        <v>0.655758613662263</v>
       </c>
       <c r="F1075" s="10" t="n">
         <f aca="false">$D1075+gm_prem*(F1074-$D1074)+0</f>
-        <v>0.660478793792801</v>
+        <v>0.660901001490768</v>
       </c>
       <c r="G1075" s="10" t="n">
         <f aca="false">$D1075+gm_prem*(G1074-$D1074)+0</f>
-        <v>0.661016203541849</v>
+        <v>0.66144006195241</v>
       </c>
       <c r="I1075" s="8" t="s">
         <v>528</v>
@@ -69388,15 +69388,15 @@
       </c>
       <c r="E1076" s="16" t="n">
         <f aca="false">E1073*E1075</f>
-        <v>940.737174239736</v>
+        <v>928.422565413409</v>
       </c>
       <c r="F1076" s="16" t="n">
         <f aca="false">F1073*F1075</f>
-        <v>1187.39987405102</v>
+        <v>1173.51631875342</v>
       </c>
       <c r="G1076" s="16" t="n">
         <f aca="false">G1073*G1075</f>
-        <v>1273.84727479018</v>
+        <v>1259.13830501501</v>
       </c>
     </row>
     <row r="1077" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69416,15 +69416,15 @@
       </c>
       <c r="E1077" s="16" t="n">
         <f aca="false">(1-phi_lo)*opx26+phi_lo*opx26/rev26*E1073</f>
-        <v>247.29540575651</v>
+        <v>246.20092008711</v>
       </c>
       <c r="F1077" s="16" t="n">
         <f aca="false">(1-phi_lo)*opx26+phi_lo*opx26/rev26*F1073</f>
-        <v>267.475323804479</v>
+        <v>266.241394856524</v>
       </c>
       <c r="G1077" s="16" t="n">
         <f aca="false">(1-phi_lo)*opx26+phi_lo*opx26/rev26*G1073</f>
-        <v>274.67755895447</v>
+        <v>273.370269631877</v>
       </c>
       <c r="I1077" s="5" t="s">
         <v>530</v>
@@ -69447,15 +69447,15 @@
       </c>
       <c r="E1078" s="16" t="n">
         <f aca="false">E1076-E1077</f>
-        <v>693.441768483226</v>
+        <v>682.221645326299</v>
       </c>
       <c r="F1078" s="16" t="n">
         <f aca="false">F1076-F1077</f>
-        <v>919.924550246539</v>
+        <v>907.274923896894</v>
       </c>
       <c r="G1078" s="16" t="n">
         <f aca="false">G1076-G1077</f>
-        <v>999.169715835708</v>
+        <v>985.768035383132</v>
       </c>
     </row>
     <row r="1079" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69475,15 +69475,15 @@
       </c>
       <c r="E1079" s="10" t="n">
         <f aca="false">E1078/E1073</f>
-        <v>0.483082844720677</v>
+        <v>0.481863256038327</v>
       </c>
       <c r="F1079" s="10" t="n">
         <f aca="false">F1078/F1073</f>
-        <v>0.51169843504726</v>
+        <v>0.510959154337001</v>
       </c>
       <c r="G1079" s="10" t="n">
         <f aca="false">G1078/G1073</f>
-        <v>0.518482384290924</v>
+        <v>0.517835465570045</v>
       </c>
     </row>
     <row r="1080" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69503,15 +69503,15 @@
       </c>
       <c r="E1080" s="16" t="n">
         <f aca="false">(E1078-fin)*(1-tax)</f>
-        <v>582.52712973799</v>
+        <v>572.821723207248</v>
       </c>
       <c r="F1080" s="16" t="n">
         <f aca="false">(F1078-fin)*(1-tax)</f>
-        <v>778.434735963256</v>
+        <v>767.492809170814</v>
       </c>
       <c r="G1080" s="16" t="n">
         <f aca="false">(G1078-fin)*(1-tax)</f>
-        <v>846.981804197887</v>
+        <v>835.389350606409</v>
       </c>
     </row>
     <row r="1081" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -69531,15 +69531,15 @@
       </c>
       <c r="E1081" s="18" t="n">
         <f aca="false">E1080/shares</f>
-        <v>7.22724890439857</v>
+        <v>7.10683667785112</v>
       </c>
       <c r="F1081" s="18" t="n">
         <f aca="false">F1080/shares</f>
-        <v>9.65781901894711</v>
+        <v>9.52206563616774</v>
       </c>
       <c r="G1081" s="18" t="n">
         <f aca="false">G1080/shares</f>
-        <v>10.5082630558133</v>
+        <v>10.3644387715161</v>
       </c>
     </row>
     <row r="1082" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70148,15 +70148,15 @@
       </c>
       <c r="E1117" s="16" t="n">
         <f aca="false">D1117*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F1117" s="16" t="n">
         <f aca="false">E1117*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G1117" s="16" t="n">
         <f aca="false">F1117*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I1117" s="8" t="s">
         <v>526</v>
@@ -70179,15 +70179,15 @@
       </c>
       <c r="E1118" s="16" t="n">
         <f aca="false">E1116+E1117</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="F1118" s="16" t="n">
         <f aca="false">F1116+F1117</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G1118" s="16" t="n">
         <f aca="false">G1116+G1117</f>
-        <v>1927.10446122904</v>
+        <v>1903.63175356863</v>
       </c>
     </row>
     <row r="1119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70207,15 +70207,15 @@
       </c>
       <c r="E1119" s="10" t="n">
         <f aca="false">E1116/E1118</f>
-        <v>0.358982699005556</v>
+        <v>0.363965498254324</v>
       </c>
       <c r="F1119" s="10" t="n">
         <f aca="false">F1116/F1118</f>
-        <v>0.422967749886054</v>
+        <v>0.428245346110634</v>
       </c>
       <c r="G1119" s="10" t="n">
         <f aca="false">G1116/G1118</f>
-        <v>0.429685371749146</v>
+        <v>0.434983601881163</v>
       </c>
     </row>
     <row r="1120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70235,15 +70235,15 @@
       </c>
       <c r="E1120" s="10" t="n">
         <f aca="false">$D1120+gm_prem*(E1119-$D1119)+0</f>
-        <v>0.655359989722361</v>
+        <v>0.655758613662263</v>
       </c>
       <c r="F1120" s="10" t="n">
         <f aca="false">$D1120+gm_prem*(F1119-$D1119)+0</f>
-        <v>0.660478793792801</v>
+        <v>0.660901001490768</v>
       </c>
       <c r="G1120" s="10" t="n">
         <f aca="false">$D1120+gm_prem*(G1119-$D1119)+0</f>
-        <v>0.661016203541849</v>
+        <v>0.66144006195241</v>
       </c>
       <c r="I1120" s="8" t="s">
         <v>528</v>
@@ -70266,15 +70266,15 @@
       </c>
       <c r="E1121" s="16" t="n">
         <f aca="false">E1118*E1120</f>
-        <v>940.737174239736</v>
+        <v>928.422565413409</v>
       </c>
       <c r="F1121" s="16" t="n">
         <f aca="false">F1118*F1120</f>
-        <v>1187.39987405102</v>
+        <v>1173.51631875342</v>
       </c>
       <c r="G1121" s="16" t="n">
         <f aca="false">G1118*G1120</f>
-        <v>1273.84727479018</v>
+        <v>1259.13830501501</v>
       </c>
     </row>
     <row r="1122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70294,15 +70294,15 @@
       </c>
       <c r="E1122" s="16" t="n">
         <f aca="false">(1-phi_hi)*opx26+phi_hi*opx26/rev26*E1118</f>
-        <v>281.123473815624</v>
+        <v>278.496708209064</v>
       </c>
       <c r="F1122" s="16" t="n">
         <f aca="false">(1-phi_hi)*opx26+phi_hi*opx26/rev26*F1118</f>
-        <v>329.55527713075</v>
+        <v>326.593847655658</v>
       </c>
       <c r="G1122" s="16" t="n">
         <f aca="false">(1-phi_hi)*opx26+phi_hi*opx26/rev26*G1118</f>
-        <v>346.840641490728</v>
+        <v>343.703147116505</v>
       </c>
       <c r="I1122" s="5" t="s">
         <v>530</v>
@@ -70325,15 +70325,15 @@
       </c>
       <c r="E1123" s="16" t="n">
         <f aca="false">E1121-E1122</f>
-        <v>659.613700424111</v>
+        <v>649.925857204345</v>
       </c>
       <c r="F1123" s="16" t="n">
         <f aca="false">F1121-F1122</f>
-        <v>857.844596920268</v>
+        <v>846.922471097761</v>
       </c>
       <c r="G1123" s="16" t="n">
         <f aca="false">G1121-G1122</f>
-        <v>927.00663329945</v>
+        <v>915.435157898504</v>
       </c>
     </row>
     <row r="1124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70353,15 +70353,15 @@
       </c>
       <c r="E1124" s="10" t="n">
         <f aca="false">E1123/E1118</f>
-        <v>0.459516685178332</v>
+        <v>0.459052262386366</v>
       </c>
       <c r="F1124" s="10" t="n">
         <f aca="false">F1123/F1118</f>
-        <v>0.477167108585381</v>
+        <v>0.476969855798961</v>
       </c>
       <c r="G1124" s="10" t="n">
         <f aca="false">G1123/G1118</f>
-        <v>0.481036006064891</v>
+        <v>0.480888783338684</v>
       </c>
     </row>
     <row r="1125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70381,15 +70381,15 @@
       </c>
       <c r="E1125" s="16" t="n">
         <f aca="false">(E1123-fin)*(1-tax)</f>
-        <v>553.265850866856</v>
+        <v>544.885866481758</v>
       </c>
       <c r="F1125" s="16" t="n">
         <f aca="false">(F1123-fin)*(1-tax)</f>
-        <v>724.735576336032</v>
+        <v>715.287937499563</v>
       </c>
       <c r="G1125" s="16" t="n">
         <f aca="false">(G1123-fin)*(1-tax)</f>
-        <v>784.560737804024</v>
+        <v>774.551411582206</v>
       </c>
     </row>
     <row r="1126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -70409,15 +70409,15 @@
       </c>
       <c r="E1126" s="18" t="n">
         <f aca="false">E1125/shares</f>
-        <v>6.86421251541902</v>
+        <v>6.76024442556659</v>
       </c>
       <c r="F1126" s="18" t="n">
         <f aca="false">F1125/shares</f>
-        <v>8.99158877357203</v>
+        <v>8.87437459770913</v>
       </c>
       <c r="G1126" s="18" t="n">
         <f aca="false">G1125/shares</f>
-        <v>9.73382258656112</v>
+        <v>9.60963971459267</v>
       </c>
     </row>
     <row r="1127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71026,15 +71026,15 @@
       </c>
       <c r="E1162" s="16" t="n">
         <f aca="false">D1162*(1+el*eqgA_27)</f>
-        <v>907.131264603358</v>
+        <v>887.757520580663</v>
       </c>
       <c r="F1162" s="16" t="n">
         <f aca="false">E1162*(1+el*eqgA_28)</f>
-        <v>1022.70459840977</v>
+        <v>1000.8625366558</v>
       </c>
       <c r="G1162" s="16" t="n">
         <f aca="false">F1162*(1+el*eqgA_29)</f>
-        <v>1083.50712079754</v>
+        <v>1060.36649008156</v>
       </c>
       <c r="I1162" s="8" t="s">
         <v>526</v>
@@ -71057,15 +71057,15 @@
       </c>
       <c r="E1163" s="16" t="n">
         <f aca="false">E1161+E1162</f>
-        <v>1416.23169290067</v>
+        <v>1396.85794887797</v>
       </c>
       <c r="F1163" s="16" t="n">
         <f aca="false">F1161+F1162</f>
-        <v>1774.67898669534</v>
+        <v>1752.83692494137</v>
       </c>
       <c r="G1163" s="16" t="n">
         <f aca="false">G1161+G1162</f>
-        <v>1901.64823175754</v>
+        <v>1878.50760104157</v>
       </c>
     </row>
     <row r="1164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71085,15 +71085,15 @@
       </c>
       <c r="E1164" s="10" t="n">
         <f aca="false">E1161/E1163</f>
-        <v>0.359475381640833</v>
+        <v>0.364461131288436</v>
       </c>
       <c r="F1164" s="10" t="n">
         <f aca="false">F1161/F1163</f>
-        <v>0.423724174300295</v>
+        <v>0.429004191767993</v>
       </c>
       <c r="G1164" s="10" t="n">
         <f aca="false">G1161/G1163</f>
-        <v>0.430227366606001</v>
+        <v>0.43552717620433</v>
       </c>
     </row>
     <row r="1165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71113,15 +71113,15 @@
       </c>
       <c r="E1165" s="10" t="n">
         <f aca="false">$D1165+gm_prem*(E1164-$D1164)+0</f>
-        <v>0.664678956571593</v>
+        <v>0.665077816543402</v>
       </c>
       <c r="F1165" s="10" t="n">
         <f aca="false">$D1165+gm_prem*(F1164-$D1164)+0</f>
-        <v>0.66981885998435</v>
+        <v>0.670241261381766</v>
       </c>
       <c r="G1165" s="10" t="n">
         <f aca="false">$D1165+gm_prem*(G1164-$D1164)+0</f>
-        <v>0.670339115368807</v>
+        <v>0.670763100136673</v>
       </c>
       <c r="I1165" s="8" t="s">
         <v>528</v>
@@ -71144,15 +71144,15 @@
       </c>
       <c r="E1166" s="16" t="n">
         <f aca="false">E1163*E1165</f>
-        <v>941.339403900837</v>
+        <v>929.019234661057</v>
       </c>
       <c r="F1166" s="16" t="n">
         <f aca="false">F1163*F1165</f>
-        <v>1188.71345570645</v>
+        <v>1174.82363156924</v>
       </c>
       <c r="G1166" s="16" t="n">
         <f aca="false">G1163*G1165</f>
-        <v>1274.749193419</v>
+        <v>1260.03358210495</v>
       </c>
     </row>
     <row r="1167" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71172,15 +71172,15 @@
       </c>
       <c r="E1167" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E1163</f>
-        <v>260.08050567738</v>
+        <v>258.354103146172</v>
       </c>
       <c r="F1167" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F1163</f>
-        <v>292.021895766293</v>
+        <v>290.075540397156</v>
       </c>
       <c r="G1167" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G1163</f>
-        <v>303.336178942747</v>
+        <v>301.274107543693</v>
       </c>
       <c r="I1167" s="5" t="s">
         <v>530</v>
@@ -71203,15 +71203,15 @@
       </c>
       <c r="E1168" s="16" t="n">
         <f aca="false">E1166-E1167</f>
-        <v>681.258898223457</v>
+        <v>670.665131514885</v>
       </c>
       <c r="F1168" s="16" t="n">
         <f aca="false">F1166-F1167</f>
-        <v>896.691559940159</v>
+        <v>884.748091172081</v>
       </c>
       <c r="G1168" s="16" t="n">
         <f aca="false">G1166-G1167</f>
-        <v>971.413014476257</v>
+        <v>958.759474561254</v>
       </c>
     </row>
     <row r="1169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71231,15 +71231,15 @@
       </c>
       <c r="E1169" s="10" t="n">
         <f aca="false">E1168/E1163</f>
-        <v>0.48103633158225</v>
+        <v>0.480124075646774</v>
       </c>
       <c r="F1169" s="10" t="n">
         <f aca="false">F1168/F1163</f>
-        <v>0.505269722954181</v>
+        <v>0.504752084225791</v>
       </c>
       <c r="G1169" s="10" t="n">
         <f aca="false">G1168/G1163</f>
-        <v>0.510826870213772</v>
+        <v>0.510383601338453</v>
       </c>
     </row>
     <row r="1170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71259,15 +71259,15 @@
       </c>
       <c r="E1170" s="16" t="n">
         <f aca="false">(E1168-fin)*(1-tax)</f>
-        <v>571.988946963291</v>
+        <v>562.825338760375</v>
       </c>
       <c r="F1170" s="16" t="n">
         <f aca="false">(F1168-fin)*(1-tax)</f>
-        <v>758.338199348238</v>
+        <v>748.00709886385</v>
       </c>
       <c r="G1170" s="16" t="n">
         <f aca="false">(G1168-fin)*(1-tax)</f>
-        <v>822.972257521963</v>
+        <v>812.026945495485</v>
       </c>
     </row>
     <row r="1171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71287,15 +71287,15 @@
       </c>
       <c r="E1171" s="18" t="n">
         <f aca="false">E1170/shares</f>
-        <v>7.09650465915276</v>
+        <v>6.98281437081436</v>
       </c>
       <c r="F1171" s="18" t="n">
         <f aca="false">F1170/shares</f>
-        <v>9.40848698818243</v>
+        <v>9.28031195418769</v>
       </c>
       <c r="G1171" s="18" t="n">
         <f aca="false">G1170/shares</f>
-        <v>10.2103834188826</v>
+        <v>10.0745880364645</v>
       </c>
     </row>
     <row r="1172" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71904,15 +71904,15 @@
       </c>
       <c r="E1207" s="16" t="n">
         <f aca="false">D1207*(1+el*eqgA_27)</f>
-        <v>933.166629174881</v>
+        <v>913.236843806872</v>
       </c>
       <c r="F1207" s="16" t="n">
         <f aca="false">E1207*(1+el*eqgA_28)</f>
-        <v>1052.05700649838</v>
+        <v>1029.5880607829</v>
       </c>
       <c r="G1207" s="16" t="n">
         <f aca="false">F1207*(1+el*eqgA_29)</f>
-        <v>1114.60460801526</v>
+        <v>1090.79982341042</v>
       </c>
       <c r="I1207" s="8" t="s">
         <v>526</v>
@@ -71935,15 +71935,15 @@
       </c>
       <c r="E1208" s="16" t="n">
         <f aca="false">E1206+E1207</f>
-        <v>1454.67037311735</v>
+        <v>1434.74058774934</v>
       </c>
       <c r="F1208" s="16" t="n">
         <f aca="false">F1206+F1207</f>
-        <v>1820.89405882932</v>
+        <v>1798.42511311385</v>
       </c>
       <c r="G1208" s="16" t="n">
         <f aca="false">G1206+G1207</f>
-        <v>1952.56069070054</v>
+        <v>1928.75590609569</v>
       </c>
     </row>
     <row r="1209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71963,15 +71963,15 @@
       </c>
       <c r="E1209" s="10" t="n">
         <f aca="false">E1206/E1208</f>
-        <v>0.358503035175513</v>
+        <v>0.363482951827927</v>
       </c>
       <c r="F1209" s="10" t="n">
         <f aca="false">F1206/F1208</f>
-        <v>0.422230523847852</v>
+        <v>0.427505736393859</v>
       </c>
       <c r="G1209" s="10" t="n">
         <f aca="false">G1206/G1208</f>
-        <v>0.429157509252442</v>
+        <v>0.434454188856647</v>
       </c>
     </row>
     <row r="1210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -71991,15 +71991,15 @@
       </c>
       <c r="E1210" s="10" t="n">
         <f aca="false">$D1210+gm_prem*(E1209-$D1209)+0</f>
-        <v>0.646300964040303</v>
+        <v>0.646699357372496</v>
       </c>
       <c r="F1210" s="10" t="n">
         <f aca="false">$D1210+gm_prem*(F1209-$D1209)+0</f>
-        <v>0.65139916313409</v>
+        <v>0.651821180137771</v>
       </c>
       <c r="G1210" s="10" t="n">
         <f aca="false">$D1210+gm_prem*(G1209-$D1209)+0</f>
-        <v>0.651953321966457</v>
+        <v>0.652377056334794</v>
       </c>
       <c r="I1210" s="8" t="s">
         <v>528</v>
@@ -72022,15 +72022,15 @@
       </c>
       <c r="E1211" s="16" t="n">
         <f aca="false">E1208*E1210</f>
-        <v>940.154864506607</v>
+        <v>927.845816093733</v>
       </c>
       <c r="F1211" s="16" t="n">
         <f aca="false">F1208*F1210</f>
-        <v>1186.12886607726</v>
+        <v>1172.25157961927</v>
       </c>
       <c r="G1211" s="16" t="n">
         <f aca="false">G1208*G1210</f>
-        <v>1272.97842864333</v>
+        <v>1258.27610040705</v>
       </c>
     </row>
     <row r="1212" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72050,15 +72050,15 @@
       </c>
       <c r="E1212" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E1208</f>
-        <v>263.505792743453</v>
+        <v>261.72984113258</v>
       </c>
       <c r="F1212" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F1208</f>
-        <v>296.140140408041</v>
+        <v>294.137923143721</v>
       </c>
       <c r="G1212" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G1208</f>
-        <v>307.873009711557</v>
+        <v>305.751755278313</v>
       </c>
       <c r="I1212" s="5" t="s">
         <v>530</v>
@@ -72081,15 +72081,15 @@
       </c>
       <c r="E1213" s="16" t="n">
         <f aca="false">E1211-E1212</f>
-        <v>676.649071763154</v>
+        <v>666.115974961154</v>
       </c>
       <c r="F1213" s="16" t="n">
         <f aca="false">F1211-F1212</f>
-        <v>889.988725669217</v>
+        <v>878.113656475553</v>
       </c>
       <c r="G1213" s="16" t="n">
         <f aca="false">G1211-G1212</f>
-        <v>965.105418931777</v>
+        <v>952.52434512874</v>
       </c>
     </row>
     <row r="1214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72109,15 +72109,15 @@
       </c>
       <c r="E1214" s="10" t="n">
         <f aca="false">E1213/E1208</f>
-        <v>0.465156288508923</v>
+        <v>0.464276246625241</v>
       </c>
       <c r="F1214" s="10" t="n">
         <f aca="false">F1213/F1208</f>
-        <v>0.488764693010972</v>
+        <v>0.488268124189591</v>
       </c>
       <c r="G1214" s="10" t="n">
         <f aca="false">G1213/G1208</f>
-        <v>0.494276784085784</v>
+        <v>0.493854272652313</v>
       </c>
     </row>
     <row r="1215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72137,15 +72137,15 @@
       </c>
       <c r="E1215" s="16" t="n">
         <f aca="false">(E1213-fin)*(1-tax)</f>
-        <v>568.001447075129</v>
+        <v>558.890318341398</v>
       </c>
       <c r="F1215" s="16" t="n">
         <f aca="false">(F1213-fin)*(1-tax)</f>
-        <v>752.540247703873</v>
+        <v>742.268312851353</v>
       </c>
       <c r="G1215" s="16" t="n">
         <f aca="false">(G1213-fin)*(1-tax)</f>
-        <v>817.516187375987</v>
+        <v>806.63355853636</v>
       </c>
     </row>
     <row r="1216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72165,15 +72165,15 @@
       </c>
       <c r="E1216" s="18" t="n">
         <f aca="false">E1215/shares</f>
-        <v>7.04703287882389</v>
+        <v>6.93399368837742</v>
       </c>
       <c r="F1216" s="18" t="n">
         <f aca="false">F1215/shares</f>
-        <v>9.33655344632603</v>
+        <v>9.20911246354757</v>
       </c>
       <c r="G1216" s="18" t="n">
         <f aca="false">G1215/shares</f>
-        <v>10.1426915038252</v>
+        <v>10.0076738139306</v>
       </c>
     </row>
     <row r="1217" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72782,15 +72782,15 @@
       </c>
       <c r="E1252" s="16" t="n">
         <f aca="false">D1252*(1+el*eqgA_27)</f>
-        <v>920.148946889119</v>
+        <v>900.497182193768</v>
       </c>
       <c r="F1252" s="16" t="n">
         <f aca="false">E1252*(1+el*eqgA_28)</f>
-        <v>1037.38080245407</v>
+        <v>1015.22529871935</v>
       </c>
       <c r="G1252" s="16" t="n">
         <f aca="false">F1252*(1+el*eqgA_29)</f>
-        <v>1099.0558644064</v>
+        <v>1075.58315674599</v>
       </c>
       <c r="I1252" s="8" t="s">
         <v>526</v>
@@ -72813,15 +72813,15 @@
       </c>
       <c r="E1253" s="16" t="n">
         <f aca="false">E1251+E1252</f>
-        <v>1435.45103300901</v>
+        <v>1415.79926831366</v>
       </c>
       <c r="F1253" s="16" t="n">
         <f aca="false">F1251+F1252</f>
-        <v>1797.78652276233</v>
+        <v>1775.63101902761</v>
       </c>
       <c r="G1253" s="16" t="n">
         <f aca="false">G1251+G1252</f>
-        <v>1927.10446122904</v>
+        <v>1903.63175356863</v>
       </c>
     </row>
     <row r="1254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72841,15 +72841,15 @@
       </c>
       <c r="E1254" s="10" t="n">
         <f aca="false">E1251/E1253</f>
-        <v>0.358982699005556</v>
+        <v>0.363965498254324</v>
       </c>
       <c r="F1254" s="10" t="n">
         <f aca="false">F1251/F1253</f>
-        <v>0.422967749886054</v>
+        <v>0.428245346110634</v>
       </c>
       <c r="G1254" s="10" t="n">
         <f aca="false">G1251/G1253</f>
-        <v>0.429685371749146</v>
+        <v>0.434983601881163</v>
       </c>
     </row>
     <row r="1255" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72869,15 +72869,15 @@
       </c>
       <c r="E1255" s="10" t="n">
         <f aca="false">$D1255+gm_prem*(E1254-$D1254)+0</f>
-        <v>0.655359989722361</v>
+        <v>0.655758613662263</v>
       </c>
       <c r="F1255" s="10" t="n">
         <f aca="false">$D1255+gm_prem*(F1254-$D1254)+0</f>
-        <v>0.660478793792801</v>
+        <v>0.660901001490768</v>
       </c>
       <c r="G1255" s="10" t="n">
         <f aca="false">$D1255+gm_prem*(G1254-$D1254)+0</f>
-        <v>0.661016203541849</v>
+        <v>0.66144006195241</v>
       </c>
       <c r="I1255" s="8" t="s">
         <v>528</v>
@@ -72900,15 +72900,15 @@
       </c>
       <c r="E1256" s="16" t="n">
         <f aca="false">E1253*E1255</f>
-        <v>940.737174239736</v>
+        <v>928.422565413409</v>
       </c>
       <c r="F1256" s="16" t="n">
         <f aca="false">F1253*F1255</f>
-        <v>1187.39987405102</v>
+        <v>1173.51631875342</v>
       </c>
       <c r="G1256" s="16" t="n">
         <f aca="false">G1253*G1255</f>
-        <v>1273.84727479018</v>
+        <v>1259.13830501501</v>
       </c>
     </row>
     <row r="1257" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72928,15 +72928,15 @@
       </c>
       <c r="E1257" s="16" t="n">
         <f aca="false">opex_fix+opex_var*E1253</f>
-        <v>261.793149210416</v>
+        <v>260.041972139376</v>
       </c>
       <c r="F1257" s="16" t="n">
         <f aca="false">opex_fix+opex_var*F1253</f>
-        <v>294.081018087167</v>
+        <v>292.106731770439</v>
       </c>
       <c r="G1257" s="16" t="n">
         <f aca="false">opex_fix+opex_var*G1253</f>
-        <v>305.604594327152</v>
+        <v>303.512931411003</v>
       </c>
       <c r="I1257" s="5" t="s">
         <v>530</v>
@@ -72959,15 +72959,15 @@
       </c>
       <c r="E1258" s="16" t="n">
         <f aca="false">E1256-E1257</f>
-        <v>678.944025029319</v>
+        <v>668.380593274033</v>
       </c>
       <c r="F1258" s="16" t="n">
         <f aca="false">F1256-F1257</f>
-        <v>893.318855963851</v>
+        <v>881.40958698298</v>
       </c>
       <c r="G1258" s="16" t="n">
         <f aca="false">G1256-G1257</f>
-        <v>968.242680463026</v>
+        <v>955.625373604005</v>
       </c>
     </row>
     <row r="1259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -72987,15 +72987,15 @@
       </c>
       <c r="E1259" s="10" t="n">
         <f aca="false">E1258/E1253</f>
-        <v>0.472983062059672</v>
+        <v>0.472087115901772</v>
       </c>
       <c r="F1259" s="10" t="n">
         <f aca="false">F1258/F1253</f>
-        <v>0.496899295135026</v>
+        <v>0.496392312106413</v>
       </c>
       <c r="G1259" s="10" t="n">
         <f aca="false">G1258/G1253</f>
-        <v>0.502433936479767</v>
+        <v>0.502001173185176</v>
       </c>
     </row>
     <row r="1260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73015,15 +73015,15 @@
       </c>
       <c r="E1260" s="16" t="n">
         <f aca="false">(E1258-fin)*(1-tax_hi)</f>
-        <v>553.512981024628</v>
+        <v>544.639698350188</v>
       </c>
       <c r="F1260" s="16" t="n">
         <f aca="false">(F1258-fin)*(1-tax_hi)</f>
-        <v>733.587839009635</v>
+        <v>723.584053065703</v>
       </c>
       <c r="G1260" s="16" t="n">
         <f aca="false">(G1258-fin)*(1-tax_hi)</f>
-        <v>796.523851588942</v>
+        <v>785.925313827364</v>
       </c>
     </row>
     <row r="1261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73043,15 +73043,15 @@
       </c>
       <c r="E1261" s="18" t="n">
         <f aca="false">E1260/shares</f>
-        <v>6.86727858920481</v>
+        <v>6.75719028736707</v>
       </c>
       <c r="F1261" s="18" t="n">
         <f aca="false">F1260/shares</f>
-        <v>9.10141628622029</v>
+        <v>8.97730215090844</v>
       </c>
       <c r="G1261" s="18" t="n">
         <f aca="false">G1260/shares</f>
-        <v>9.88224554676579</v>
+        <v>9.75075249431338</v>
       </c>
     </row>
     <row r="1262" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73116,15 +73116,15 @@
       </c>
       <c r="C1267" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>97.6798684202028</v>
+        <v>96.2266486628942</v>
       </c>
       <c r="D1267" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>222.178187448096</v>
+        <v>218.34283553683</v>
       </c>
       <c r="E1267" s="13" t="n">
         <f aca="false">tp_w_dcf*C1267+(1-tp_w_dcf)*D1267</f>
-        <v>159.929027934149</v>
+        <v>157.284742099862</v>
       </c>
       <c r="F1267" s="10" t="n">
         <f aca="false">E1267/E$1267-1</f>
@@ -73140,19 +73140,19 @@
       </c>
       <c r="C1268" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!B82*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!B83*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!B84*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B85*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B86*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*MAX(0,Val!C81*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!C82*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!C83*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!C84*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C85*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C86*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*MAX(0,Val!D81*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!D82*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!D83*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!D84*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D85*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D86*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
-        <v>84.5300035208355</v>
+        <v>83.26460195942</v>
       </c>
       <c r="D1268" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>222.178187448096</v>
+        <v>218.34283553683</v>
       </c>
       <c r="E1268" s="13" t="n">
         <f aca="false">tp_w_dcf*C1268+(1-tp_w_dcf)*D1268</f>
-        <v>153.354095484466</v>
+        <v>150.803718748125</v>
       </c>
       <c r="F1268" s="10" t="n">
         <f aca="false">E1268/E$1267-1</f>
-        <v>-0.0411115638893955</v>
+        <v>-0.0412056710982317</v>
       </c>
     </row>
     <row r="1269" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73164,19 +73164,19 @@
       </c>
       <c r="C1269" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!B82*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!B83*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!B84*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B85*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B86*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*MAX(0,Val!C81*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!C82*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!C83*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!C84*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C85*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C86*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*MAX(0,Val!D81*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!D82*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!D83*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!D84*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D85*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D86*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
-        <v>116.08316484556</v>
+        <v>114.367271996706</v>
       </c>
       <c r="D1269" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>222.178187448096</v>
+        <v>218.34283553683</v>
       </c>
       <c r="E1269" s="13" t="n">
         <f aca="false">tp_w_dcf*C1269+(1-tp_w_dcf)*D1269</f>
-        <v>169.130676146828</v>
+        <v>166.355053766768</v>
       </c>
       <c r="F1269" s="10" t="n">
         <f aca="false">E1269/E$1267-1</f>
-        <v>0.0575358228055221</v>
+        <v>0.0576680963824652</v>
       </c>
     </row>
     <row r="1270" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73188,19 +73188,19 @@
       </c>
       <c r="C1270" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B82*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B83*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B84*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B85*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B86*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B86*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*MAX(0,Val!C81*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C82*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C83*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C84*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C85*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C86*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C86*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*MAX(0,Val!D81*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D82*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D83*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D84*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D85*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D86*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D86*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>108.618992598606</v>
+        <v>107.011994083856</v>
       </c>
       <c r="D1270" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>222.178187448096</v>
+        <v>218.34283553683</v>
       </c>
       <c r="E1270" s="13" t="n">
         <f aca="false">tp_w_dcf*C1270+(1-tp_w_dcf)*D1270</f>
-        <v>165.398590023351</v>
+        <v>162.677414810343</v>
       </c>
       <c r="F1270" s="10" t="n">
         <f aca="false">E1270/E$1267-1</f>
-        <v>0.0341999333070009</v>
+        <v>0.0342860511355709</v>
       </c>
     </row>
     <row r="1271" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73212,19 +73212,19 @@
       </c>
       <c r="C1271" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B82*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B83*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B84*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B85*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B86*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B86*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*MAX(0,Val!C81*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C82*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C83*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C84*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C85*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C86*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C86*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*MAX(0,Val!D81*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D82*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D83*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D84*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D85*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D86*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D86*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>90.0972926493276</v>
+        <v>88.7500345650288</v>
       </c>
       <c r="D1271" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>222.178187448096</v>
+        <v>218.34283553683</v>
       </c>
       <c r="E1271" s="13" t="n">
         <f aca="false">tp_w_dcf*C1271+(1-tp_w_dcf)*D1271</f>
-        <v>156.137740048712</v>
+        <v>153.54643505093</v>
       </c>
       <c r="F1271" s="10" t="n">
         <f aca="false">E1271/E$1267-1</f>
-        <v>-0.023706064711396</v>
+        <v>-0.0237677666569794</v>
       </c>
     </row>
     <row r="1272" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73236,19 +73236,19 @@
       </c>
       <c r="C1272" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>97.6798684202028</v>
+        <v>96.2266486628942</v>
       </c>
       <c r="D1272" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>222.178187448096</v>
+        <v>218.34283553683</v>
       </c>
       <c r="E1272" s="13" t="n">
         <f aca="false">0.3*C1272+(1-0.3)*D1272</f>
-        <v>184.828691739728</v>
+        <v>181.70797947465</v>
       </c>
       <c r="F1272" s="10" t="n">
         <f aca="false">E1272/E$1267-1</f>
-        <v>0.155691959910061</v>
+        <v>0.155280398141102</v>
       </c>
     </row>
     <row r="1273" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -73260,19 +73260,19 @@
       </c>
       <c r="C1273" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D81*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D82*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D83*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D84*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D85*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D86*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D86*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>97.6798684202028</v>
+        <v>96.2266486628942</v>
       </c>
       <c r="D1273" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>222.178187448096</v>
+        <v>218.34283553683</v>
       </c>
       <c r="E1273" s="13" t="n">
         <f aca="false">0.7*C1273+(1-0.7)*D1273</f>
-        <v>135.029364128571</v>
+        <v>132.861504725075</v>
       </c>
       <c r="F1273" s="10" t="n">
         <f aca="false">E1273/E$1267-1</f>
-        <v>-0.155691959910061</v>
+        <v>-0.155280398141103</v>
       </c>
     </row>
   </sheetData>
